--- a/2026年1月_売上データ_clean.xlsx
+++ b/2026年1月_売上データ_clean.xlsx
@@ -18,10 +18,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="1">
+  <numFmts count="2">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
+    <numFmt numFmtId="165" formatCode="yyyy-mm-dd"/>
   </numFmts>
-  <fonts count="5">
+  <fonts count="6">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -44,6 +45,10 @@
     <font>
       <name val="Arial"/>
       <sz val="11"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <color rgb="00CC6600"/>
     </font>
   </fonts>
   <fills count="4">
@@ -76,13 +81,15 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -448,7 +455,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N269"/>
+  <dimension ref="A1:O269"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -465,6 +472,7 @@
     <col width="14" customWidth="1" min="12" max="12"/>
     <col width="14" customWidth="1" min="13" max="13"/>
     <col width="12" customWidth="1" min="14" max="14"/>
+    <col width="10" customWidth="1" min="15" max="15"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -538,6 +546,11 @@
           <t>有効フラグ</t>
         </is>
       </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>単価補完</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -545,7 +558,7 @@
           <t>A-20260001</t>
         </is>
       </c>
-      <c r="B2" s="3" t="n">
+      <c r="B2" s="6" t="n">
         <v>46040</v>
       </c>
       <c r="C2" s="2" t="inlineStr">
@@ -578,15 +591,11 @@
           <t>コーヒーゼリー 4個</t>
         </is>
       </c>
-      <c r="I2" s="2" t="inlineStr">
-        <is>
-          <t>２０</t>
-        </is>
-      </c>
-      <c r="J2" s="2" t="inlineStr">
-        <is>
-          <t>980円</t>
-        </is>
+      <c r="I2" s="2" t="n">
+        <v>20</v>
+      </c>
+      <c r="J2" s="2" t="n">
+        <v>980</v>
       </c>
       <c r="K2" s="2" t="n">
         <v>0</v>
@@ -606,6 +615,7 @@
           <t>無効</t>
         </is>
       </c>
+      <c r="O2" s="2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -613,7 +623,7 @@
           <t>A-20260002</t>
         </is>
       </c>
-      <c r="B3" s="3" t="n">
+      <c r="B3" s="6" t="n">
         <v>46035</v>
       </c>
       <c r="C3" s="2" t="inlineStr">
@@ -623,7 +633,7 @@
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>オフライン</t>
+          <t>店頭</t>
         </is>
       </c>
       <c r="E3" s="2" t="inlineStr">
@@ -638,7 +648,7 @@
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t>お菓子</t>
+          <t>菓子</t>
         </is>
       </c>
       <c r="H3" s="2" t="inlineStr">
@@ -666,6 +676,7 @@
           <t>有効</t>
         </is>
       </c>
+      <c r="O3" s="2" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -673,7 +684,7 @@
           <t>A-20260003</t>
         </is>
       </c>
-      <c r="B4" s="3" t="n">
+      <c r="B4" s="6" t="n">
         <v>46042</v>
       </c>
       <c r="C4" s="2" t="inlineStr">
@@ -726,6 +737,7 @@
           <t>有効</t>
         </is>
       </c>
+      <c r="O4" s="2" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -733,10 +745,8 @@
           <t>A-20260004</t>
         </is>
       </c>
-      <c r="B5" s="2" t="inlineStr">
-        <is>
-          <t>2026-01-11</t>
-        </is>
+      <c r="B5" s="6" t="n">
+        <v>46033</v>
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
@@ -745,7 +755,7 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>オフライン</t>
+          <t>店頭</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
@@ -756,7 +766,7 @@
       <c r="F5" s="2" t="n"/>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>コーヒー</t>
+          <t>コーヒー豆</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
@@ -784,6 +794,7 @@
           <t>有効</t>
         </is>
       </c>
+      <c r="O5" s="2" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -791,17 +802,17 @@
           <t>A-20260005</t>
         </is>
       </c>
-      <c r="B6" s="3" t="n">
+      <c r="B6" s="6" t="n">
         <v>46051</v>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">渋谷店 </t>
+          <t>渋谷店</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>Web</t>
+          <t>EC</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
@@ -812,7 +823,7 @@
       <c r="F6" s="2" t="n"/>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>コーヒー</t>
+          <t>コーヒー豆</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
@@ -840,6 +851,7 @@
           <t>有効</t>
         </is>
       </c>
+      <c r="O6" s="2" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
@@ -847,7 +859,7 @@
           <t>A-20260006</t>
         </is>
       </c>
-      <c r="B7" s="3" t="n">
+      <c r="B7" s="6" t="n">
         <v>46034</v>
       </c>
       <c r="C7" s="2" t="inlineStr">
@@ -857,7 +869,7 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>ec</t>
+          <t>EC</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
@@ -900,6 +912,7 @@
           <t>有効</t>
         </is>
       </c>
+      <c r="O7" s="2" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
@@ -907,7 +920,7 @@
           <t>A-20260007</t>
         </is>
       </c>
-      <c r="B8" s="3" t="n">
+      <c r="B8" s="6" t="n">
         <v>46028</v>
       </c>
       <c r="C8" s="2" t="inlineStr">
@@ -927,12 +940,12 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>メンバー</t>
+          <t>会員</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>抽出器具</t>
+          <t>器具</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
@@ -960,6 +973,7 @@
           <t>有効</t>
         </is>
       </c>
+      <c r="O8" s="2" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
@@ -967,10 +981,8 @@
           <t>A-20260008</t>
         </is>
       </c>
-      <c r="B9" s="2" t="inlineStr">
-        <is>
-          <t>1月13日</t>
-        </is>
+      <c r="B9" s="6" t="n">
+        <v>46035</v>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
@@ -1022,6 +1034,7 @@
           <t>有効</t>
         </is>
       </c>
+      <c r="O9" s="2" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
@@ -1029,12 +1042,12 @@
           <t>A-20260009</t>
         </is>
       </c>
-      <c r="B10" s="3" t="n">
+      <c r="B10" s="6" t="n">
         <v>46045</v>
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>しんじゅく店</t>
+          <t>新宿店</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
@@ -1082,6 +1095,7 @@
           <t>有効</t>
         </is>
       </c>
+      <c r="O10" s="2" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
@@ -1089,7 +1103,7 @@
           <t>A-20260010</t>
         </is>
       </c>
-      <c r="B11" s="3" t="n">
+      <c r="B11" s="6" t="n">
         <v>46051</v>
       </c>
       <c r="C11" s="2" t="inlineStr">
@@ -1109,7 +1123,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>一般客</t>
+          <t>一般</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1142,6 +1156,7 @@
           <t>有効</t>
         </is>
       </c>
+      <c r="O11" s="2" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
@@ -1149,14 +1164,12 @@
           <t>A-20260011</t>
         </is>
       </c>
-      <c r="B12" s="2" t="inlineStr">
-        <is>
-          <t>2026/1/12</t>
-        </is>
+      <c r="B12" s="6" t="n">
+        <v>46034</v>
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>シブヤ店</t>
+          <t>渋谷店</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
@@ -1204,6 +1217,7 @@
           <t>有効</t>
         </is>
       </c>
+      <c r="O12" s="2" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
@@ -1211,8 +1225,8 @@
           <t>A-20260012</t>
         </is>
       </c>
-      <c r="B13" s="2" t="n">
-        <v>20260113</v>
+      <c r="B13" s="6" t="n">
+        <v>46035</v>
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
@@ -1231,7 +1245,7 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>一般客</t>
+          <t>一般</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1264,6 +1278,7 @@
           <t>有効</t>
         </is>
       </c>
+      <c r="O13" s="2" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
@@ -1271,17 +1286,17 @@
           <t>A-20260013</t>
         </is>
       </c>
-      <c r="B14" s="3" t="n">
+      <c r="B14" s="6" t="n">
         <v>46048</v>
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>しんじゅく店</t>
+          <t>新宿店</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>Ｅ Ｃ</t>
+          <t>EC</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
@@ -1324,6 +1339,7 @@
           <t>有効</t>
         </is>
       </c>
+      <c r="O14" s="2" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
@@ -1331,7 +1347,7 @@
           <t>A-20260014</t>
         </is>
       </c>
-      <c r="B15" s="3" t="n">
+      <c r="B15" s="6" t="n">
         <v>46050</v>
       </c>
       <c r="C15" s="2" t="inlineStr">
@@ -1351,7 +1367,7 @@
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>一般客</t>
+          <t>一般</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -1384,6 +1400,7 @@
           <t>有効</t>
         </is>
       </c>
+      <c r="O15" s="2" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
@@ -1391,7 +1408,7 @@
           <t>A-20260015</t>
         </is>
       </c>
-      <c r="B16" s="3" t="n">
+      <c r="B16" s="6" t="n">
         <v>46034</v>
       </c>
       <c r="C16" s="2" t="inlineStr">
@@ -1401,7 +1418,7 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>オフライン</t>
+          <t>店頭</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
@@ -1440,6 +1457,7 @@
           <t>有効</t>
         </is>
       </c>
+      <c r="O16" s="2" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
@@ -1447,10 +1465,8 @@
           <t>A-20260016</t>
         </is>
       </c>
-      <c r="B17" s="2" t="inlineStr">
-        <is>
-          <t>2026-01-02</t>
-        </is>
+      <c r="B17" s="6" t="n">
+        <v>46024</v>
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
@@ -1498,6 +1514,7 @@
           <t>有効</t>
         </is>
       </c>
+      <c r="O17" s="2" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
@@ -1505,7 +1522,7 @@
           <t>A-20260017</t>
         </is>
       </c>
-      <c r="B18" s="3" t="n">
+      <c r="B18" s="6" t="n">
         <v>46033</v>
       </c>
       <c r="C18" s="2" t="inlineStr">
@@ -1530,7 +1547,7 @@
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>コーヒー</t>
+          <t>コーヒー豆</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
@@ -1558,6 +1575,7 @@
           <t>有効</t>
         </is>
       </c>
+      <c r="O18" s="2" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
@@ -1565,17 +1583,17 @@
           <t>A-20260018</t>
         </is>
       </c>
-      <c r="B19" s="3" t="n">
+      <c r="B19" s="6" t="n">
         <v>46024</v>
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>しんじゅく店</t>
+          <t>新宿店</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>オフライン</t>
+          <t>店頭</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
@@ -1590,7 +1608,7 @@
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>お菓子</t>
+          <t>菓子</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
@@ -1601,10 +1619,8 @@
       <c r="I19" s="2" t="n">
         <v>20</v>
       </c>
-      <c r="J19" s="2" t="inlineStr">
-        <is>
-          <t>880円</t>
-        </is>
+      <c r="J19" s="2" t="n">
+        <v>880</v>
       </c>
       <c r="K19" s="2" t="n">
         <v>0</v>
@@ -1620,6 +1636,7 @@
           <t>有効</t>
         </is>
       </c>
+      <c r="O19" s="2" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
@@ -1627,12 +1644,12 @@
           <t>A-20260019</t>
         </is>
       </c>
-      <c r="B20" s="3" t="n">
+      <c r="B20" s="6" t="n">
         <v>46040</v>
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>シブヤ店</t>
+          <t>渋谷店</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
@@ -1680,6 +1697,7 @@
           <t>有効</t>
         </is>
       </c>
+      <c r="O20" s="2" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
@@ -1687,10 +1705,8 @@
           <t>A-20260020</t>
         </is>
       </c>
-      <c r="B21" s="2" t="inlineStr">
-        <is>
-          <t>1月2日</t>
-        </is>
+      <c r="B21" s="6" t="n">
+        <v>46024</v>
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
@@ -1714,7 +1730,7 @@
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>抽出器具</t>
+          <t>器具</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
@@ -1729,7 +1745,7 @@
         <v>3200</v>
       </c>
       <c r="K21" s="2" t="n">
-        <v>5</v>
+        <v>0.05</v>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
@@ -1742,6 +1758,7 @@
           <t>有効</t>
         </is>
       </c>
+      <c r="O21" s="2" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
@@ -1749,12 +1766,12 @@
           <t>A-20260021</t>
         </is>
       </c>
-      <c r="B22" s="3" t="n">
+      <c r="B22" s="6" t="n">
         <v>46042</v>
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>渋谷　店</t>
+          <t>渋谷店</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
@@ -1769,7 +1786,7 @@
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>メンバー</t>
+          <t>会員</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -1802,6 +1819,7 @@
           <t>有効</t>
         </is>
       </c>
+      <c r="O22" s="2" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
@@ -1809,17 +1827,17 @@
           <t>A-20260022</t>
         </is>
       </c>
-      <c r="B23" s="3" t="n">
+      <c r="B23" s="6" t="n">
         <v>46031</v>
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>渋谷　店</t>
+          <t>渋谷店</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>オンライン</t>
+          <t>EC</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
@@ -1862,6 +1880,7 @@
           <t>有効</t>
         </is>
       </c>
+      <c r="O23" s="2" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
@@ -1869,14 +1888,12 @@
           <t>A-20260023</t>
         </is>
       </c>
-      <c r="B24" s="2" t="inlineStr">
-        <is>
-          <t>2026/1/16</t>
-        </is>
+      <c r="B24" s="6" t="n">
+        <v>46038</v>
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>新宿 店</t>
+          <t>新宿店</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
@@ -1920,6 +1937,7 @@
           <t>有効</t>
         </is>
       </c>
+      <c r="O24" s="2" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
@@ -1927,12 +1945,12 @@
           <t>A-20260024</t>
         </is>
       </c>
-      <c r="B25" s="2" t="n">
-        <v>20260130</v>
+      <c r="B25" s="6" t="n">
+        <v>46052</v>
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">横浜店 </t>
+          <t>横浜店</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
@@ -1952,7 +1970,7 @@
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>ギフト商品</t>
+          <t>ギフト</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
@@ -1960,18 +1978,14 @@
           <t>ギフトセットA</t>
         </is>
       </c>
-      <c r="I25" s="2" t="inlineStr">
-        <is>
-          <t>１</t>
-        </is>
+      <c r="I25" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="J25" s="2" t="n">
         <v>3800</v>
       </c>
-      <c r="K25" s="2" t="inlineStr">
-        <is>
-          <t>10%</t>
-        </is>
+      <c r="K25" s="2" t="n">
+        <v>0.1</v>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
@@ -1984,6 +1998,7 @@
           <t>有効</t>
         </is>
       </c>
+      <c r="O25" s="2" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
@@ -1991,12 +2006,12 @@
           <t>A-20260025</t>
         </is>
       </c>
-      <c r="B26" s="3" t="n">
+      <c r="B26" s="6" t="n">
         <v>46032</v>
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>シブヤ店</t>
+          <t>渋谷店</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
@@ -2011,7 +2026,7 @@
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>メンバー</t>
+          <t>会員</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -2044,6 +2059,7 @@
           <t>有効</t>
         </is>
       </c>
+      <c r="O26" s="2" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
@@ -2051,7 +2067,7 @@
           <t>A-20260026</t>
         </is>
       </c>
-      <c r="B27" s="3" t="n">
+      <c r="B27" s="6" t="n">
         <v>46042</v>
       </c>
       <c r="C27" s="2" t="inlineStr">
@@ -2071,7 +2087,7 @@
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>一般客</t>
+          <t>一般</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -2104,6 +2120,7 @@
           <t>有効</t>
         </is>
       </c>
+      <c r="O27" s="2" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
@@ -2111,7 +2128,7 @@
           <t>A-20260027</t>
         </is>
       </c>
-      <c r="B28" s="3" t="n">
+      <c r="B28" s="6" t="n">
         <v>46041</v>
       </c>
       <c r="C28" s="2" t="inlineStr">
@@ -2164,6 +2181,7 @@
           <t>有効</t>
         </is>
       </c>
+      <c r="O28" s="2" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
@@ -2171,10 +2189,8 @@
           <t>A-20260028</t>
         </is>
       </c>
-      <c r="B29" s="2" t="inlineStr">
-        <is>
-          <t>2026-01-31</t>
-        </is>
+      <c r="B29" s="6" t="n">
+        <v>46053</v>
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
@@ -2183,7 +2199,7 @@
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>店舗</t>
+          <t>店頭</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
@@ -2198,7 +2214,7 @@
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>抽出器具</t>
+          <t>器具</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
@@ -2226,6 +2242,7 @@
           <t>有効</t>
         </is>
       </c>
+      <c r="O29" s="2" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
@@ -2233,7 +2250,7 @@
           <t>A-20260029</t>
         </is>
       </c>
-      <c r="B30" s="3" t="n">
+      <c r="B30" s="6" t="n">
         <v>46035</v>
       </c>
       <c r="C30" s="2" t="inlineStr">
@@ -2286,6 +2303,7 @@
           <t>有効</t>
         </is>
       </c>
+      <c r="O30" s="2" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
@@ -2293,17 +2311,17 @@
           <t>A-20260030</t>
         </is>
       </c>
-      <c r="B31" s="3" t="n">
+      <c r="B31" s="6" t="n">
         <v>46036</v>
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>名古屋 店</t>
+          <t>名古屋店</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>Web</t>
+          <t>EC</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
@@ -2313,7 +2331,7 @@
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>メンバー</t>
+          <t>会員</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -2329,10 +2347,8 @@
       <c r="I31" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="J31" s="2" t="inlineStr">
-        <is>
-          <t>¥2,800</t>
-        </is>
+      <c r="J31" s="2" t="n">
+        <v>2800</v>
       </c>
       <c r="K31" s="2" t="n">
         <v>0</v>
@@ -2348,6 +2364,7 @@
           <t>有効</t>
         </is>
       </c>
+      <c r="O31" s="2" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
@@ -2355,7 +2372,7 @@
           <t>A-20260031</t>
         </is>
       </c>
-      <c r="B32" s="3" t="n">
+      <c r="B32" s="6" t="n">
         <v>46046</v>
       </c>
       <c r="C32" s="2" t="inlineStr">
@@ -2380,7 +2397,7 @@
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>抽出器具</t>
+          <t>器具</t>
         </is>
       </c>
       <c r="H32" s="2" t="inlineStr">
@@ -2408,6 +2425,7 @@
           <t>有効</t>
         </is>
       </c>
+      <c r="O32" s="2" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
@@ -2415,10 +2433,8 @@
           <t>A-20260032</t>
         </is>
       </c>
-      <c r="B33" s="2" t="inlineStr">
-        <is>
-          <t>1月13日</t>
-        </is>
+      <c r="B33" s="6" t="n">
+        <v>46035</v>
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
@@ -2437,7 +2453,7 @@
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>メンバー</t>
+          <t>会員</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -2450,10 +2466,8 @@
           <t>コーヒーゼリー 4個</t>
         </is>
       </c>
-      <c r="I33" s="2" t="inlineStr">
-        <is>
-          <t>4個</t>
-        </is>
+      <c r="I33" s="2" t="n">
+        <v>4</v>
       </c>
       <c r="J33" s="2" t="n">
         <v>980</v>
@@ -2472,6 +2486,7 @@
           <t>有効</t>
         </is>
       </c>
+      <c r="O33" s="2" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
@@ -2479,7 +2494,7 @@
           <t>A-20260033</t>
         </is>
       </c>
-      <c r="B34" s="3" t="n">
+      <c r="B34" s="6" t="n">
         <v>46046</v>
       </c>
       <c r="C34" s="2" t="inlineStr">
@@ -2489,7 +2504,7 @@
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>オフライン</t>
+          <t>店頭</t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr">
@@ -2532,6 +2547,7 @@
           <t>有効</t>
         </is>
       </c>
+      <c r="O34" s="2" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
@@ -2539,12 +2555,12 @@
           <t>A-20260034</t>
         </is>
       </c>
-      <c r="B35" s="3" t="n">
+      <c r="B35" s="6" t="n">
         <v>46048</v>
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>渋谷　店</t>
+          <t>渋谷店</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
@@ -2564,7 +2580,7 @@
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>珈琲豆</t>
+          <t>コーヒー豆</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
@@ -2578,10 +2594,8 @@
       <c r="J35" s="2" t="n">
         <v>2600</v>
       </c>
-      <c r="K35" s="2" t="inlineStr">
-        <is>
-          <t>10%</t>
-        </is>
+      <c r="K35" s="2" t="n">
+        <v>0.1</v>
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
@@ -2594,6 +2608,7 @@
           <t>有効</t>
         </is>
       </c>
+      <c r="O35" s="2" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
@@ -2601,10 +2616,8 @@
           <t>A-20260035</t>
         </is>
       </c>
-      <c r="B36" s="2" t="inlineStr">
-        <is>
-          <t>2026/1/12</t>
-        </is>
+      <c r="B36" s="6" t="n">
+        <v>46034</v>
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
@@ -2613,7 +2626,7 @@
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>オフライン</t>
+          <t>店頭</t>
         </is>
       </c>
       <c r="E36" s="2" t="inlineStr">
@@ -2623,7 +2636,7 @@
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>メンバー</t>
+          <t>会員</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -2639,10 +2652,8 @@
       <c r="I36" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="J36" s="2" t="inlineStr">
-        <is>
-          <t>3,200円</t>
-        </is>
+      <c r="J36" s="2" t="n">
+        <v>3200</v>
       </c>
       <c r="K36" s="2" t="n">
         <v>0.05</v>
@@ -2658,6 +2669,7 @@
           <t>有効</t>
         </is>
       </c>
+      <c r="O36" s="2" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
@@ -2665,17 +2677,17 @@
           <t>A-20260036</t>
         </is>
       </c>
-      <c r="B37" s="2" t="n">
-        <v>20260125</v>
+      <c r="B37" s="6" t="n">
+        <v>46047</v>
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>渋谷　店</t>
+          <t>渋谷店</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>オフライン</t>
+          <t>店頭</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
@@ -2685,7 +2697,7 @@
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>一般客</t>
+          <t>一般</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -2718,6 +2730,7 @@
           <t>有効</t>
         </is>
       </c>
+      <c r="O37" s="2" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
@@ -2725,7 +2738,7 @@
           <t>A-20260037</t>
         </is>
       </c>
-      <c r="B38" s="3" t="n">
+      <c r="B38" s="6" t="n">
         <v>46036</v>
       </c>
       <c r="C38" s="2" t="inlineStr">
@@ -2735,7 +2748,7 @@
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>ec</t>
+          <t>EC</t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr">
@@ -2750,7 +2763,7 @@
       </c>
       <c r="G38" s="2" t="inlineStr">
         <is>
-          <t>ギフト商品</t>
+          <t>ギフト</t>
         </is>
       </c>
       <c r="H38" s="2" t="inlineStr">
@@ -2778,6 +2791,7 @@
           <t>有効</t>
         </is>
       </c>
+      <c r="O38" s="2" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
@@ -2785,7 +2799,7 @@
           <t>A-20260038</t>
         </is>
       </c>
-      <c r="B39" s="3" t="n">
+      <c r="B39" s="6" t="n">
         <v>46025</v>
       </c>
       <c r="C39" s="2" t="inlineStr">
@@ -2842,6 +2856,7 @@
           <t>無効</t>
         </is>
       </c>
+      <c r="O39" s="2" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
@@ -2849,17 +2864,17 @@
           <t>A-20260039</t>
         </is>
       </c>
-      <c r="B40" s="3" t="n">
+      <c r="B40" s="6" t="n">
         <v>46032</v>
       </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">渋谷店 </t>
+          <t>渋谷店</t>
         </is>
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
-          <t>オフライン</t>
+          <t>店頭</t>
         </is>
       </c>
       <c r="E40" s="2" t="inlineStr">
@@ -2869,7 +2884,7 @@
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>メンバー</t>
+          <t>会員</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
@@ -2902,6 +2917,7 @@
           <t>有効</t>
         </is>
       </c>
+      <c r="O40" s="2" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
@@ -2909,10 +2925,8 @@
           <t>A-20260040</t>
         </is>
       </c>
-      <c r="B41" s="2" t="inlineStr">
-        <is>
-          <t>2026-01-19</t>
-        </is>
+      <c r="B41" s="6" t="n">
+        <v>46041</v>
       </c>
       <c r="C41" s="2" t="inlineStr">
         <is>
@@ -2921,7 +2935,7 @@
       </c>
       <c r="D41" s="2" t="inlineStr">
         <is>
-          <t>店舗</t>
+          <t>店頭</t>
         </is>
       </c>
       <c r="E41" s="2" t="inlineStr">
@@ -2964,6 +2978,7 @@
           <t>有効</t>
         </is>
       </c>
+      <c r="O41" s="2" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
@@ -2971,12 +2986,12 @@
           <t>A-20260041</t>
         </is>
       </c>
-      <c r="B42" s="3" t="n">
+      <c r="B42" s="6" t="n">
         <v>46041</v>
       </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
-          <t>渋谷　店</t>
+          <t>渋谷店</t>
         </is>
       </c>
       <c r="D42" s="2" t="inlineStr">
@@ -3024,6 +3039,7 @@
           <t>有効</t>
         </is>
       </c>
+      <c r="O42" s="2" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
@@ -3031,7 +3047,7 @@
           <t>A-20260042</t>
         </is>
       </c>
-      <c r="B43" s="3" t="n">
+      <c r="B43" s="6" t="n">
         <v>46053</v>
       </c>
       <c r="C43" s="2" t="inlineStr">
@@ -3051,12 +3067,12 @@
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>一般客</t>
+          <t>一般</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
         <is>
-          <t>珈琲豆</t>
+          <t>コーヒー豆</t>
         </is>
       </c>
       <c r="H43" s="2" t="inlineStr">
@@ -3067,7 +3083,9 @@
       <c r="I43" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="J43" s="2" t="n"/>
+      <c r="J43" s="7" t="n">
+        <v>1400</v>
+      </c>
       <c r="K43" s="2" t="n">
         <v>0.1</v>
       </c>
@@ -3082,6 +3100,11 @@
           <t>有効</t>
         </is>
       </c>
+      <c r="O43" s="2" t="inlineStr">
+        <is>
+          <t>補完</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
@@ -3089,17 +3112,17 @@
           <t>A-20260043</t>
         </is>
       </c>
-      <c r="B44" s="3" t="n">
+      <c r="B44" s="6" t="n">
         <v>46035</v>
       </c>
       <c r="C44" s="2" t="inlineStr">
         <is>
-          <t>しんじゅく店</t>
+          <t>新宿店</t>
         </is>
       </c>
       <c r="D44" s="2" t="inlineStr">
         <is>
-          <t>オフライン</t>
+          <t>店頭</t>
         </is>
       </c>
       <c r="E44" s="2" t="inlineStr">
@@ -3114,7 +3137,7 @@
       </c>
       <c r="G44" s="2" t="inlineStr">
         <is>
-          <t>珈琲豆</t>
+          <t>コーヒー豆</t>
         </is>
       </c>
       <c r="H44" s="2" t="inlineStr">
@@ -3142,6 +3165,7 @@
           <t>有効</t>
         </is>
       </c>
+      <c r="O44" s="2" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
@@ -3149,10 +3173,8 @@
           <t>A-20260044</t>
         </is>
       </c>
-      <c r="B45" s="2" t="inlineStr">
-        <is>
-          <t>1月26日</t>
-        </is>
+      <c r="B45" s="6" t="n">
+        <v>46048</v>
       </c>
       <c r="C45" s="2" t="inlineStr">
         <is>
@@ -3171,7 +3193,7 @@
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
-          <t>メンバー</t>
+          <t>会員</t>
         </is>
       </c>
       <c r="G45" s="2" t="inlineStr">
@@ -3204,6 +3226,7 @@
           <t>有効</t>
         </is>
       </c>
+      <c r="O45" s="2" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
@@ -3211,7 +3234,7 @@
           <t>A-20260045</t>
         </is>
       </c>
-      <c r="B46" s="3" t="n">
+      <c r="B46" s="6" t="n">
         <v>46052</v>
       </c>
       <c r="C46" s="2" t="inlineStr">
@@ -3264,6 +3287,7 @@
           <t>有効</t>
         </is>
       </c>
+      <c r="O46" s="2" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
@@ -3271,7 +3295,7 @@
           <t>A-20260046</t>
         </is>
       </c>
-      <c r="B47" s="3" t="n">
+      <c r="B47" s="6" t="n">
         <v>46029</v>
       </c>
       <c r="C47" s="2" t="inlineStr">
@@ -3281,7 +3305,7 @@
       </c>
       <c r="D47" s="2" t="inlineStr">
         <is>
-          <t>店舗</t>
+          <t>店頭</t>
         </is>
       </c>
       <c r="E47" s="2" t="inlineStr">
@@ -3296,7 +3320,7 @@
       </c>
       <c r="G47" s="2" t="inlineStr">
         <is>
-          <t>珈琲豆</t>
+          <t>コーヒー豆</t>
         </is>
       </c>
       <c r="H47" s="2" t="inlineStr">
@@ -3324,6 +3348,7 @@
           <t>有効</t>
         </is>
       </c>
+      <c r="O47" s="2" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
@@ -3331,10 +3356,8 @@
           <t>A-20260047</t>
         </is>
       </c>
-      <c r="B48" s="2" t="inlineStr">
-        <is>
-          <t>2026/1/30</t>
-        </is>
+      <c r="B48" s="6" t="n">
+        <v>46052</v>
       </c>
       <c r="C48" s="2" t="inlineStr">
         <is>
@@ -3343,7 +3366,7 @@
       </c>
       <c r="D48" s="2" t="inlineStr">
         <is>
-          <t>ec</t>
+          <t>EC</t>
         </is>
       </c>
       <c r="E48" s="2" t="inlineStr">
@@ -3358,7 +3381,7 @@
       </c>
       <c r="G48" s="2" t="inlineStr">
         <is>
-          <t>抽出器具</t>
+          <t>器具</t>
         </is>
       </c>
       <c r="H48" s="2" t="inlineStr">
@@ -3366,10 +3389,8 @@
           <t>サーバー 600ml</t>
         </is>
       </c>
-      <c r="I48" s="2" t="inlineStr">
-        <is>
-          <t>１</t>
-        </is>
+      <c r="I48" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="J48" s="2" t="n">
         <v>3200</v>
@@ -3388,6 +3409,7 @@
           <t>有効</t>
         </is>
       </c>
+      <c r="O48" s="2" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
@@ -3395,17 +3417,17 @@
           <t>A-20260048</t>
         </is>
       </c>
-      <c r="B49" s="2" t="n">
-        <v>20260114</v>
+      <c r="B49" s="6" t="n">
+        <v>46036</v>
       </c>
       <c r="C49" s="2" t="inlineStr">
         <is>
-          <t>シブヤ店</t>
+          <t>渋谷店</t>
         </is>
       </c>
       <c r="D49" s="2" t="inlineStr">
         <is>
-          <t>オンライン</t>
+          <t>EC</t>
         </is>
       </c>
       <c r="E49" s="2" t="inlineStr">
@@ -3448,6 +3470,7 @@
           <t>有効</t>
         </is>
       </c>
+      <c r="O49" s="2" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
@@ -3455,7 +3478,7 @@
           <t>A-20260049</t>
         </is>
       </c>
-      <c r="B50" s="3" t="n">
+      <c r="B50" s="6" t="n">
         <v>46033</v>
       </c>
       <c r="C50" s="2" t="inlineStr">
@@ -3508,6 +3531,7 @@
           <t>有効</t>
         </is>
       </c>
+      <c r="O50" s="2" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
@@ -3515,7 +3539,7 @@
           <t>A-20260050</t>
         </is>
       </c>
-      <c r="B51" s="3" t="n">
+      <c r="B51" s="6" t="n">
         <v>46024</v>
       </c>
       <c r="C51" s="2" t="inlineStr">
@@ -3525,7 +3549,7 @@
       </c>
       <c r="D51" s="2" t="inlineStr">
         <is>
-          <t>オンライン</t>
+          <t>EC</t>
         </is>
       </c>
       <c r="E51" s="2" t="inlineStr">
@@ -3535,12 +3559,12 @@
       </c>
       <c r="F51" s="2" t="inlineStr">
         <is>
-          <t>一般客</t>
+          <t>一般</t>
         </is>
       </c>
       <c r="G51" s="2" t="inlineStr">
         <is>
-          <t>ギフト商品</t>
+          <t>ギフト</t>
         </is>
       </c>
       <c r="H51" s="2" t="inlineStr">
@@ -3568,6 +3592,7 @@
           <t>有効</t>
         </is>
       </c>
+      <c r="O51" s="2" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
@@ -3575,12 +3600,12 @@
           <t>A-20260051</t>
         </is>
       </c>
-      <c r="B52" s="3" t="n">
+      <c r="B52" s="6" t="n">
         <v>46034</v>
       </c>
       <c r="C52" s="2" t="inlineStr">
         <is>
-          <t>ヨコハマ店</t>
+          <t>横浜店</t>
         </is>
       </c>
       <c r="D52" s="2" t="inlineStr">
@@ -3628,6 +3653,7 @@
           <t>有効</t>
         </is>
       </c>
+      <c r="O52" s="2" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
@@ -3635,10 +3661,8 @@
           <t>A-20260052</t>
         </is>
       </c>
-      <c r="B53" s="2" t="inlineStr">
-        <is>
-          <t>2026-01-26</t>
-        </is>
+      <c r="B53" s="6" t="n">
+        <v>46048</v>
       </c>
       <c r="C53" s="2" t="inlineStr">
         <is>
@@ -3673,10 +3697,8 @@
       <c r="I53" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="J53" s="2" t="inlineStr">
-        <is>
-          <t>1,600円</t>
-        </is>
+      <c r="J53" s="2" t="n">
+        <v>1600</v>
       </c>
       <c r="K53" s="2" t="n">
         <v>0</v>
@@ -3692,6 +3714,7 @@
           <t>有効</t>
         </is>
       </c>
+      <c r="O53" s="2" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
@@ -3699,7 +3722,7 @@
           <t>A-20260053</t>
         </is>
       </c>
-      <c r="B54" s="3" t="n">
+      <c r="B54" s="6" t="n">
         <v>46052</v>
       </c>
       <c r="C54" s="2" t="inlineStr">
@@ -3752,6 +3775,7 @@
           <t>有効</t>
         </is>
       </c>
+      <c r="O54" s="2" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
@@ -3759,7 +3783,7 @@
           <t>A-20260054</t>
         </is>
       </c>
-      <c r="B55" s="3" t="n">
+      <c r="B55" s="6" t="n">
         <v>46052</v>
       </c>
       <c r="C55" s="2" t="inlineStr">
@@ -3779,7 +3803,7 @@
       </c>
       <c r="F55" s="2" t="inlineStr">
         <is>
-          <t>一般客</t>
+          <t>一般</t>
         </is>
       </c>
       <c r="G55" s="2" t="inlineStr">
@@ -3816,6 +3840,7 @@
           <t>無効</t>
         </is>
       </c>
+      <c r="O55" s="2" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
@@ -3823,17 +3848,17 @@
           <t>A-20260055</t>
         </is>
       </c>
-      <c r="B56" s="3" t="n">
+      <c r="B56" s="6" t="n">
         <v>46047</v>
       </c>
       <c r="C56" s="2" t="inlineStr">
         <is>
-          <t>ヨコハマ店</t>
+          <t>横浜店</t>
         </is>
       </c>
       <c r="D56" s="2" t="inlineStr">
         <is>
-          <t>Ｅ Ｃ</t>
+          <t>EC</t>
         </is>
       </c>
       <c r="E56" s="2" t="inlineStr">
@@ -3872,6 +3897,7 @@
           <t>有効</t>
         </is>
       </c>
+      <c r="O56" s="2" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
@@ -3879,10 +3905,8 @@
           <t>A-20260056</t>
         </is>
       </c>
-      <c r="B57" s="2" t="inlineStr">
-        <is>
-          <t>1月7日</t>
-        </is>
+      <c r="B57" s="6" t="n">
+        <v>46029</v>
       </c>
       <c r="C57" s="2" t="inlineStr">
         <is>
@@ -3934,6 +3958,7 @@
           <t>有効</t>
         </is>
       </c>
+      <c r="O57" s="2" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
@@ -3941,7 +3966,7 @@
           <t>A-20260057</t>
         </is>
       </c>
-      <c r="B58" s="3" t="n">
+      <c r="B58" s="6" t="n">
         <v>46053</v>
       </c>
       <c r="C58" s="2" t="inlineStr">
@@ -3951,7 +3976,7 @@
       </c>
       <c r="D58" s="2" t="inlineStr">
         <is>
-          <t>ec</t>
+          <t>EC</t>
         </is>
       </c>
       <c r="E58" s="2" t="inlineStr">
@@ -3994,6 +4019,7 @@
           <t>有効</t>
         </is>
       </c>
+      <c r="O58" s="2" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
@@ -4001,17 +4027,17 @@
           <t>A-20260058</t>
         </is>
       </c>
-      <c r="B59" s="3" t="n">
+      <c r="B59" s="6" t="n">
         <v>46053</v>
       </c>
       <c r="C59" s="2" t="inlineStr">
         <is>
-          <t>しんじゅく店</t>
+          <t>新宿店</t>
         </is>
       </c>
       <c r="D59" s="2" t="inlineStr">
         <is>
-          <t>店舗</t>
+          <t>店頭</t>
         </is>
       </c>
       <c r="E59" s="2" t="inlineStr">
@@ -4026,7 +4052,7 @@
       </c>
       <c r="G59" s="2" t="inlineStr">
         <is>
-          <t>珈琲豆</t>
+          <t>コーヒー豆</t>
         </is>
       </c>
       <c r="H59" s="2" t="inlineStr">
@@ -4054,6 +4080,7 @@
           <t>有効</t>
         </is>
       </c>
+      <c r="O59" s="2" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
@@ -4061,10 +4088,8 @@
           <t>A-20260059</t>
         </is>
       </c>
-      <c r="B60" s="2" t="inlineStr">
-        <is>
-          <t>2026/1/8</t>
-        </is>
+      <c r="B60" s="6" t="n">
+        <v>46030</v>
       </c>
       <c r="C60" s="2" t="inlineStr">
         <is>
@@ -4073,7 +4098,7 @@
       </c>
       <c r="D60" s="2" t="inlineStr">
         <is>
-          <t>店舗</t>
+          <t>店頭</t>
         </is>
       </c>
       <c r="E60" s="2" t="inlineStr">
@@ -4095,10 +4120,8 @@
       <c r="I60" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="J60" s="2" t="inlineStr">
-        <is>
-          <t>¥1,500</t>
-        </is>
+      <c r="J60" s="2" t="n">
+        <v>1500</v>
       </c>
       <c r="K60" s="2" t="n">
         <v>0.05</v>
@@ -4114,6 +4137,7 @@
           <t>有効</t>
         </is>
       </c>
+      <c r="O60" s="2" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
@@ -4121,8 +4145,8 @@
           <t>A-20260060</t>
         </is>
       </c>
-      <c r="B61" s="2" t="n">
-        <v>20260107</v>
+      <c r="B61" s="6" t="n">
+        <v>46029</v>
       </c>
       <c r="C61" s="2" t="inlineStr">
         <is>
@@ -4174,6 +4198,7 @@
           <t>有効</t>
         </is>
       </c>
+      <c r="O61" s="2" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
@@ -4181,7 +4206,7 @@
           <t>A-20260061</t>
         </is>
       </c>
-      <c r="B62" s="3" t="n">
+      <c r="B62" s="6" t="n">
         <v>46025</v>
       </c>
       <c r="C62" s="2" t="inlineStr">
@@ -4206,7 +4231,7 @@
       </c>
       <c r="G62" s="2" t="inlineStr">
         <is>
-          <t>抽出器具</t>
+          <t>器具</t>
         </is>
       </c>
       <c r="H62" s="2" t="inlineStr">
@@ -4234,6 +4259,7 @@
           <t>有効</t>
         </is>
       </c>
+      <c r="O62" s="2" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
@@ -4241,12 +4267,12 @@
           <t>A-20260062</t>
         </is>
       </c>
-      <c r="B63" s="3" t="n">
+      <c r="B63" s="6" t="n">
         <v>46029</v>
       </c>
       <c r="C63" s="2" t="inlineStr">
         <is>
-          <t>名古屋 店</t>
+          <t>名古屋店</t>
         </is>
       </c>
       <c r="D63" s="2" t="inlineStr">
@@ -4298,6 +4324,7 @@
           <t>有効</t>
         </is>
       </c>
+      <c r="O63" s="2" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
@@ -4305,7 +4332,7 @@
           <t>A-20260063</t>
         </is>
       </c>
-      <c r="B64" s="3" t="n">
+      <c r="B64" s="6" t="n">
         <v>46036</v>
       </c>
       <c r="C64" s="2" t="inlineStr">
@@ -4315,7 +4342,7 @@
       </c>
       <c r="D64" s="2" t="inlineStr">
         <is>
-          <t>店舗</t>
+          <t>店頭</t>
         </is>
       </c>
       <c r="E64" s="2" t="inlineStr">
@@ -4338,10 +4365,8 @@
           <t>モカ 200g</t>
         </is>
       </c>
-      <c r="I64" s="2" t="inlineStr">
-        <is>
-          <t>12個</t>
-        </is>
+      <c r="I64" s="2" t="n">
+        <v>12</v>
       </c>
       <c r="J64" s="2" t="n">
         <v>1400</v>
@@ -4360,6 +4385,7 @@
           <t>有効</t>
         </is>
       </c>
+      <c r="O64" s="2" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
@@ -4367,10 +4393,8 @@
           <t>A-20260064</t>
         </is>
       </c>
-      <c r="B65" s="2" t="inlineStr">
-        <is>
-          <t>2026-01-02</t>
-        </is>
+      <c r="B65" s="6" t="n">
+        <v>46024</v>
       </c>
       <c r="C65" s="2" t="inlineStr">
         <is>
@@ -4422,6 +4446,7 @@
           <t>有効</t>
         </is>
       </c>
+      <c r="O65" s="2" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
@@ -4429,7 +4454,7 @@
           <t>A-20260065</t>
         </is>
       </c>
-      <c r="B66" s="3" t="n">
+      <c r="B66" s="6" t="n">
         <v>46036</v>
       </c>
       <c r="C66" s="2" t="inlineStr">
@@ -4449,7 +4474,7 @@
       </c>
       <c r="F66" s="2" t="inlineStr">
         <is>
-          <t>メンバー</t>
+          <t>会員</t>
         </is>
       </c>
       <c r="G66" s="2" t="inlineStr">
@@ -4482,6 +4507,7 @@
           <t>有効</t>
         </is>
       </c>
+      <c r="O66" s="2" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
@@ -4489,12 +4515,12 @@
           <t>A-20260066</t>
         </is>
       </c>
-      <c r="B67" s="3" t="n">
+      <c r="B67" s="6" t="n">
         <v>46046</v>
       </c>
       <c r="C67" s="2" t="inlineStr">
         <is>
-          <t>名古屋 店</t>
+          <t>名古屋店</t>
         </is>
       </c>
       <c r="D67" s="2" t="inlineStr">
@@ -4510,7 +4536,7 @@
       <c r="F67" s="2" t="n"/>
       <c r="G67" s="2" t="inlineStr">
         <is>
-          <t>珈琲豆</t>
+          <t>コーヒー豆</t>
         </is>
       </c>
       <c r="H67" s="2" t="inlineStr">
@@ -4538,6 +4564,7 @@
           <t>有効</t>
         </is>
       </c>
+      <c r="O67" s="2" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
@@ -4545,12 +4572,12 @@
           <t>A-20260067</t>
         </is>
       </c>
-      <c r="B68" s="3" t="n">
+      <c r="B68" s="6" t="n">
         <v>46041</v>
       </c>
       <c r="C68" s="2" t="inlineStr">
         <is>
-          <t>しんじゅく店</t>
+          <t>新宿店</t>
         </is>
       </c>
       <c r="D68" s="2" t="inlineStr">
@@ -4570,7 +4597,7 @@
       </c>
       <c r="G68" s="2" t="inlineStr">
         <is>
-          <t>抽出器具</t>
+          <t>器具</t>
         </is>
       </c>
       <c r="H68" s="2" t="inlineStr">
@@ -4598,6 +4625,7 @@
           <t>有効</t>
         </is>
       </c>
+      <c r="O68" s="2" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
@@ -4605,19 +4633,17 @@
           <t>A-20260068</t>
         </is>
       </c>
-      <c r="B69" s="2" t="inlineStr">
-        <is>
-          <t>1月27日</t>
-        </is>
+      <c r="B69" s="6" t="n">
+        <v>46049</v>
       </c>
       <c r="C69" s="2" t="inlineStr">
         <is>
-          <t>渋谷　店</t>
+          <t>渋谷店</t>
         </is>
       </c>
       <c r="D69" s="2" t="inlineStr">
         <is>
-          <t>オンライン</t>
+          <t>EC</t>
         </is>
       </c>
       <c r="E69" s="2" t="inlineStr">
@@ -4660,6 +4686,7 @@
           <t>有効</t>
         </is>
       </c>
+      <c r="O69" s="2" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
@@ -4667,7 +4694,7 @@
           <t>A-20260069</t>
         </is>
       </c>
-      <c r="B70" s="3" t="n">
+      <c r="B70" s="6" t="n">
         <v>46028</v>
       </c>
       <c r="C70" s="2" t="inlineStr">
@@ -4677,7 +4704,7 @@
       </c>
       <c r="D70" s="2" t="inlineStr">
         <is>
-          <t>オフライン</t>
+          <t>店頭</t>
         </is>
       </c>
       <c r="E70" s="2" t="inlineStr">
@@ -4687,12 +4714,12 @@
       </c>
       <c r="F70" s="2" t="inlineStr">
         <is>
-          <t>一般客</t>
+          <t>一般</t>
         </is>
       </c>
       <c r="G70" s="2" t="inlineStr">
         <is>
-          <t>珈琲豆</t>
+          <t>コーヒー豆</t>
         </is>
       </c>
       <c r="H70" s="2" t="inlineStr">
@@ -4703,10 +4730,8 @@
       <c r="I70" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="J70" s="2" t="inlineStr">
-        <is>
-          <t>2,600円</t>
-        </is>
+      <c r="J70" s="2" t="n">
+        <v>2600</v>
       </c>
       <c r="K70" s="2" t="n">
         <v>0</v>
@@ -4722,6 +4747,7 @@
           <t>有効</t>
         </is>
       </c>
+      <c r="O70" s="2" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
@@ -4729,7 +4755,7 @@
           <t>A-20260070</t>
         </is>
       </c>
-      <c r="B71" s="3" t="n">
+      <c r="B71" s="6" t="n">
         <v>46037</v>
       </c>
       <c r="C71" s="2" t="inlineStr">
@@ -4739,7 +4765,7 @@
       </c>
       <c r="D71" s="2" t="inlineStr">
         <is>
-          <t>オフライン</t>
+          <t>店頭</t>
         </is>
       </c>
       <c r="E71" s="2" t="inlineStr">
@@ -4750,7 +4776,7 @@
       <c r="F71" s="2" t="n"/>
       <c r="G71" s="2" t="inlineStr">
         <is>
-          <t>抽出器具</t>
+          <t>器具</t>
         </is>
       </c>
       <c r="H71" s="2" t="inlineStr">
@@ -4758,10 +4784,8 @@
           <t>ドリッパー</t>
         </is>
       </c>
-      <c r="I71" s="2" t="inlineStr">
-        <is>
-          <t>２</t>
-        </is>
+      <c r="I71" s="2" t="n">
+        <v>2</v>
       </c>
       <c r="J71" s="2" t="n">
         <v>2800</v>
@@ -4780,6 +4804,7 @@
           <t>有効</t>
         </is>
       </c>
+      <c r="O71" s="2" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
@@ -4787,10 +4812,8 @@
           <t>A-20260071</t>
         </is>
       </c>
-      <c r="B72" s="2" t="inlineStr">
-        <is>
-          <t>2026/1/24</t>
-        </is>
+      <c r="B72" s="6" t="n">
+        <v>46046</v>
       </c>
       <c r="C72" s="2" t="inlineStr">
         <is>
@@ -4799,7 +4822,7 @@
       </c>
       <c r="D72" s="2" t="inlineStr">
         <is>
-          <t>Ｅ Ｃ</t>
+          <t>EC</t>
         </is>
       </c>
       <c r="E72" s="2" t="inlineStr">
@@ -4810,7 +4833,7 @@
       <c r="F72" s="2" t="n"/>
       <c r="G72" s="2" t="inlineStr">
         <is>
-          <t>抽出器具</t>
+          <t>器具</t>
         </is>
       </c>
       <c r="H72" s="2" t="inlineStr">
@@ -4838,6 +4861,7 @@
           <t>有効</t>
         </is>
       </c>
+      <c r="O72" s="2" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
@@ -4845,8 +4869,8 @@
           <t>A-20260072</t>
         </is>
       </c>
-      <c r="B73" s="2" t="n">
-        <v>20260101</v>
+      <c r="B73" s="6" t="n">
+        <v>46023</v>
       </c>
       <c r="C73" s="2" t="inlineStr">
         <is>
@@ -4855,7 +4879,7 @@
       </c>
       <c r="D73" s="2" t="inlineStr">
         <is>
-          <t>オンライン</t>
+          <t>EC</t>
         </is>
       </c>
       <c r="E73" s="2" t="inlineStr">
@@ -4866,7 +4890,7 @@
       <c r="F73" s="2" t="n"/>
       <c r="G73" s="2" t="inlineStr">
         <is>
-          <t>抽出器具</t>
+          <t>器具</t>
         </is>
       </c>
       <c r="H73" s="2" t="inlineStr">
@@ -4894,6 +4918,7 @@
           <t>有効</t>
         </is>
       </c>
+      <c r="O73" s="2" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
@@ -4901,17 +4926,17 @@
           <t>A-20260073</t>
         </is>
       </c>
-      <c r="B74" s="3" t="n">
+      <c r="B74" s="6" t="n">
         <v>46030</v>
       </c>
       <c r="C74" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">横浜店 </t>
+          <t>横浜店</t>
         </is>
       </c>
       <c r="D74" s="2" t="inlineStr">
         <is>
-          <t>Ｅ Ｃ</t>
+          <t>EC</t>
         </is>
       </c>
       <c r="E74" s="2" t="inlineStr">
@@ -4926,7 +4951,7 @@
       </c>
       <c r="G74" s="2" t="inlineStr">
         <is>
-          <t>コーヒー</t>
+          <t>コーヒー豆</t>
         </is>
       </c>
       <c r="H74" s="2" t="inlineStr">
@@ -4954,6 +4979,7 @@
           <t>有効</t>
         </is>
       </c>
+      <c r="O74" s="2" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
@@ -4961,12 +4987,12 @@
           <t>A-20260074</t>
         </is>
       </c>
-      <c r="B75" s="3" t="n">
+      <c r="B75" s="6" t="n">
         <v>46031</v>
       </c>
       <c r="C75" s="2" t="inlineStr">
         <is>
-          <t>フクオカ店</t>
+          <t>福岡店</t>
         </is>
       </c>
       <c r="D75" s="2" t="inlineStr">
@@ -5014,6 +5040,7 @@
           <t>有効</t>
         </is>
       </c>
+      <c r="O75" s="2" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
@@ -5021,17 +5048,17 @@
           <t>A-20260075</t>
         </is>
       </c>
-      <c r="B76" s="3" t="n">
+      <c r="B76" s="6" t="n">
         <v>46025</v>
       </c>
       <c r="C76" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">横浜店 </t>
+          <t>横浜店</t>
         </is>
       </c>
       <c r="D76" s="2" t="inlineStr">
         <is>
-          <t>Web</t>
+          <t>EC</t>
         </is>
       </c>
       <c r="E76" s="2" t="inlineStr">
@@ -5041,7 +5068,7 @@
       </c>
       <c r="F76" s="2" t="inlineStr">
         <is>
-          <t>一般客</t>
+          <t>一般</t>
         </is>
       </c>
       <c r="G76" s="2" t="inlineStr">
@@ -5078,6 +5105,7 @@
           <t>無効</t>
         </is>
       </c>
+      <c r="O76" s="2" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
@@ -5085,10 +5113,8 @@
           <t>A-20260076</t>
         </is>
       </c>
-      <c r="B77" s="2" t="inlineStr">
-        <is>
-          <t>2026-01-21</t>
-        </is>
+      <c r="B77" s="6" t="n">
+        <v>46043</v>
       </c>
       <c r="C77" s="2" t="inlineStr">
         <is>
@@ -5140,6 +5166,7 @@
           <t>有効</t>
         </is>
       </c>
+      <c r="O77" s="2" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
@@ -5147,17 +5174,17 @@
           <t>A-20260077</t>
         </is>
       </c>
-      <c r="B78" s="3" t="n">
+      <c r="B78" s="6" t="n">
         <v>46034</v>
       </c>
       <c r="C78" s="2" t="inlineStr">
         <is>
-          <t>シブヤ店</t>
+          <t>渋谷店</t>
         </is>
       </c>
       <c r="D78" s="2" t="inlineStr">
         <is>
-          <t>オンライン</t>
+          <t>EC</t>
         </is>
       </c>
       <c r="E78" s="2" t="inlineStr">
@@ -5196,6 +5223,7 @@
           <t>有効</t>
         </is>
       </c>
+      <c r="O78" s="2" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
@@ -5203,12 +5231,12 @@
           <t>A-20260078</t>
         </is>
       </c>
-      <c r="B79" s="3" t="n">
+      <c r="B79" s="6" t="n">
         <v>46038</v>
       </c>
       <c r="C79" s="2" t="inlineStr">
         <is>
-          <t>渋谷　店</t>
+          <t>渋谷店</t>
         </is>
       </c>
       <c r="D79" s="2" t="inlineStr">
@@ -5256,6 +5284,7 @@
           <t>有効</t>
         </is>
       </c>
+      <c r="O79" s="2" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
@@ -5263,7 +5292,7 @@
           <t>A-20260079</t>
         </is>
       </c>
-      <c r="B80" s="3" t="n">
+      <c r="B80" s="6" t="n">
         <v>46034</v>
       </c>
       <c r="C80" s="2" t="inlineStr">
@@ -5283,7 +5312,7 @@
       </c>
       <c r="F80" s="2" t="inlineStr">
         <is>
-          <t>メンバー</t>
+          <t>会員</t>
         </is>
       </c>
       <c r="G80" s="2" t="inlineStr">
@@ -5316,6 +5345,7 @@
           <t>有効</t>
         </is>
       </c>
+      <c r="O80" s="2" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
@@ -5323,10 +5353,8 @@
           <t>A-20260080</t>
         </is>
       </c>
-      <c r="B81" s="2" t="inlineStr">
-        <is>
-          <t>1月30日</t>
-        </is>
+      <c r="B81" s="6" t="n">
+        <v>46052</v>
       </c>
       <c r="C81" s="2" t="inlineStr">
         <is>
@@ -5345,7 +5373,7 @@
       </c>
       <c r="F81" s="2" t="inlineStr">
         <is>
-          <t>メンバー</t>
+          <t>会員</t>
         </is>
       </c>
       <c r="G81" s="2" t="inlineStr">
@@ -5378,6 +5406,7 @@
           <t>有効</t>
         </is>
       </c>
+      <c r="O81" s="2" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
@@ -5385,12 +5414,12 @@
           <t>A-20260081</t>
         </is>
       </c>
-      <c r="B82" s="3" t="n">
+      <c r="B82" s="6" t="n">
         <v>46044</v>
       </c>
       <c r="C82" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">渋谷店 </t>
+          <t>渋谷店</t>
         </is>
       </c>
       <c r="D82" s="2" t="inlineStr">
@@ -5438,6 +5467,7 @@
           <t>有効</t>
         </is>
       </c>
+      <c r="O82" s="2" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
@@ -5445,7 +5475,7 @@
           <t>A-20260082</t>
         </is>
       </c>
-      <c r="B83" s="3" t="n">
+      <c r="B83" s="6" t="n">
         <v>46023</v>
       </c>
       <c r="C83" s="2" t="inlineStr">
@@ -5498,6 +5528,7 @@
           <t>有効</t>
         </is>
       </c>
+      <c r="O83" s="2" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
@@ -5505,10 +5536,8 @@
           <t>A-20260083</t>
         </is>
       </c>
-      <c r="B84" s="2" t="inlineStr">
-        <is>
-          <t>2026/1/30</t>
-        </is>
+      <c r="B84" s="6" t="n">
+        <v>46052</v>
       </c>
       <c r="C84" s="2" t="inlineStr">
         <is>
@@ -5543,7 +5572,9 @@
       <c r="I84" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="J84" s="2" t="n"/>
+      <c r="J84" s="7" t="n">
+        <v>1800</v>
+      </c>
       <c r="K84" s="2" t="n">
         <v>0</v>
       </c>
@@ -5558,6 +5589,11 @@
           <t>有効</t>
         </is>
       </c>
+      <c r="O84" s="2" t="inlineStr">
+        <is>
+          <t>補完</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
@@ -5565,8 +5601,8 @@
           <t>A-20260084</t>
         </is>
       </c>
-      <c r="B85" s="2" t="n">
-        <v>20260112</v>
+      <c r="B85" s="6" t="n">
+        <v>46034</v>
       </c>
       <c r="C85" s="2" t="inlineStr">
         <is>
@@ -5575,7 +5611,7 @@
       </c>
       <c r="D85" s="2" t="inlineStr">
         <is>
-          <t>ec</t>
+          <t>EC</t>
         </is>
       </c>
       <c r="E85" s="2" t="inlineStr">
@@ -5614,6 +5650,7 @@
           <t>有効</t>
         </is>
       </c>
+      <c r="O85" s="2" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
@@ -5621,7 +5658,7 @@
           <t>A-20260085</t>
         </is>
       </c>
-      <c r="B86" s="3" t="n">
+      <c r="B86" s="6" t="n">
         <v>46047</v>
       </c>
       <c r="C86" s="2" t="inlineStr">
@@ -5670,6 +5707,7 @@
           <t>有効</t>
         </is>
       </c>
+      <c r="O86" s="2" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
@@ -5677,7 +5715,7 @@
           <t>A-20260086</t>
         </is>
       </c>
-      <c r="B87" s="3" t="n">
+      <c r="B87" s="6" t="n">
         <v>46025</v>
       </c>
       <c r="C87" s="2" t="inlineStr">
@@ -5713,10 +5751,8 @@
       <c r="I87" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="J87" s="2" t="inlineStr">
-        <is>
-          <t>1,800円</t>
-        </is>
+      <c r="J87" s="2" t="n">
+        <v>1800</v>
       </c>
       <c r="K87" s="2" t="n">
         <v>0</v>
@@ -5732,6 +5768,7 @@
           <t>有効</t>
         </is>
       </c>
+      <c r="O87" s="2" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" s="2" t="inlineStr">
@@ -5739,7 +5776,7 @@
           <t>A-20260087</t>
         </is>
       </c>
-      <c r="B88" s="3" t="n">
+      <c r="B88" s="6" t="n">
         <v>46052</v>
       </c>
       <c r="C88" s="2" t="inlineStr">
@@ -5749,7 +5786,7 @@
       </c>
       <c r="D88" s="2" t="inlineStr">
         <is>
-          <t>ec</t>
+          <t>EC</t>
         </is>
       </c>
       <c r="E88" s="2" t="inlineStr">
@@ -5759,12 +5796,12 @@
       </c>
       <c r="F88" s="2" t="inlineStr">
         <is>
-          <t>メンバー</t>
+          <t>会員</t>
         </is>
       </c>
       <c r="G88" s="2" t="inlineStr">
         <is>
-          <t>お菓子</t>
+          <t>菓子</t>
         </is>
       </c>
       <c r="H88" s="2" t="inlineStr">
@@ -5792,6 +5829,7 @@
           <t>有効</t>
         </is>
       </c>
+      <c r="O88" s="2" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" s="2" t="inlineStr">
@@ -5799,10 +5837,8 @@
           <t>A-20260088</t>
         </is>
       </c>
-      <c r="B89" s="2" t="inlineStr">
-        <is>
-          <t>2026-01-30</t>
-        </is>
+      <c r="B89" s="6" t="n">
+        <v>46052</v>
       </c>
       <c r="C89" s="2" t="inlineStr">
         <is>
@@ -5811,7 +5847,7 @@
       </c>
       <c r="D89" s="2" t="inlineStr">
         <is>
-          <t>オフライン</t>
+          <t>店頭</t>
         </is>
       </c>
       <c r="E89" s="2" t="inlineStr">
@@ -5822,7 +5858,7 @@
       <c r="F89" s="2" t="n"/>
       <c r="G89" s="2" t="inlineStr">
         <is>
-          <t>珈琲豆</t>
+          <t>コーヒー豆</t>
         </is>
       </c>
       <c r="H89" s="2" t="inlineStr">
@@ -5833,10 +5869,8 @@
       <c r="I89" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="J89" s="2" t="inlineStr">
-        <is>
-          <t>¥1,400</t>
-        </is>
+      <c r="J89" s="2" t="n">
+        <v>1400</v>
       </c>
       <c r="K89" s="2" t="n">
         <v>0</v>
@@ -5852,6 +5886,7 @@
           <t>有効</t>
         </is>
       </c>
+      <c r="O89" s="2" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" s="2" t="inlineStr">
@@ -5859,7 +5894,7 @@
           <t>A-20260089</t>
         </is>
       </c>
-      <c r="B90" s="3" t="n">
+      <c r="B90" s="6" t="n">
         <v>46023</v>
       </c>
       <c r="C90" s="2" t="inlineStr">
@@ -5869,7 +5904,7 @@
       </c>
       <c r="D90" s="2" t="inlineStr">
         <is>
-          <t>店舗</t>
+          <t>店頭</t>
         </is>
       </c>
       <c r="E90" s="2" t="inlineStr">
@@ -5908,6 +5943,7 @@
           <t>有効</t>
         </is>
       </c>
+      <c r="O90" s="2" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="A91" s="2" t="inlineStr">
@@ -5915,7 +5951,7 @@
           <t>A-20260090</t>
         </is>
       </c>
-      <c r="B91" s="3" t="n">
+      <c r="B91" s="6" t="n">
         <v>46052</v>
       </c>
       <c r="C91" s="2" t="inlineStr">
@@ -5925,7 +5961,7 @@
       </c>
       <c r="D91" s="2" t="inlineStr">
         <is>
-          <t>オフライン</t>
+          <t>店頭</t>
         </is>
       </c>
       <c r="E91" s="2" t="inlineStr">
@@ -5950,10 +5986,8 @@
       <c r="J91" s="2" t="n">
         <v>1500</v>
       </c>
-      <c r="K91" s="2" t="inlineStr">
-        <is>
-          <t>10%</t>
-        </is>
+      <c r="K91" s="2" t="n">
+        <v>0.1</v>
       </c>
       <c r="L91" s="2" t="inlineStr">
         <is>
@@ -5966,6 +6000,7 @@
           <t>有効</t>
         </is>
       </c>
+      <c r="O91" s="2" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="A92" s="2" t="inlineStr">
@@ -5973,17 +6008,17 @@
           <t>A-20260091</t>
         </is>
       </c>
-      <c r="B92" s="3" t="n">
+      <c r="B92" s="6" t="n">
         <v>46052</v>
       </c>
       <c r="C92" s="2" t="inlineStr">
         <is>
-          <t>新宿 店</t>
+          <t>新宿店</t>
         </is>
       </c>
       <c r="D92" s="2" t="inlineStr">
         <is>
-          <t>Ｅ Ｃ</t>
+          <t>EC</t>
         </is>
       </c>
       <c r="E92" s="2" t="inlineStr">
@@ -6013,7 +6048,7 @@
         <v>1800</v>
       </c>
       <c r="K92" s="2" t="n">
-        <v>5</v>
+        <v>0.05</v>
       </c>
       <c r="L92" s="2" t="inlineStr">
         <is>
@@ -6026,6 +6061,7 @@
           <t>有効</t>
         </is>
       </c>
+      <c r="O92" s="2" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" s="2" t="inlineStr">
@@ -6033,10 +6069,8 @@
           <t>A-20260092</t>
         </is>
       </c>
-      <c r="B93" s="2" t="inlineStr">
-        <is>
-          <t>1月13日</t>
-        </is>
+      <c r="B93" s="6" t="n">
+        <v>46035</v>
       </c>
       <c r="C93" s="2" t="inlineStr">
         <is>
@@ -6045,7 +6079,7 @@
       </c>
       <c r="D93" s="2" t="inlineStr">
         <is>
-          <t>店舗</t>
+          <t>店頭</t>
         </is>
       </c>
       <c r="E93" s="2" t="inlineStr">
@@ -6074,10 +6108,8 @@
       <c r="J93" s="2" t="n">
         <v>5800</v>
       </c>
-      <c r="K93" s="2" t="inlineStr">
-        <is>
-          <t>10%</t>
-        </is>
+      <c r="K93" s="2" t="n">
+        <v>0.1</v>
       </c>
       <c r="L93" s="2" t="inlineStr">
         <is>
@@ -6090,6 +6122,7 @@
           <t>有効</t>
         </is>
       </c>
+      <c r="O93" s="2" t="inlineStr"/>
     </row>
     <row r="94">
       <c r="A94" s="2" t="inlineStr">
@@ -6097,7 +6130,7 @@
           <t>A-20260093</t>
         </is>
       </c>
-      <c r="B94" s="3" t="n">
+      <c r="B94" s="6" t="n">
         <v>46029</v>
       </c>
       <c r="C94" s="2" t="inlineStr">
@@ -6107,7 +6140,7 @@
       </c>
       <c r="D94" s="2" t="inlineStr">
         <is>
-          <t>Ｅ Ｃ</t>
+          <t>EC</t>
         </is>
       </c>
       <c r="E94" s="2" t="inlineStr">
@@ -6117,7 +6150,7 @@
       </c>
       <c r="F94" s="2" t="inlineStr">
         <is>
-          <t>一般客</t>
+          <t>一般</t>
         </is>
       </c>
       <c r="G94" s="2" t="inlineStr">
@@ -6130,10 +6163,8 @@
           <t>電動ミル</t>
         </is>
       </c>
-      <c r="I94" s="2" t="inlineStr">
-        <is>
-          <t>２</t>
-        </is>
+      <c r="I94" s="2" t="n">
+        <v>2</v>
       </c>
       <c r="J94" s="2" t="n">
         <v>9800</v>
@@ -6152,6 +6183,7 @@
           <t>有効</t>
         </is>
       </c>
+      <c r="O94" s="2" t="inlineStr"/>
     </row>
     <row r="95">
       <c r="A95" s="2" t="inlineStr">
@@ -6159,7 +6191,7 @@
           <t>A-20260094</t>
         </is>
       </c>
-      <c r="B95" s="3" t="n">
+      <c r="B95" s="6" t="n">
         <v>46052</v>
       </c>
       <c r="C95" s="2" t="inlineStr">
@@ -6192,10 +6224,8 @@
           <t>サーバー 600ml</t>
         </is>
       </c>
-      <c r="I95" s="2" t="inlineStr">
-        <is>
-          <t>1個</t>
-        </is>
+      <c r="I95" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="J95" s="2" t="n">
         <v>3200</v>
@@ -6214,6 +6244,7 @@
           <t>有効</t>
         </is>
       </c>
+      <c r="O95" s="2" t="inlineStr"/>
     </row>
     <row r="96">
       <c r="A96" s="2" t="inlineStr">
@@ -6221,14 +6252,12 @@
           <t>A-20260095</t>
         </is>
       </c>
-      <c r="B96" s="2" t="inlineStr">
-        <is>
-          <t>2026/1/19</t>
-        </is>
+      <c r="B96" s="6" t="n">
+        <v>46041</v>
       </c>
       <c r="C96" s="2" t="inlineStr">
         <is>
-          <t>ヨコハマ店</t>
+          <t>横浜店</t>
         </is>
       </c>
       <c r="D96" s="2" t="inlineStr">
@@ -6276,6 +6305,7 @@
           <t>有効</t>
         </is>
       </c>
+      <c r="O96" s="2" t="inlineStr"/>
     </row>
     <row r="97">
       <c r="A97" s="2" t="inlineStr">
@@ -6283,8 +6313,8 @@
           <t>A-20260096</t>
         </is>
       </c>
-      <c r="B97" s="2" t="n">
-        <v>20260119</v>
+      <c r="B97" s="6" t="n">
+        <v>46041</v>
       </c>
       <c r="C97" s="2" t="inlineStr">
         <is>
@@ -6293,7 +6323,7 @@
       </c>
       <c r="D97" s="2" t="inlineStr">
         <is>
-          <t>ec</t>
+          <t>EC</t>
         </is>
       </c>
       <c r="E97" s="2" t="inlineStr">
@@ -6336,6 +6366,7 @@
           <t>有効</t>
         </is>
       </c>
+      <c r="O97" s="2" t="inlineStr"/>
     </row>
     <row r="98">
       <c r="A98" s="2" t="inlineStr">
@@ -6343,7 +6374,7 @@
           <t>A-20260097</t>
         </is>
       </c>
-      <c r="B98" s="3" t="n">
+      <c r="B98" s="6" t="n">
         <v>46045</v>
       </c>
       <c r="C98" s="2" t="inlineStr">
@@ -6353,7 +6384,7 @@
       </c>
       <c r="D98" s="2" t="inlineStr">
         <is>
-          <t>オフライン</t>
+          <t>店頭</t>
         </is>
       </c>
       <c r="E98" s="2" t="inlineStr">
@@ -6363,7 +6394,7 @@
       </c>
       <c r="F98" s="2" t="inlineStr">
         <is>
-          <t>一般客</t>
+          <t>一般</t>
         </is>
       </c>
       <c r="G98" s="2" t="inlineStr">
@@ -6383,7 +6414,7 @@
         <v>2600</v>
       </c>
       <c r="K98" s="2" t="n">
-        <v>5</v>
+        <v>0.05</v>
       </c>
       <c r="L98" s="2" t="inlineStr">
         <is>
@@ -6396,6 +6427,7 @@
           <t>有効</t>
         </is>
       </c>
+      <c r="O98" s="2" t="inlineStr"/>
     </row>
     <row r="99">
       <c r="A99" s="2" t="inlineStr">
@@ -6403,7 +6435,7 @@
           <t>A-20260098</t>
         </is>
       </c>
-      <c r="B99" s="3" t="n">
+      <c r="B99" s="6" t="n">
         <v>46046</v>
       </c>
       <c r="C99" s="2" t="inlineStr">
@@ -6456,6 +6488,7 @@
           <t>有効</t>
         </is>
       </c>
+      <c r="O99" s="2" t="inlineStr"/>
     </row>
     <row r="100">
       <c r="A100" s="2" t="inlineStr">
@@ -6463,7 +6496,7 @@
           <t>A-20260099</t>
         </is>
       </c>
-      <c r="B100" s="3" t="n">
+      <c r="B100" s="6" t="n">
         <v>46034</v>
       </c>
       <c r="C100" s="2" t="inlineStr">
@@ -6516,6 +6549,7 @@
           <t>有効</t>
         </is>
       </c>
+      <c r="O100" s="2" t="inlineStr"/>
     </row>
     <row r="101">
       <c r="A101" s="2" t="inlineStr">
@@ -6523,19 +6557,17 @@
           <t>A-20260100</t>
         </is>
       </c>
-      <c r="B101" s="2" t="inlineStr">
-        <is>
-          <t>2026-01-13</t>
-        </is>
+      <c r="B101" s="6" t="n">
+        <v>46035</v>
       </c>
       <c r="C101" s="2" t="inlineStr">
         <is>
-          <t>ヨコハマ店</t>
+          <t>横浜店</t>
         </is>
       </c>
       <c r="D101" s="2" t="inlineStr">
         <is>
-          <t>店舗</t>
+          <t>店頭</t>
         </is>
       </c>
       <c r="E101" s="2" t="inlineStr">
@@ -6578,6 +6610,7 @@
           <t>有効</t>
         </is>
       </c>
+      <c r="O101" s="2" t="inlineStr"/>
     </row>
     <row r="102">
       <c r="A102" s="2" t="inlineStr">
@@ -6585,17 +6618,17 @@
           <t>A-20260101</t>
         </is>
       </c>
-      <c r="B102" s="3" t="n">
+      <c r="B102" s="6" t="n">
         <v>46042</v>
       </c>
       <c r="C102" s="2" t="inlineStr">
         <is>
-          <t>新宿 店</t>
+          <t>新宿店</t>
         </is>
       </c>
       <c r="D102" s="2" t="inlineStr">
         <is>
-          <t>ec</t>
+          <t>EC</t>
         </is>
       </c>
       <c r="E102" s="2" t="inlineStr">
@@ -6638,6 +6671,7 @@
           <t>有効</t>
         </is>
       </c>
+      <c r="O102" s="2" t="inlineStr"/>
     </row>
     <row r="103">
       <c r="A103" s="2" t="inlineStr">
@@ -6645,7 +6679,7 @@
           <t>A-20260102</t>
         </is>
       </c>
-      <c r="B103" s="3" t="n">
+      <c r="B103" s="6" t="n">
         <v>46045</v>
       </c>
       <c r="C103" s="2" t="inlineStr">
@@ -6698,6 +6732,7 @@
           <t>有効</t>
         </is>
       </c>
+      <c r="O103" s="2" t="inlineStr"/>
     </row>
     <row r="104">
       <c r="A104" s="2" t="inlineStr">
@@ -6705,7 +6740,7 @@
           <t>A-20260103</t>
         </is>
       </c>
-      <c r="B104" s="3" t="n">
+      <c r="B104" s="6" t="n">
         <v>46035</v>
       </c>
       <c r="C104" s="2" t="inlineStr">
@@ -6741,10 +6776,8 @@
       <c r="I104" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="J104" s="2" t="inlineStr">
-        <is>
-          <t>2,600円</t>
-        </is>
+      <c r="J104" s="2" t="n">
+        <v>2600</v>
       </c>
       <c r="K104" s="2" t="n">
         <v>0</v>
@@ -6760,6 +6793,7 @@
           <t>有効</t>
         </is>
       </c>
+      <c r="O104" s="2" t="inlineStr"/>
     </row>
     <row r="105">
       <c r="A105" s="2" t="inlineStr">
@@ -6767,10 +6801,8 @@
           <t>A-20260104</t>
         </is>
       </c>
-      <c r="B105" s="2" t="inlineStr">
-        <is>
-          <t>1月28日</t>
-        </is>
+      <c r="B105" s="6" t="n">
+        <v>46050</v>
       </c>
       <c r="C105" s="2" t="inlineStr">
         <is>
@@ -6779,7 +6811,7 @@
       </c>
       <c r="D105" s="2" t="inlineStr">
         <is>
-          <t>店舗</t>
+          <t>店頭</t>
         </is>
       </c>
       <c r="E105" s="2" t="inlineStr">
@@ -6794,7 +6826,7 @@
       </c>
       <c r="G105" s="2" t="inlineStr">
         <is>
-          <t>抽出器具</t>
+          <t>器具</t>
         </is>
       </c>
       <c r="H105" s="2" t="inlineStr">
@@ -6822,6 +6854,7 @@
           <t>有効</t>
         </is>
       </c>
+      <c r="O105" s="2" t="inlineStr"/>
     </row>
     <row r="106">
       <c r="A106" s="2" t="inlineStr">
@@ -6829,17 +6862,17 @@
           <t>A-20260105</t>
         </is>
       </c>
-      <c r="B106" s="3" t="n">
+      <c r="B106" s="6" t="n">
         <v>46034</v>
       </c>
       <c r="C106" s="2" t="inlineStr">
         <is>
-          <t>ヨコハマ店</t>
+          <t>横浜店</t>
         </is>
       </c>
       <c r="D106" s="2" t="inlineStr">
         <is>
-          <t>オンライン</t>
+          <t>EC</t>
         </is>
       </c>
       <c r="E106" s="2" t="inlineStr">
@@ -6850,7 +6883,7 @@
       <c r="F106" s="2" t="n"/>
       <c r="G106" s="2" t="inlineStr">
         <is>
-          <t>ギフト商品</t>
+          <t>ギフト</t>
         </is>
       </c>
       <c r="H106" s="2" t="inlineStr">
@@ -6878,6 +6911,7 @@
           <t>有効</t>
         </is>
       </c>
+      <c r="O106" s="2" t="inlineStr"/>
     </row>
     <row r="107">
       <c r="A107" s="2" t="inlineStr">
@@ -6885,17 +6919,17 @@
           <t>A-20260106</t>
         </is>
       </c>
-      <c r="B107" s="3" t="n">
+      <c r="B107" s="6" t="n">
         <v>46053</v>
       </c>
       <c r="C107" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">渋谷店 </t>
+          <t>渋谷店</t>
         </is>
       </c>
       <c r="D107" s="2" t="inlineStr">
         <is>
-          <t>オフライン</t>
+          <t>店頭</t>
         </is>
       </c>
       <c r="E107" s="2" t="inlineStr">
@@ -6938,6 +6972,7 @@
           <t>有効</t>
         </is>
       </c>
+      <c r="O107" s="2" t="inlineStr"/>
     </row>
     <row r="108">
       <c r="A108" s="2" t="inlineStr">
@@ -6945,10 +6980,8 @@
           <t>A-20260107</t>
         </is>
       </c>
-      <c r="B108" s="2" t="inlineStr">
-        <is>
-          <t>2026/1/8</t>
-        </is>
+      <c r="B108" s="6" t="n">
+        <v>46030</v>
       </c>
       <c r="C108" s="2" t="inlineStr">
         <is>
@@ -6957,7 +6990,7 @@
       </c>
       <c r="D108" s="2" t="inlineStr">
         <is>
-          <t>オフライン</t>
+          <t>店頭</t>
         </is>
       </c>
       <c r="E108" s="2" t="inlineStr">
@@ -7004,6 +7037,7 @@
           <t>無効</t>
         </is>
       </c>
+      <c r="O108" s="2" t="inlineStr"/>
     </row>
     <row r="109">
       <c r="A109" s="2" t="inlineStr">
@@ -7011,8 +7045,8 @@
           <t>A-20260108</t>
         </is>
       </c>
-      <c r="B109" s="2" t="n">
-        <v>20260128</v>
+      <c r="B109" s="6" t="n">
+        <v>46050</v>
       </c>
       <c r="C109" s="2" t="inlineStr">
         <is>
@@ -7036,7 +7070,7 @@
       </c>
       <c r="G109" s="2" t="inlineStr">
         <is>
-          <t>お菓子</t>
+          <t>菓子</t>
         </is>
       </c>
       <c r="H109" s="2" t="inlineStr">
@@ -7064,6 +7098,7 @@
           <t>有効</t>
         </is>
       </c>
+      <c r="O109" s="2" t="inlineStr"/>
     </row>
     <row r="110">
       <c r="A110" s="2" t="inlineStr">
@@ -7071,17 +7106,17 @@
           <t>A-20260109</t>
         </is>
       </c>
-      <c r="B110" s="3" t="n">
+      <c r="B110" s="6" t="n">
         <v>46025</v>
       </c>
       <c r="C110" s="2" t="inlineStr">
         <is>
-          <t>名古屋 店</t>
+          <t>名古屋店</t>
         </is>
       </c>
       <c r="D110" s="2" t="inlineStr">
         <is>
-          <t>オンライン</t>
+          <t>EC</t>
         </is>
       </c>
       <c r="E110" s="2" t="inlineStr">
@@ -7124,6 +7159,7 @@
           <t>有効</t>
         </is>
       </c>
+      <c r="O110" s="2" t="inlineStr"/>
     </row>
     <row r="111">
       <c r="A111" s="2" t="inlineStr">
@@ -7131,7 +7167,7 @@
           <t>A-20260110</t>
         </is>
       </c>
-      <c r="B111" s="3" t="n">
+      <c r="B111" s="6" t="n">
         <v>46025</v>
       </c>
       <c r="C111" s="2" t="inlineStr">
@@ -7184,6 +7220,7 @@
           <t>有効</t>
         </is>
       </c>
+      <c r="O111" s="2" t="inlineStr"/>
     </row>
     <row r="112">
       <c r="A112" s="2" t="inlineStr">
@@ -7191,17 +7228,17 @@
           <t>A-20260111</t>
         </is>
       </c>
-      <c r="B112" s="3" t="n">
+      <c r="B112" s="6" t="n">
         <v>46031</v>
       </c>
       <c r="C112" s="2" t="inlineStr">
         <is>
-          <t>しんじゅく店</t>
+          <t>新宿店</t>
         </is>
       </c>
       <c r="D112" s="2" t="inlineStr">
         <is>
-          <t>店舗</t>
+          <t>店頭</t>
         </is>
       </c>
       <c r="E112" s="2" t="inlineStr">
@@ -7244,6 +7281,7 @@
           <t>有効</t>
         </is>
       </c>
+      <c r="O112" s="2" t="inlineStr"/>
     </row>
     <row r="113">
       <c r="A113" s="2" t="inlineStr">
@@ -7251,19 +7289,17 @@
           <t>A-20260112</t>
         </is>
       </c>
-      <c r="B113" s="2" t="inlineStr">
-        <is>
-          <t>2026-01-19</t>
-        </is>
+      <c r="B113" s="6" t="n">
+        <v>46041</v>
       </c>
       <c r="C113" s="2" t="inlineStr">
         <is>
-          <t>シブヤ店</t>
+          <t>渋谷店</t>
         </is>
       </c>
       <c r="D113" s="2" t="inlineStr">
         <is>
-          <t>オンライン</t>
+          <t>EC</t>
         </is>
       </c>
       <c r="E113" s="2" t="inlineStr">
@@ -7278,7 +7314,7 @@
       </c>
       <c r="G113" s="2" t="inlineStr">
         <is>
-          <t>抽出器具</t>
+          <t>器具</t>
         </is>
       </c>
       <c r="H113" s="2" t="inlineStr">
@@ -7310,6 +7346,7 @@
           <t>無効</t>
         </is>
       </c>
+      <c r="O113" s="2" t="inlineStr"/>
     </row>
     <row r="114">
       <c r="A114" s="2" t="inlineStr">
@@ -7317,12 +7354,12 @@
           <t>A-20260113</t>
         </is>
       </c>
-      <c r="B114" s="3" t="n">
+      <c r="B114" s="6" t="n">
         <v>46025</v>
       </c>
       <c r="C114" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">横浜店 </t>
+          <t>横浜店</t>
         </is>
       </c>
       <c r="D114" s="2" t="inlineStr">
@@ -7370,6 +7407,7 @@
           <t>有効</t>
         </is>
       </c>
+      <c r="O114" s="2" t="inlineStr"/>
     </row>
     <row r="115">
       <c r="A115" s="2" t="inlineStr">
@@ -7377,7 +7415,7 @@
           <t>A-20260114</t>
         </is>
       </c>
-      <c r="B115" s="3" t="n">
+      <c r="B115" s="6" t="n">
         <v>46038</v>
       </c>
       <c r="C115" s="2" t="inlineStr">
@@ -7387,7 +7425,7 @@
       </c>
       <c r="D115" s="2" t="inlineStr">
         <is>
-          <t>オンライン</t>
+          <t>EC</t>
         </is>
       </c>
       <c r="E115" s="2" t="inlineStr">
@@ -7430,6 +7468,7 @@
           <t>有効</t>
         </is>
       </c>
+      <c r="O115" s="2" t="inlineStr"/>
     </row>
     <row r="116">
       <c r="A116" s="2" t="inlineStr">
@@ -7437,12 +7476,12 @@
           <t>A-20260115</t>
         </is>
       </c>
-      <c r="B116" s="3" t="n">
+      <c r="B116" s="6" t="n">
         <v>46032</v>
       </c>
       <c r="C116" s="2" t="inlineStr">
         <is>
-          <t>名古屋 店</t>
+          <t>名古屋店</t>
         </is>
       </c>
       <c r="D116" s="2" t="inlineStr">
@@ -7490,6 +7529,7 @@
           <t>有効</t>
         </is>
       </c>
+      <c r="O116" s="2" t="inlineStr"/>
     </row>
     <row r="117">
       <c r="A117" s="2" t="inlineStr">
@@ -7497,19 +7537,17 @@
           <t>A-20260116</t>
         </is>
       </c>
-      <c r="B117" s="2" t="inlineStr">
-        <is>
-          <t>1月18日</t>
-        </is>
+      <c r="B117" s="6" t="n">
+        <v>46040</v>
       </c>
       <c r="C117" s="2" t="inlineStr">
         <is>
-          <t>シブヤ店</t>
+          <t>渋谷店</t>
         </is>
       </c>
       <c r="D117" s="2" t="inlineStr">
         <is>
-          <t>店舗</t>
+          <t>店頭</t>
         </is>
       </c>
       <c r="E117" s="2" t="inlineStr">
@@ -7532,10 +7570,8 @@
           <t>ドリップバッグ12個入</t>
         </is>
       </c>
-      <c r="I117" s="2" t="inlineStr">
-        <is>
-          <t>４</t>
-        </is>
+      <c r="I117" s="2" t="n">
+        <v>4</v>
       </c>
       <c r="J117" s="2" t="n">
         <v>1800</v>
@@ -7554,6 +7590,7 @@
           <t>有効</t>
         </is>
       </c>
+      <c r="O117" s="2" t="inlineStr"/>
     </row>
     <row r="118">
       <c r="A118" s="2" t="inlineStr">
@@ -7561,17 +7598,17 @@
           <t>A-20260117</t>
         </is>
       </c>
-      <c r="B118" s="3" t="n">
+      <c r="B118" s="6" t="n">
         <v>46036</v>
       </c>
       <c r="C118" s="2" t="inlineStr">
         <is>
-          <t>しんじゅく店</t>
+          <t>新宿店</t>
         </is>
       </c>
       <c r="D118" s="2" t="inlineStr">
         <is>
-          <t>ec</t>
+          <t>EC</t>
         </is>
       </c>
       <c r="E118" s="2" t="inlineStr">
@@ -7597,10 +7634,8 @@
       <c r="I118" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="J118" s="2" t="inlineStr">
-        <is>
-          <t>¥5,800</t>
-        </is>
+      <c r="J118" s="2" t="n">
+        <v>5800</v>
       </c>
       <c r="K118" s="2" t="n">
         <v>0</v>
@@ -7616,6 +7651,7 @@
           <t>有効</t>
         </is>
       </c>
+      <c r="O118" s="2" t="inlineStr"/>
     </row>
     <row r="119">
       <c r="A119" s="2" t="inlineStr">
@@ -7623,7 +7659,7 @@
           <t>A-20260118</t>
         </is>
       </c>
-      <c r="B119" s="3" t="n">
+      <c r="B119" s="6" t="n">
         <v>46039</v>
       </c>
       <c r="C119" s="2" t="inlineStr">
@@ -7676,6 +7712,7 @@
           <t>有効</t>
         </is>
       </c>
+      <c r="O119" s="2" t="inlineStr"/>
     </row>
     <row r="120">
       <c r="A120" s="2" t="inlineStr">
@@ -7683,19 +7720,17 @@
           <t>A-20260119</t>
         </is>
       </c>
-      <c r="B120" s="2" t="inlineStr">
-        <is>
-          <t>2026/1/11</t>
-        </is>
+      <c r="B120" s="6" t="n">
+        <v>46033</v>
       </c>
       <c r="C120" s="2" t="inlineStr">
         <is>
-          <t>名古屋 店</t>
+          <t>名古屋店</t>
         </is>
       </c>
       <c r="D120" s="2" t="inlineStr">
         <is>
-          <t>ec</t>
+          <t>EC</t>
         </is>
       </c>
       <c r="E120" s="2" t="inlineStr">
@@ -7738,6 +7773,7 @@
           <t>有効</t>
         </is>
       </c>
+      <c r="O120" s="2" t="inlineStr"/>
     </row>
     <row r="121">
       <c r="A121" s="2" t="inlineStr">
@@ -7745,17 +7781,17 @@
           <t>A-20260120</t>
         </is>
       </c>
-      <c r="B121" s="2" t="n">
-        <v>20260129</v>
+      <c r="B121" s="6" t="n">
+        <v>46051</v>
       </c>
       <c r="C121" s="2" t="inlineStr">
         <is>
-          <t>渋谷　店</t>
+          <t>渋谷店</t>
         </is>
       </c>
       <c r="D121" s="2" t="inlineStr">
         <is>
-          <t>Web</t>
+          <t>EC</t>
         </is>
       </c>
       <c r="E121" s="2" t="inlineStr">
@@ -7765,12 +7801,12 @@
       </c>
       <c r="F121" s="2" t="inlineStr">
         <is>
-          <t>一般客</t>
+          <t>一般</t>
         </is>
       </c>
       <c r="G121" s="2" t="inlineStr">
         <is>
-          <t>ギフト商品</t>
+          <t>ギフト</t>
         </is>
       </c>
       <c r="H121" s="2" t="inlineStr">
@@ -7781,10 +7817,8 @@
       <c r="I121" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="J121" s="2" t="inlineStr">
-        <is>
-          <t>3,800円</t>
-        </is>
+      <c r="J121" s="2" t="n">
+        <v>3800</v>
       </c>
       <c r="K121" s="2" t="n">
         <v>0</v>
@@ -7800,6 +7834,7 @@
           <t>有効</t>
         </is>
       </c>
+      <c r="O121" s="2" t="inlineStr"/>
     </row>
     <row r="122">
       <c r="A122" s="2" t="inlineStr">
@@ -7807,12 +7842,12 @@
           <t>A-20260121</t>
         </is>
       </c>
-      <c r="B122" s="3" t="n">
+      <c r="B122" s="6" t="n">
         <v>46027</v>
       </c>
       <c r="C122" s="2" t="inlineStr">
         <is>
-          <t>フクオカ店</t>
+          <t>福岡店</t>
         </is>
       </c>
       <c r="D122" s="2" t="inlineStr">
@@ -7860,6 +7895,7 @@
           <t>有効</t>
         </is>
       </c>
+      <c r="O122" s="2" t="inlineStr"/>
     </row>
     <row r="123">
       <c r="A123" s="2" t="inlineStr">
@@ -7867,7 +7903,7 @@
           <t>A-20260122</t>
         </is>
       </c>
-      <c r="B123" s="3" t="n">
+      <c r="B123" s="6" t="n">
         <v>46051</v>
       </c>
       <c r="C123" s="2" t="inlineStr">
@@ -7877,7 +7913,7 @@
       </c>
       <c r="D123" s="2" t="inlineStr">
         <is>
-          <t>Web</t>
+          <t>EC</t>
         </is>
       </c>
       <c r="E123" s="2" t="inlineStr">
@@ -7892,7 +7928,7 @@
       </c>
       <c r="G123" s="2" t="inlineStr">
         <is>
-          <t>珈琲豆</t>
+          <t>コーヒー豆</t>
         </is>
       </c>
       <c r="H123" s="2" t="inlineStr">
@@ -7920,6 +7956,7 @@
           <t>有効</t>
         </is>
       </c>
+      <c r="O123" s="2" t="inlineStr"/>
     </row>
     <row r="124">
       <c r="A124" s="2" t="inlineStr">
@@ -7927,7 +7964,7 @@
           <t>A-20260123</t>
         </is>
       </c>
-      <c r="B124" s="3" t="n">
+      <c r="B124" s="6" t="n">
         <v>46035</v>
       </c>
       <c r="C124" s="2" t="inlineStr">
@@ -7937,7 +7974,7 @@
       </c>
       <c r="D124" s="2" t="inlineStr">
         <is>
-          <t>店舗</t>
+          <t>店頭</t>
         </is>
       </c>
       <c r="E124" s="2" t="inlineStr">
@@ -7952,7 +7989,7 @@
       </c>
       <c r="G124" s="2" t="inlineStr">
         <is>
-          <t>抽出器具</t>
+          <t>器具</t>
         </is>
       </c>
       <c r="H124" s="2" t="inlineStr">
@@ -7984,6 +8021,7 @@
           <t>有効</t>
         </is>
       </c>
+      <c r="O124" s="2" t="inlineStr"/>
     </row>
     <row r="125">
       <c r="A125" s="2" t="inlineStr">
@@ -7991,14 +8029,12 @@
           <t>A-20260124</t>
         </is>
       </c>
-      <c r="B125" s="2" t="inlineStr">
-        <is>
-          <t>2026-01-02</t>
-        </is>
+      <c r="B125" s="6" t="n">
+        <v>46024</v>
       </c>
       <c r="C125" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">横浜店 </t>
+          <t>横浜店</t>
         </is>
       </c>
       <c r="D125" s="2" t="inlineStr">
@@ -8013,7 +8049,7 @@
       </c>
       <c r="F125" s="2" t="inlineStr">
         <is>
-          <t>メンバー</t>
+          <t>会員</t>
         </is>
       </c>
       <c r="G125" s="2" t="inlineStr">
@@ -8029,7 +8065,9 @@
       <c r="I125" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="J125" s="2" t="n"/>
+      <c r="J125" s="7" t="n">
+        <v>5800</v>
+      </c>
       <c r="K125" s="2" t="n">
         <v>0</v>
       </c>
@@ -8044,6 +8082,11 @@
           <t>有効</t>
         </is>
       </c>
+      <c r="O125" s="2" t="inlineStr">
+        <is>
+          <t>補完</t>
+        </is>
+      </c>
     </row>
     <row r="126">
       <c r="A126" s="2" t="inlineStr">
@@ -8051,12 +8094,12 @@
           <t>A-20260125</t>
         </is>
       </c>
-      <c r="B126" s="3" t="n">
+      <c r="B126" s="6" t="n">
         <v>46053</v>
       </c>
       <c r="C126" s="2" t="inlineStr">
         <is>
-          <t>渋谷　店</t>
+          <t>渋谷店</t>
         </is>
       </c>
       <c r="D126" s="2" t="inlineStr">
@@ -8084,10 +8127,8 @@
           <t>季節限定ブレンド 200g</t>
         </is>
       </c>
-      <c r="I126" s="2" t="inlineStr">
-        <is>
-          <t>1個</t>
-        </is>
+      <c r="I126" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="J126" s="2" t="n">
         <v>1600</v>
@@ -8106,6 +8147,7 @@
           <t>有効</t>
         </is>
       </c>
+      <c r="O126" s="2" t="inlineStr"/>
     </row>
     <row r="127">
       <c r="A127" s="2" t="inlineStr">
@@ -8113,7 +8155,7 @@
           <t>A-20260126</t>
         </is>
       </c>
-      <c r="B127" s="3" t="n">
+      <c r="B127" s="6" t="n">
         <v>46037</v>
       </c>
       <c r="C127" s="2" t="inlineStr">
@@ -8123,7 +8165,7 @@
       </c>
       <c r="D127" s="2" t="inlineStr">
         <is>
-          <t>店舗</t>
+          <t>店頭</t>
         </is>
       </c>
       <c r="E127" s="2" t="inlineStr">
@@ -8152,10 +8194,8 @@
       <c r="J127" s="2" t="n">
         <v>2800</v>
       </c>
-      <c r="K127" s="2" t="inlineStr">
-        <is>
-          <t>10%</t>
-        </is>
+      <c r="K127" s="2" t="n">
+        <v>0.1</v>
       </c>
       <c r="L127" s="2" t="inlineStr">
         <is>
@@ -8168,6 +8208,7 @@
           <t>有効</t>
         </is>
       </c>
+      <c r="O127" s="2" t="inlineStr"/>
     </row>
     <row r="128">
       <c r="A128" s="2" t="inlineStr">
@@ -8175,17 +8216,17 @@
           <t>A-20260127</t>
         </is>
       </c>
-      <c r="B128" s="3" t="n">
+      <c r="B128" s="6" t="n">
         <v>46037</v>
       </c>
       <c r="C128" s="2" t="inlineStr">
         <is>
-          <t>新宿 店</t>
+          <t>新宿店</t>
         </is>
       </c>
       <c r="D128" s="2" t="inlineStr">
         <is>
-          <t>Web</t>
+          <t>EC</t>
         </is>
       </c>
       <c r="E128" s="2" t="inlineStr">
@@ -8228,6 +8269,7 @@
           <t>有効</t>
         </is>
       </c>
+      <c r="O128" s="2" t="inlineStr"/>
     </row>
     <row r="129">
       <c r="A129" s="2" t="inlineStr">
@@ -8235,10 +8277,8 @@
           <t>A-20260128</t>
         </is>
       </c>
-      <c r="B129" s="2" t="inlineStr">
-        <is>
-          <t>1月24日</t>
-        </is>
+      <c r="B129" s="6" t="n">
+        <v>46046</v>
       </c>
       <c r="C129" s="2" t="inlineStr">
         <is>
@@ -8257,7 +8297,7 @@
       </c>
       <c r="F129" s="2" t="inlineStr">
         <is>
-          <t>一般客</t>
+          <t>一般</t>
         </is>
       </c>
       <c r="G129" s="2" t="inlineStr">
@@ -8290,6 +8330,7 @@
           <t>有効</t>
         </is>
       </c>
+      <c r="O129" s="2" t="inlineStr"/>
     </row>
     <row r="130">
       <c r="A130" s="2" t="inlineStr">
@@ -8297,17 +8338,17 @@
           <t>A-20260129</t>
         </is>
       </c>
-      <c r="B130" s="3" t="n">
+      <c r="B130" s="6" t="n">
         <v>46039</v>
       </c>
       <c r="C130" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">渋谷店 </t>
+          <t>渋谷店</t>
         </is>
       </c>
       <c r="D130" s="2" t="inlineStr">
         <is>
-          <t>Ｅ Ｃ</t>
+          <t>EC</t>
         </is>
       </c>
       <c r="E130" s="2" t="inlineStr">
@@ -8350,6 +8391,7 @@
           <t>有効</t>
         </is>
       </c>
+      <c r="O130" s="2" t="inlineStr"/>
     </row>
     <row r="131">
       <c r="A131" s="2" t="inlineStr">
@@ -8357,7 +8399,7 @@
           <t>A-20260130</t>
         </is>
       </c>
-      <c r="B131" s="3" t="n">
+      <c r="B131" s="6" t="n">
         <v>46052</v>
       </c>
       <c r="C131" s="2" t="inlineStr">
@@ -8377,7 +8419,7 @@
       </c>
       <c r="F131" s="2" t="inlineStr">
         <is>
-          <t>一般客</t>
+          <t>一般</t>
         </is>
       </c>
       <c r="G131" s="2" t="inlineStr">
@@ -8410,6 +8452,7 @@
           <t>有効</t>
         </is>
       </c>
+      <c r="O131" s="2" t="inlineStr"/>
     </row>
     <row r="132">
       <c r="A132" s="2" t="inlineStr">
@@ -8417,10 +8460,8 @@
           <t>A-20260131</t>
         </is>
       </c>
-      <c r="B132" s="2" t="inlineStr">
-        <is>
-          <t>2026/1/10</t>
-        </is>
+      <c r="B132" s="6" t="n">
+        <v>46032</v>
       </c>
       <c r="C132" s="2" t="inlineStr">
         <is>
@@ -8472,6 +8513,7 @@
           <t>有効</t>
         </is>
       </c>
+      <c r="O132" s="2" t="inlineStr"/>
     </row>
     <row r="133">
       <c r="A133" s="2" t="inlineStr">
@@ -8479,8 +8521,8 @@
           <t>A-20260132</t>
         </is>
       </c>
-      <c r="B133" s="2" t="n">
-        <v>20260108</v>
+      <c r="B133" s="6" t="n">
+        <v>46030</v>
       </c>
       <c r="C133" s="2" t="inlineStr">
         <is>
@@ -8532,6 +8574,7 @@
           <t>有効</t>
         </is>
       </c>
+      <c r="O133" s="2" t="inlineStr"/>
     </row>
     <row r="134">
       <c r="A134" s="2" t="inlineStr">
@@ -8539,7 +8582,7 @@
           <t>A-20260133</t>
         </is>
       </c>
-      <c r="B134" s="3" t="n">
+      <c r="B134" s="6" t="n">
         <v>46040</v>
       </c>
       <c r="C134" s="2" t="inlineStr">
@@ -8549,7 +8592,7 @@
       </c>
       <c r="D134" s="2" t="inlineStr">
         <is>
-          <t>ec</t>
+          <t>EC</t>
         </is>
       </c>
       <c r="E134" s="2" t="inlineStr">
@@ -8564,7 +8607,7 @@
       </c>
       <c r="G134" s="2" t="inlineStr">
         <is>
-          <t>コーヒー</t>
+          <t>コーヒー豆</t>
         </is>
       </c>
       <c r="H134" s="2" t="inlineStr">
@@ -8592,6 +8635,7 @@
           <t>有効</t>
         </is>
       </c>
+      <c r="O134" s="2" t="inlineStr"/>
     </row>
     <row r="135">
       <c r="A135" s="2" t="inlineStr">
@@ -8599,7 +8643,7 @@
           <t>A-20260134</t>
         </is>
       </c>
-      <c r="B135" s="3" t="n">
+      <c r="B135" s="6" t="n">
         <v>46044</v>
       </c>
       <c r="C135" s="2" t="inlineStr">
@@ -8609,7 +8653,7 @@
       </c>
       <c r="D135" s="2" t="inlineStr">
         <is>
-          <t>店舗</t>
+          <t>店頭</t>
         </is>
       </c>
       <c r="E135" s="2" t="inlineStr">
@@ -8624,7 +8668,7 @@
       </c>
       <c r="G135" s="2" t="inlineStr">
         <is>
-          <t>ギフト商品</t>
+          <t>ギフト</t>
         </is>
       </c>
       <c r="H135" s="2" t="inlineStr">
@@ -8652,6 +8696,7 @@
           <t>有効</t>
         </is>
       </c>
+      <c r="O135" s="2" t="inlineStr"/>
     </row>
     <row r="136">
       <c r="A136" s="2" t="inlineStr">
@@ -8659,12 +8704,12 @@
           <t>A-20260135</t>
         </is>
       </c>
-      <c r="B136" s="3" t="n">
+      <c r="B136" s="6" t="n">
         <v>46050</v>
       </c>
       <c r="C136" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">渋谷店 </t>
+          <t>渋谷店</t>
         </is>
       </c>
       <c r="D136" s="2" t="inlineStr">
@@ -8684,7 +8729,7 @@
       </c>
       <c r="G136" s="2" t="inlineStr">
         <is>
-          <t>抽出器具</t>
+          <t>器具</t>
         </is>
       </c>
       <c r="H136" s="2" t="inlineStr">
@@ -8712,6 +8757,7 @@
           <t>有効</t>
         </is>
       </c>
+      <c r="O136" s="2" t="inlineStr"/>
     </row>
     <row r="137">
       <c r="A137" s="2" t="inlineStr">
@@ -8719,10 +8765,8 @@
           <t>A-20260136</t>
         </is>
       </c>
-      <c r="B137" s="2" t="inlineStr">
-        <is>
-          <t>2026-01-11</t>
-        </is>
+      <c r="B137" s="6" t="n">
+        <v>46033</v>
       </c>
       <c r="C137" s="2" t="inlineStr">
         <is>
@@ -8741,7 +8785,7 @@
       </c>
       <c r="F137" s="2" t="inlineStr">
         <is>
-          <t>一般客</t>
+          <t>一般</t>
         </is>
       </c>
       <c r="G137" s="2" t="inlineStr">
@@ -8774,6 +8818,7 @@
           <t>有効</t>
         </is>
       </c>
+      <c r="O137" s="2" t="inlineStr"/>
     </row>
     <row r="138">
       <c r="A138" s="2" t="inlineStr">
@@ -8781,12 +8826,12 @@
           <t>A-20260137</t>
         </is>
       </c>
-      <c r="B138" s="3" t="n">
+      <c r="B138" s="6" t="n">
         <v>46040</v>
       </c>
       <c r="C138" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">横浜店 </t>
+          <t>横浜店</t>
         </is>
       </c>
       <c r="D138" s="2" t="inlineStr">
@@ -8817,10 +8862,8 @@
       <c r="I138" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="J138" s="2" t="inlineStr">
-        <is>
-          <t>1,600円</t>
-        </is>
+      <c r="J138" s="2" t="n">
+        <v>1600</v>
       </c>
       <c r="K138" s="2" t="n">
         <v>0</v>
@@ -8836,6 +8879,7 @@
           <t>有効</t>
         </is>
       </c>
+      <c r="O138" s="2" t="inlineStr"/>
     </row>
     <row r="139">
       <c r="A139" s="2" t="inlineStr">
@@ -8843,7 +8887,7 @@
           <t>A-20260138</t>
         </is>
       </c>
-      <c r="B139" s="3" t="n">
+      <c r="B139" s="6" t="n">
         <v>46041</v>
       </c>
       <c r="C139" s="2" t="inlineStr">
@@ -8892,6 +8936,7 @@
           <t>有効</t>
         </is>
       </c>
+      <c r="O139" s="2" t="inlineStr"/>
     </row>
     <row r="140">
       <c r="A140" s="2" t="inlineStr">
@@ -8899,7 +8944,7 @@
           <t>A-20260139</t>
         </is>
       </c>
-      <c r="B140" s="3" t="n">
+      <c r="B140" s="6" t="n">
         <v>46052</v>
       </c>
       <c r="C140" s="2" t="inlineStr">
@@ -8909,7 +8954,7 @@
       </c>
       <c r="D140" s="2" t="inlineStr">
         <is>
-          <t>Ｅ Ｃ</t>
+          <t>EC</t>
         </is>
       </c>
       <c r="E140" s="2" t="inlineStr">
@@ -8924,7 +8969,7 @@
       </c>
       <c r="G140" s="2" t="inlineStr">
         <is>
-          <t>ギフト商品</t>
+          <t>ギフト</t>
         </is>
       </c>
       <c r="H140" s="2" t="inlineStr">
@@ -8932,10 +8977,8 @@
           <t>ギフトセットB</t>
         </is>
       </c>
-      <c r="I140" s="2" t="inlineStr">
-        <is>
-          <t>２</t>
-        </is>
+      <c r="I140" s="2" t="n">
+        <v>2</v>
       </c>
       <c r="J140" s="2" t="n">
         <v>5800</v>
@@ -8954,6 +8997,7 @@
           <t>有効</t>
         </is>
       </c>
+      <c r="O140" s="2" t="inlineStr"/>
     </row>
     <row r="141">
       <c r="A141" s="2" t="inlineStr">
@@ -8961,14 +9005,12 @@
           <t>A-20260140</t>
         </is>
       </c>
-      <c r="B141" s="2" t="inlineStr">
-        <is>
-          <t>1月28日</t>
-        </is>
+      <c r="B141" s="6" t="n">
+        <v>46050</v>
       </c>
       <c r="C141" s="2" t="inlineStr">
         <is>
-          <t>新宿 店</t>
+          <t>新宿店</t>
         </is>
       </c>
       <c r="D141" s="2" t="inlineStr">
@@ -9016,6 +9058,7 @@
           <t>有効</t>
         </is>
       </c>
+      <c r="O141" s="2" t="inlineStr"/>
     </row>
     <row r="142">
       <c r="A142" s="2" t="inlineStr">
@@ -9023,17 +9066,17 @@
           <t>A-20260141</t>
         </is>
       </c>
-      <c r="B142" s="3" t="n">
+      <c r="B142" s="6" t="n">
         <v>46050</v>
       </c>
       <c r="C142" s="2" t="inlineStr">
         <is>
-          <t>ヨコハマ店</t>
+          <t>横浜店</t>
         </is>
       </c>
       <c r="D142" s="2" t="inlineStr">
         <is>
-          <t>Ｅ Ｃ</t>
+          <t>EC</t>
         </is>
       </c>
       <c r="E142" s="2" t="inlineStr">
@@ -9048,7 +9091,7 @@
       </c>
       <c r="G142" s="2" t="inlineStr">
         <is>
-          <t>ギフト商品</t>
+          <t>ギフト</t>
         </is>
       </c>
       <c r="H142" s="2" t="inlineStr">
@@ -9063,7 +9106,7 @@
         <v>5800</v>
       </c>
       <c r="K142" s="2" t="n">
-        <v>5</v>
+        <v>0.05</v>
       </c>
       <c r="L142" s="2" t="inlineStr">
         <is>
@@ -9076,6 +9119,7 @@
           <t>有効</t>
         </is>
       </c>
+      <c r="O142" s="2" t="inlineStr"/>
     </row>
     <row r="143">
       <c r="A143" s="2" t="inlineStr">
@@ -9083,7 +9127,7 @@
           <t>A-20260142</t>
         </is>
       </c>
-      <c r="B143" s="3" t="n">
+      <c r="B143" s="6" t="n">
         <v>46039</v>
       </c>
       <c r="C143" s="2" t="inlineStr">
@@ -9093,7 +9137,7 @@
       </c>
       <c r="D143" s="2" t="inlineStr">
         <is>
-          <t>ec</t>
+          <t>EC</t>
         </is>
       </c>
       <c r="E143" s="2" t="inlineStr">
@@ -9136,6 +9180,7 @@
           <t>有効</t>
         </is>
       </c>
+      <c r="O143" s="2" t="inlineStr"/>
     </row>
     <row r="144">
       <c r="A144" s="2" t="inlineStr">
@@ -9143,10 +9188,8 @@
           <t>A-20260143</t>
         </is>
       </c>
-      <c r="B144" s="2" t="inlineStr">
-        <is>
-          <t>2026/1/30</t>
-        </is>
+      <c r="B144" s="6" t="n">
+        <v>46052</v>
       </c>
       <c r="C144" s="2" t="inlineStr">
         <is>
@@ -9155,7 +9198,7 @@
       </c>
       <c r="D144" s="2" t="inlineStr">
         <is>
-          <t>店舗</t>
+          <t>店頭</t>
         </is>
       </c>
       <c r="E144" s="2" t="inlineStr">
@@ -9184,10 +9227,8 @@
       <c r="J144" s="2" t="n">
         <v>1200</v>
       </c>
-      <c r="K144" s="2" t="inlineStr">
-        <is>
-          <t>10%</t>
-        </is>
+      <c r="K144" s="2" t="n">
+        <v>0.1</v>
       </c>
       <c r="L144" s="2" t="inlineStr">
         <is>
@@ -9200,6 +9241,7 @@
           <t>有効</t>
         </is>
       </c>
+      <c r="O144" s="2" t="inlineStr"/>
     </row>
     <row r="145">
       <c r="A145" s="2" t="inlineStr">
@@ -9207,8 +9249,8 @@
           <t>A-20260144</t>
         </is>
       </c>
-      <c r="B145" s="2" t="n">
-        <v>20260101</v>
+      <c r="B145" s="6" t="n">
+        <v>46023</v>
       </c>
       <c r="C145" s="2" t="inlineStr">
         <is>
@@ -9260,6 +9302,7 @@
           <t>有効</t>
         </is>
       </c>
+      <c r="O145" s="2" t="inlineStr"/>
     </row>
     <row r="146">
       <c r="A146" s="2" t="inlineStr">
@@ -9267,12 +9310,12 @@
           <t>A-20260145</t>
         </is>
       </c>
-      <c r="B146" s="3" t="n">
+      <c r="B146" s="6" t="n">
         <v>46035</v>
       </c>
       <c r="C146" s="2" t="inlineStr">
         <is>
-          <t>名古屋 店</t>
+          <t>名古屋店</t>
         </is>
       </c>
       <c r="D146" s="2" t="inlineStr">
@@ -9320,6 +9363,7 @@
           <t>有効</t>
         </is>
       </c>
+      <c r="O146" s="2" t="inlineStr"/>
     </row>
     <row r="147">
       <c r="A147" s="2" t="inlineStr">
@@ -9327,17 +9371,17 @@
           <t>A-20260146</t>
         </is>
       </c>
-      <c r="B147" s="3" t="n">
+      <c r="B147" s="6" t="n">
         <v>46051</v>
       </c>
       <c r="C147" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">渋谷店 </t>
+          <t>渋谷店</t>
         </is>
       </c>
       <c r="D147" s="2" t="inlineStr">
         <is>
-          <t>店舗</t>
+          <t>店頭</t>
         </is>
       </c>
       <c r="E147" s="2" t="inlineStr">
@@ -9352,7 +9396,7 @@
       </c>
       <c r="G147" s="2" t="inlineStr">
         <is>
-          <t>抽出器具</t>
+          <t>器具</t>
         </is>
       </c>
       <c r="H147" s="2" t="inlineStr">
@@ -9363,10 +9407,8 @@
       <c r="I147" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="J147" s="2" t="inlineStr">
-        <is>
-          <t>¥3,200</t>
-        </is>
+      <c r="J147" s="2" t="n">
+        <v>3200</v>
       </c>
       <c r="K147" s="2" t="n">
         <v>0</v>
@@ -9382,6 +9424,7 @@
           <t>有効</t>
         </is>
       </c>
+      <c r="O147" s="2" t="inlineStr"/>
     </row>
     <row r="148">
       <c r="A148" s="2" t="inlineStr">
@@ -9389,12 +9432,12 @@
           <t>A-20260147</t>
         </is>
       </c>
-      <c r="B148" s="3" t="n">
+      <c r="B148" s="6" t="n">
         <v>46042</v>
       </c>
       <c r="C148" s="2" t="inlineStr">
         <is>
-          <t>ヨコハマ店</t>
+          <t>横浜店</t>
         </is>
       </c>
       <c r="D148" s="2" t="inlineStr">
@@ -9429,7 +9472,7 @@
         <v>1500</v>
       </c>
       <c r="K148" s="2" t="n">
-        <v>5</v>
+        <v>0.05</v>
       </c>
       <c r="L148" s="2" t="inlineStr">
         <is>
@@ -9442,6 +9485,7 @@
           <t>有効</t>
         </is>
       </c>
+      <c r="O148" s="2" t="inlineStr"/>
     </row>
     <row r="149">
       <c r="A149" s="2" t="inlineStr">
@@ -9449,14 +9493,12 @@
           <t>A-20260148</t>
         </is>
       </c>
-      <c r="B149" s="2" t="inlineStr">
-        <is>
-          <t>2026-01-12</t>
-        </is>
+      <c r="B149" s="6" t="n">
+        <v>46034</v>
       </c>
       <c r="C149" s="2" t="inlineStr">
         <is>
-          <t>渋谷　店</t>
+          <t>渋谷店</t>
         </is>
       </c>
       <c r="D149" s="2" t="inlineStr">
@@ -9472,7 +9514,7 @@
       <c r="F149" s="2" t="n"/>
       <c r="G149" s="2" t="inlineStr">
         <is>
-          <t>お菓子</t>
+          <t>菓子</t>
         </is>
       </c>
       <c r="H149" s="2" t="inlineStr">
@@ -9500,6 +9542,7 @@
           <t>有効</t>
         </is>
       </c>
+      <c r="O149" s="2" t="inlineStr"/>
     </row>
     <row r="150">
       <c r="A150" s="2" t="inlineStr">
@@ -9507,7 +9550,7 @@
           <t>A-20260149</t>
         </is>
       </c>
-      <c r="B150" s="3" t="n">
+      <c r="B150" s="6" t="n">
         <v>46050</v>
       </c>
       <c r="C150" s="2" t="inlineStr">
@@ -9517,7 +9560,7 @@
       </c>
       <c r="D150" s="2" t="inlineStr">
         <is>
-          <t>オフライン</t>
+          <t>店頭</t>
         </is>
       </c>
       <c r="E150" s="2" t="inlineStr">
@@ -9564,6 +9607,7 @@
           <t>無効</t>
         </is>
       </c>
+      <c r="O150" s="2" t="inlineStr"/>
     </row>
     <row r="151">
       <c r="A151" s="2" t="inlineStr">
@@ -9571,7 +9615,7 @@
           <t>A-20260150</t>
         </is>
       </c>
-      <c r="B151" s="3" t="n">
+      <c r="B151" s="6" t="n">
         <v>46040</v>
       </c>
       <c r="C151" s="2" t="inlineStr">
@@ -9581,7 +9625,7 @@
       </c>
       <c r="D151" s="2" t="inlineStr">
         <is>
-          <t>Web</t>
+          <t>EC</t>
         </is>
       </c>
       <c r="E151" s="2" t="inlineStr">
@@ -9596,7 +9640,7 @@
       </c>
       <c r="G151" s="2" t="inlineStr">
         <is>
-          <t>お菓子</t>
+          <t>菓子</t>
         </is>
       </c>
       <c r="H151" s="2" t="inlineStr">
@@ -9624,6 +9668,7 @@
           <t>有効</t>
         </is>
       </c>
+      <c r="O151" s="2" t="inlineStr"/>
     </row>
     <row r="152">
       <c r="A152" s="2" t="inlineStr">
@@ -9631,12 +9676,12 @@
           <t>A-20260151</t>
         </is>
       </c>
-      <c r="B152" s="3" t="n">
+      <c r="B152" s="6" t="n">
         <v>46048</v>
       </c>
       <c r="C152" s="2" t="inlineStr">
         <is>
-          <t>渋谷　店</t>
+          <t>渋谷店</t>
         </is>
       </c>
       <c r="D152" s="2" t="inlineStr">
@@ -9670,10 +9715,8 @@
       <c r="J152" s="2" t="n">
         <v>1400</v>
       </c>
-      <c r="K152" s="2" t="inlineStr">
-        <is>
-          <t>10%</t>
-        </is>
+      <c r="K152" s="2" t="n">
+        <v>0.1</v>
       </c>
       <c r="L152" s="2" t="inlineStr">
         <is>
@@ -9686,6 +9729,7 @@
           <t>有効</t>
         </is>
       </c>
+      <c r="O152" s="2" t="inlineStr"/>
     </row>
     <row r="153">
       <c r="A153" s="2" t="inlineStr">
@@ -9693,10 +9737,8 @@
           <t>A-20260152</t>
         </is>
       </c>
-      <c r="B153" s="2" t="inlineStr">
-        <is>
-          <t>1月29日</t>
-        </is>
+      <c r="B153" s="6" t="n">
+        <v>46051</v>
       </c>
       <c r="C153" s="2" t="inlineStr">
         <is>
@@ -9715,7 +9757,7 @@
       </c>
       <c r="F153" s="2" t="inlineStr">
         <is>
-          <t>メンバー</t>
+          <t>会員</t>
         </is>
       </c>
       <c r="G153" s="2" t="inlineStr">
@@ -9748,6 +9790,7 @@
           <t>有効</t>
         </is>
       </c>
+      <c r="O153" s="2" t="inlineStr"/>
     </row>
     <row r="154">
       <c r="A154" s="2" t="inlineStr">
@@ -9755,17 +9798,17 @@
           <t>A-20260153</t>
         </is>
       </c>
-      <c r="B154" s="3" t="n">
+      <c r="B154" s="6" t="n">
         <v>46051</v>
       </c>
       <c r="C154" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">渋谷店 </t>
+          <t>渋谷店</t>
         </is>
       </c>
       <c r="D154" s="2" t="inlineStr">
         <is>
-          <t>オンライン</t>
+          <t>EC</t>
         </is>
       </c>
       <c r="E154" s="2" t="inlineStr">
@@ -9775,12 +9818,12 @@
       </c>
       <c r="F154" s="2" t="inlineStr">
         <is>
-          <t>メンバー</t>
+          <t>会員</t>
         </is>
       </c>
       <c r="G154" s="2" t="inlineStr">
         <is>
-          <t>ギフト商品</t>
+          <t>ギフト</t>
         </is>
       </c>
       <c r="H154" s="2" t="inlineStr">
@@ -9808,6 +9851,7 @@
           <t>有効</t>
         </is>
       </c>
+      <c r="O154" s="2" t="inlineStr"/>
     </row>
     <row r="155">
       <c r="A155" s="2" t="inlineStr">
@@ -9815,7 +9859,7 @@
           <t>A-20260154</t>
         </is>
       </c>
-      <c r="B155" s="3" t="n">
+      <c r="B155" s="6" t="n">
         <v>46049</v>
       </c>
       <c r="C155" s="2" t="inlineStr">
@@ -9851,10 +9895,8 @@
       <c r="I155" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="J155" s="2" t="inlineStr">
-        <is>
-          <t>880円</t>
-        </is>
+      <c r="J155" s="2" t="n">
+        <v>880</v>
       </c>
       <c r="K155" s="2" t="n">
         <v>0.1</v>
@@ -9870,6 +9912,7 @@
           <t>有効</t>
         </is>
       </c>
+      <c r="O155" s="2" t="inlineStr"/>
     </row>
     <row r="156">
       <c r="A156" s="2" t="inlineStr">
@@ -9877,10 +9920,8 @@
           <t>A-20260155</t>
         </is>
       </c>
-      <c r="B156" s="2" t="inlineStr">
-        <is>
-          <t>2026/1/30</t>
-        </is>
+      <c r="B156" s="6" t="n">
+        <v>46052</v>
       </c>
       <c r="C156" s="2" t="inlineStr">
         <is>
@@ -9899,7 +9940,7 @@
       </c>
       <c r="F156" s="2" t="inlineStr">
         <is>
-          <t>一般客</t>
+          <t>一般</t>
         </is>
       </c>
       <c r="G156" s="2" t="inlineStr">
@@ -9932,6 +9973,7 @@
           <t>有効</t>
         </is>
       </c>
+      <c r="O156" s="2" t="inlineStr"/>
     </row>
     <row r="157">
       <c r="A157" s="2" t="inlineStr">
@@ -9939,12 +9981,12 @@
           <t>A-20260156</t>
         </is>
       </c>
-      <c r="B157" s="2" t="n">
-        <v>20260114</v>
+      <c r="B157" s="6" t="n">
+        <v>46036</v>
       </c>
       <c r="C157" s="2" t="inlineStr">
         <is>
-          <t>名古屋 店</t>
+          <t>名古屋店</t>
         </is>
       </c>
       <c r="D157" s="2" t="inlineStr">
@@ -9972,10 +10014,8 @@
           <t>ペーパーフィルター</t>
         </is>
       </c>
-      <c r="I157" s="2" t="inlineStr">
-        <is>
-          <t>4個</t>
-        </is>
+      <c r="I157" s="2" t="n">
+        <v>4</v>
       </c>
       <c r="J157" s="2" t="n">
         <v>480</v>
@@ -9994,6 +10034,7 @@
           <t>有効</t>
         </is>
       </c>
+      <c r="O157" s="2" t="inlineStr"/>
     </row>
     <row r="158">
       <c r="A158" s="2" t="inlineStr">
@@ -10001,12 +10042,12 @@
           <t>A-20260157</t>
         </is>
       </c>
-      <c r="B158" s="3" t="n">
+      <c r="B158" s="6" t="n">
         <v>46040</v>
       </c>
       <c r="C158" s="2" t="inlineStr">
         <is>
-          <t>シブヤ店</t>
+          <t>渋谷店</t>
         </is>
       </c>
       <c r="D158" s="2" t="inlineStr">
@@ -10021,7 +10062,7 @@
       </c>
       <c r="F158" s="2" t="inlineStr">
         <is>
-          <t>一般客</t>
+          <t>一般</t>
         </is>
       </c>
       <c r="G158" s="2" t="inlineStr">
@@ -10054,6 +10095,7 @@
           <t>有効</t>
         </is>
       </c>
+      <c r="O158" s="2" t="inlineStr"/>
     </row>
     <row r="159">
       <c r="A159" s="2" t="inlineStr">
@@ -10061,17 +10103,17 @@
           <t>A-20260158</t>
         </is>
       </c>
-      <c r="B159" s="3" t="n">
+      <c r="B159" s="6" t="n">
         <v>46034</v>
       </c>
       <c r="C159" s="2" t="inlineStr">
         <is>
-          <t>名古屋 店</t>
+          <t>名古屋店</t>
         </is>
       </c>
       <c r="D159" s="2" t="inlineStr">
         <is>
-          <t>Web</t>
+          <t>EC</t>
         </is>
       </c>
       <c r="E159" s="2" t="inlineStr">
@@ -10086,7 +10128,7 @@
       </c>
       <c r="G159" s="2" t="inlineStr">
         <is>
-          <t>コーヒー</t>
+          <t>コーヒー豆</t>
         </is>
       </c>
       <c r="H159" s="2" t="inlineStr">
@@ -10114,6 +10156,7 @@
           <t>有効</t>
         </is>
       </c>
+      <c r="O159" s="2" t="inlineStr"/>
     </row>
     <row r="160">
       <c r="A160" s="2" t="inlineStr">
@@ -10121,12 +10164,12 @@
           <t>A-20260159</t>
         </is>
       </c>
-      <c r="B160" s="3" t="n">
+      <c r="B160" s="6" t="n">
         <v>46040</v>
       </c>
       <c r="C160" s="2" t="inlineStr">
         <is>
-          <t>渋谷　店</t>
+          <t>渋谷店</t>
         </is>
       </c>
       <c r="D160" s="2" t="inlineStr">
@@ -10174,6 +10217,7 @@
           <t>有効</t>
         </is>
       </c>
+      <c r="O160" s="2" t="inlineStr"/>
     </row>
     <row r="161">
       <c r="A161" s="2" t="inlineStr">
@@ -10181,19 +10225,17 @@
           <t>A-20260160</t>
         </is>
       </c>
-      <c r="B161" s="2" t="inlineStr">
-        <is>
-          <t>2026-01-28</t>
-        </is>
+      <c r="B161" s="6" t="n">
+        <v>46050</v>
       </c>
       <c r="C161" s="2" t="inlineStr">
         <is>
-          <t>新宿 店</t>
+          <t>新宿店</t>
         </is>
       </c>
       <c r="D161" s="2" t="inlineStr">
         <is>
-          <t>オンライン</t>
+          <t>EC</t>
         </is>
       </c>
       <c r="E161" s="2" t="inlineStr">
@@ -10240,6 +10282,7 @@
           <t>無効</t>
         </is>
       </c>
+      <c r="O161" s="2" t="inlineStr"/>
     </row>
     <row r="162">
       <c r="A162" s="2" t="inlineStr">
@@ -10247,7 +10290,7 @@
           <t>A-20260161</t>
         </is>
       </c>
-      <c r="B162" s="3" t="n">
+      <c r="B162" s="6" t="n">
         <v>46033</v>
       </c>
       <c r="C162" s="2" t="inlineStr">
@@ -10296,6 +10339,7 @@
           <t>有効</t>
         </is>
       </c>
+      <c r="O162" s="2" t="inlineStr"/>
     </row>
     <row r="163">
       <c r="A163" s="2" t="inlineStr">
@@ -10303,7 +10347,7 @@
           <t>A-20260162</t>
         </is>
       </c>
-      <c r="B163" s="3" t="n">
+      <c r="B163" s="6" t="n">
         <v>46025</v>
       </c>
       <c r="C163" s="2" t="inlineStr">
@@ -10313,7 +10357,7 @@
       </c>
       <c r="D163" s="2" t="inlineStr">
         <is>
-          <t>店舗</t>
+          <t>店頭</t>
         </is>
       </c>
       <c r="E163" s="2" t="inlineStr">
@@ -10336,10 +10380,8 @@
           <t>ブレンド 200g</t>
         </is>
       </c>
-      <c r="I163" s="2" t="inlineStr">
-        <is>
-          <t>４</t>
-        </is>
+      <c r="I163" s="2" t="n">
+        <v>4</v>
       </c>
       <c r="J163" s="2" t="n">
         <v>1200</v>
@@ -10358,6 +10400,7 @@
           <t>有効</t>
         </is>
       </c>
+      <c r="O163" s="2" t="inlineStr"/>
     </row>
     <row r="164">
       <c r="A164" s="2" t="inlineStr">
@@ -10365,7 +10408,7 @@
           <t>A-20260163</t>
         </is>
       </c>
-      <c r="B164" s="3" t="n">
+      <c r="B164" s="6" t="n">
         <v>46030</v>
       </c>
       <c r="C164" s="2" t="inlineStr">
@@ -10385,7 +10428,7 @@
       </c>
       <c r="F164" s="2" t="inlineStr">
         <is>
-          <t>メンバー</t>
+          <t>会員</t>
         </is>
       </c>
       <c r="G164" s="2" t="inlineStr">
@@ -10418,6 +10461,7 @@
           <t>有効</t>
         </is>
       </c>
+      <c r="O164" s="2" t="inlineStr"/>
     </row>
     <row r="165">
       <c r="A165" s="2" t="inlineStr">
@@ -10425,10 +10469,8 @@
           <t>A-20260164</t>
         </is>
       </c>
-      <c r="B165" s="2" t="inlineStr">
-        <is>
-          <t>1月29日</t>
-        </is>
+      <c r="B165" s="6" t="n">
+        <v>46051</v>
       </c>
       <c r="C165" s="2" t="inlineStr">
         <is>
@@ -10437,7 +10479,7 @@
       </c>
       <c r="D165" s="2" t="inlineStr">
         <is>
-          <t>店舗</t>
+          <t>店頭</t>
         </is>
       </c>
       <c r="E165" s="2" t="inlineStr">
@@ -10480,6 +10522,7 @@
           <t>有効</t>
         </is>
       </c>
+      <c r="O165" s="2" t="inlineStr"/>
     </row>
     <row r="166">
       <c r="A166" s="2" t="inlineStr">
@@ -10487,7 +10530,7 @@
           <t>A-20260165</t>
         </is>
       </c>
-      <c r="B166" s="3" t="n">
+      <c r="B166" s="6" t="n">
         <v>46049</v>
       </c>
       <c r="C166" s="2" t="inlineStr">
@@ -10497,7 +10540,7 @@
       </c>
       <c r="D166" s="2" t="inlineStr">
         <is>
-          <t>店舗</t>
+          <t>店頭</t>
         </is>
       </c>
       <c r="E166" s="2" t="inlineStr">
@@ -10523,7 +10566,9 @@
       <c r="I166" s="2" t="n">
         <v>10</v>
       </c>
-      <c r="J166" s="2" t="n"/>
+      <c r="J166" s="7" t="n">
+        <v>1800</v>
+      </c>
       <c r="K166" s="2" t="n">
         <v>0</v>
       </c>
@@ -10538,6 +10583,11 @@
           <t>有効</t>
         </is>
       </c>
+      <c r="O166" s="2" t="inlineStr">
+        <is>
+          <t>補完</t>
+        </is>
+      </c>
     </row>
     <row r="167">
       <c r="A167" s="2" t="inlineStr">
@@ -10545,17 +10595,17 @@
           <t>A-20260166</t>
         </is>
       </c>
-      <c r="B167" s="3" t="n">
+      <c r="B167" s="6" t="n">
         <v>46031</v>
       </c>
       <c r="C167" s="2" t="inlineStr">
         <is>
-          <t>新宿 店</t>
+          <t>新宿店</t>
         </is>
       </c>
       <c r="D167" s="2" t="inlineStr">
         <is>
-          <t>店舗</t>
+          <t>店頭</t>
         </is>
       </c>
       <c r="E167" s="2" t="inlineStr">
@@ -10594,6 +10644,7 @@
           <t>有効</t>
         </is>
       </c>
+      <c r="O167" s="2" t="inlineStr"/>
     </row>
     <row r="168">
       <c r="A168" s="2" t="inlineStr">
@@ -10601,10 +10652,8 @@
           <t>A-20260167</t>
         </is>
       </c>
-      <c r="B168" s="2" t="inlineStr">
-        <is>
-          <t>2026/1/27</t>
-        </is>
+      <c r="B168" s="6" t="n">
+        <v>46049</v>
       </c>
       <c r="C168" s="2" t="inlineStr">
         <is>
@@ -10628,7 +10677,7 @@
       </c>
       <c r="G168" s="2" t="inlineStr">
         <is>
-          <t>抽出器具</t>
+          <t>器具</t>
         </is>
       </c>
       <c r="H168" s="2" t="inlineStr">
@@ -10656,6 +10705,7 @@
           <t>有効</t>
         </is>
       </c>
+      <c r="O168" s="2" t="inlineStr"/>
     </row>
     <row r="169">
       <c r="A169" s="2" t="inlineStr">
@@ -10663,8 +10713,8 @@
           <t>A-20260168</t>
         </is>
       </c>
-      <c r="B169" s="2" t="n">
-        <v>20260119</v>
+      <c r="B169" s="6" t="n">
+        <v>46041</v>
       </c>
       <c r="C169" s="2" t="inlineStr">
         <is>
@@ -10673,7 +10723,7 @@
       </c>
       <c r="D169" s="2" t="inlineStr">
         <is>
-          <t>店舗</t>
+          <t>店頭</t>
         </is>
       </c>
       <c r="E169" s="2" t="inlineStr">
@@ -10683,7 +10733,7 @@
       </c>
       <c r="F169" s="2" t="inlineStr">
         <is>
-          <t>メンバー</t>
+          <t>会員</t>
         </is>
       </c>
       <c r="G169" s="2" t="inlineStr">
@@ -10716,6 +10766,7 @@
           <t>有効</t>
         </is>
       </c>
+      <c r="O169" s="2" t="inlineStr"/>
     </row>
     <row r="170">
       <c r="A170" s="2" t="inlineStr">
@@ -10723,12 +10774,12 @@
           <t>A-20260169</t>
         </is>
       </c>
-      <c r="B170" s="3" t="n">
+      <c r="B170" s="6" t="n">
         <v>46029</v>
       </c>
       <c r="C170" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">渋谷店 </t>
+          <t>渋谷店</t>
         </is>
       </c>
       <c r="D170" s="2" t="inlineStr">
@@ -10772,6 +10823,7 @@
           <t>有効</t>
         </is>
       </c>
+      <c r="O170" s="2" t="inlineStr"/>
     </row>
     <row r="171">
       <c r="A171" s="2" t="inlineStr">
@@ -10779,7 +10831,7 @@
           <t>A-20260170</t>
         </is>
       </c>
-      <c r="B171" s="3" t="n">
+      <c r="B171" s="6" t="n">
         <v>46039</v>
       </c>
       <c r="C171" s="2" t="inlineStr">
@@ -10804,7 +10856,7 @@
       </c>
       <c r="G171" s="2" t="inlineStr">
         <is>
-          <t>コーヒー</t>
+          <t>コーヒー豆</t>
         </is>
       </c>
       <c r="H171" s="2" t="inlineStr">
@@ -10832,6 +10884,7 @@
           <t>有効</t>
         </is>
       </c>
+      <c r="O171" s="2" t="inlineStr"/>
     </row>
     <row r="172">
       <c r="A172" s="2" t="inlineStr">
@@ -10839,17 +10892,17 @@
           <t>A-20260171</t>
         </is>
       </c>
-      <c r="B172" s="3" t="n">
+      <c r="B172" s="6" t="n">
         <v>46042</v>
       </c>
       <c r="C172" s="2" t="inlineStr">
         <is>
-          <t>しんじゅく店</t>
+          <t>新宿店</t>
         </is>
       </c>
       <c r="D172" s="2" t="inlineStr">
         <is>
-          <t>Ｅ Ｃ</t>
+          <t>EC</t>
         </is>
       </c>
       <c r="E172" s="2" t="inlineStr">
@@ -10864,7 +10917,7 @@
       </c>
       <c r="G172" s="2" t="inlineStr">
         <is>
-          <t>お菓子</t>
+          <t>菓子</t>
         </is>
       </c>
       <c r="H172" s="2" t="inlineStr">
@@ -10875,10 +10928,8 @@
       <c r="I172" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="J172" s="2" t="inlineStr">
-        <is>
-          <t>1,500円</t>
-        </is>
+      <c r="J172" s="2" t="n">
+        <v>1500</v>
       </c>
       <c r="K172" s="2" t="n">
         <v>0</v>
@@ -10894,6 +10945,7 @@
           <t>有効</t>
         </is>
       </c>
+      <c r="O172" s="2" t="inlineStr"/>
     </row>
     <row r="173">
       <c r="A173" s="2" t="inlineStr">
@@ -10901,19 +10953,17 @@
           <t>A-20260172</t>
         </is>
       </c>
-      <c r="B173" s="2" t="inlineStr">
-        <is>
-          <t>2026-01-03</t>
-        </is>
+      <c r="B173" s="6" t="n">
+        <v>46025</v>
       </c>
       <c r="C173" s="2" t="inlineStr">
         <is>
-          <t>ヨコハマ店</t>
+          <t>横浜店</t>
         </is>
       </c>
       <c r="D173" s="2" t="inlineStr">
         <is>
-          <t>店舗</t>
+          <t>店頭</t>
         </is>
       </c>
       <c r="E173" s="2" t="inlineStr">
@@ -10923,12 +10973,12 @@
       </c>
       <c r="F173" s="2" t="inlineStr">
         <is>
-          <t>一般客</t>
+          <t>一般</t>
         </is>
       </c>
       <c r="G173" s="2" t="inlineStr">
         <is>
-          <t>珈琲豆</t>
+          <t>コーヒー豆</t>
         </is>
       </c>
       <c r="H173" s="2" t="inlineStr">
@@ -10956,6 +11006,7 @@
           <t>有効</t>
         </is>
       </c>
+      <c r="O173" s="2" t="inlineStr"/>
     </row>
     <row r="174">
       <c r="A174" s="2" t="inlineStr">
@@ -10963,7 +11014,7 @@
           <t>A-20260173</t>
         </is>
       </c>
-      <c r="B174" s="3" t="n">
+      <c r="B174" s="6" t="n">
         <v>46031</v>
       </c>
       <c r="C174" s="2" t="inlineStr">
@@ -10973,7 +11024,7 @@
       </c>
       <c r="D174" s="2" t="inlineStr">
         <is>
-          <t>店舗</t>
+          <t>店頭</t>
         </is>
       </c>
       <c r="E174" s="2" t="inlineStr">
@@ -10988,7 +11039,7 @@
       </c>
       <c r="G174" s="2" t="inlineStr">
         <is>
-          <t>ギフト商品</t>
+          <t>ギフト</t>
         </is>
       </c>
       <c r="H174" s="2" t="inlineStr">
@@ -11016,6 +11067,7 @@
           <t>有効</t>
         </is>
       </c>
+      <c r="O174" s="2" t="inlineStr"/>
     </row>
     <row r="175">
       <c r="A175" s="2" t="inlineStr">
@@ -11023,12 +11075,12 @@
           <t>A-20260174</t>
         </is>
       </c>
-      <c r="B175" s="3" t="n">
+      <c r="B175" s="6" t="n">
         <v>46033</v>
       </c>
       <c r="C175" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">横浜店 </t>
+          <t>横浜店</t>
         </is>
       </c>
       <c r="D175" s="2" t="inlineStr">
@@ -11048,7 +11100,7 @@
       </c>
       <c r="G175" s="2" t="inlineStr">
         <is>
-          <t>珈琲豆</t>
+          <t>コーヒー豆</t>
         </is>
       </c>
       <c r="H175" s="2" t="inlineStr">
@@ -11076,6 +11128,7 @@
           <t>有効</t>
         </is>
       </c>
+      <c r="O175" s="2" t="inlineStr"/>
     </row>
     <row r="176">
       <c r="A176" s="2" t="inlineStr">
@@ -11083,7 +11136,7 @@
           <t>A-20260175</t>
         </is>
       </c>
-      <c r="B176" s="3" t="n">
+      <c r="B176" s="6" t="n">
         <v>46043</v>
       </c>
       <c r="C176" s="2" t="inlineStr">
@@ -11093,7 +11146,7 @@
       </c>
       <c r="D176" s="2" t="inlineStr">
         <is>
-          <t>Ｅ Ｃ</t>
+          <t>EC</t>
         </is>
       </c>
       <c r="E176" s="2" t="inlineStr">
@@ -11119,10 +11172,8 @@
       <c r="I176" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="J176" s="2" t="inlineStr">
-        <is>
-          <t>¥1,600</t>
-        </is>
+      <c r="J176" s="2" t="n">
+        <v>1600</v>
       </c>
       <c r="K176" s="2" t="n">
         <v>0</v>
@@ -11138,6 +11189,7 @@
           <t>有効</t>
         </is>
       </c>
+      <c r="O176" s="2" t="inlineStr"/>
     </row>
     <row r="177">
       <c r="A177" s="2" t="inlineStr">
@@ -11145,14 +11197,12 @@
           <t>A-20260176</t>
         </is>
       </c>
-      <c r="B177" s="2" t="inlineStr">
-        <is>
-          <t>1月22日</t>
-        </is>
+      <c r="B177" s="6" t="n">
+        <v>46044</v>
       </c>
       <c r="C177" s="2" t="inlineStr">
         <is>
-          <t>しんじゅく店</t>
+          <t>新宿店</t>
         </is>
       </c>
       <c r="D177" s="2" t="inlineStr">
@@ -11196,6 +11246,7 @@
           <t>有効</t>
         </is>
       </c>
+      <c r="O177" s="2" t="inlineStr"/>
     </row>
     <row r="178">
       <c r="A178" s="2" t="inlineStr">
@@ -11203,17 +11254,17 @@
           <t>A-20260177</t>
         </is>
       </c>
-      <c r="B178" s="3" t="n">
+      <c r="B178" s="6" t="n">
         <v>46046</v>
       </c>
       <c r="C178" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">横浜店 </t>
+          <t>横浜店</t>
         </is>
       </c>
       <c r="D178" s="2" t="inlineStr">
         <is>
-          <t>Web</t>
+          <t>EC</t>
         </is>
       </c>
       <c r="E178" s="2" t="inlineStr">
@@ -11223,7 +11274,7 @@
       </c>
       <c r="F178" s="2" t="inlineStr">
         <is>
-          <t>メンバー</t>
+          <t>会員</t>
         </is>
       </c>
       <c r="G178" s="2" t="inlineStr">
@@ -11256,6 +11307,7 @@
           <t>有効</t>
         </is>
       </c>
+      <c r="O178" s="2" t="inlineStr"/>
     </row>
     <row r="179">
       <c r="A179" s="2" t="inlineStr">
@@ -11263,17 +11315,17 @@
           <t>A-20260178</t>
         </is>
       </c>
-      <c r="B179" s="3" t="n">
+      <c r="B179" s="6" t="n">
         <v>46053</v>
       </c>
       <c r="C179" s="2" t="inlineStr">
         <is>
-          <t>渋谷　店</t>
+          <t>渋谷店</t>
         </is>
       </c>
       <c r="D179" s="2" t="inlineStr">
         <is>
-          <t>店舗</t>
+          <t>店頭</t>
         </is>
       </c>
       <c r="E179" s="2" t="inlineStr">
@@ -11283,7 +11335,7 @@
       </c>
       <c r="F179" s="2" t="inlineStr">
         <is>
-          <t>一般客</t>
+          <t>一般</t>
         </is>
       </c>
       <c r="G179" s="2" t="inlineStr">
@@ -11316,6 +11368,7 @@
           <t>有効</t>
         </is>
       </c>
+      <c r="O179" s="2" t="inlineStr"/>
     </row>
     <row r="180">
       <c r="A180" s="2" t="inlineStr">
@@ -11323,10 +11376,8 @@
           <t>A-20260179</t>
         </is>
       </c>
-      <c r="B180" s="2" t="inlineStr">
-        <is>
-          <t>2026/1/3</t>
-        </is>
+      <c r="B180" s="6" t="n">
+        <v>46025</v>
       </c>
       <c r="C180" s="2" t="inlineStr">
         <is>
@@ -11345,12 +11396,12 @@
       </c>
       <c r="F180" s="2" t="inlineStr">
         <is>
-          <t>一般客</t>
+          <t>一般</t>
         </is>
       </c>
       <c r="G180" s="2" t="inlineStr">
         <is>
-          <t>ギフト商品</t>
+          <t>ギフト</t>
         </is>
       </c>
       <c r="H180" s="2" t="inlineStr">
@@ -11378,6 +11429,7 @@
           <t>有効</t>
         </is>
       </c>
+      <c r="O180" s="2" t="inlineStr"/>
     </row>
     <row r="181">
       <c r="A181" s="2" t="inlineStr">
@@ -11385,8 +11437,8 @@
           <t>A-20260180</t>
         </is>
       </c>
-      <c r="B181" s="2" t="n">
-        <v>20260124</v>
+      <c r="B181" s="6" t="n">
+        <v>46046</v>
       </c>
       <c r="C181" s="2" t="inlineStr">
         <is>
@@ -11410,7 +11462,7 @@
       </c>
       <c r="G181" s="2" t="inlineStr">
         <is>
-          <t>抽出器具</t>
+          <t>器具</t>
         </is>
       </c>
       <c r="H181" s="2" t="inlineStr">
@@ -11438,6 +11490,7 @@
           <t>有効</t>
         </is>
       </c>
+      <c r="O181" s="2" t="inlineStr"/>
     </row>
     <row r="182">
       <c r="A182" s="2" t="inlineStr">
@@ -11445,7 +11498,7 @@
           <t>A-20260181</t>
         </is>
       </c>
-      <c r="B182" s="3" t="n">
+      <c r="B182" s="6" t="n">
         <v>46025</v>
       </c>
       <c r="C182" s="2" t="inlineStr">
@@ -11455,7 +11508,7 @@
       </c>
       <c r="D182" s="2" t="inlineStr">
         <is>
-          <t>オフライン</t>
+          <t>店頭</t>
         </is>
       </c>
       <c r="E182" s="2" t="inlineStr">
@@ -11465,7 +11518,7 @@
       </c>
       <c r="F182" s="2" t="inlineStr">
         <is>
-          <t>メンバー</t>
+          <t>会員</t>
         </is>
       </c>
       <c r="G182" s="2" t="inlineStr">
@@ -11498,6 +11551,7 @@
           <t>有効</t>
         </is>
       </c>
+      <c r="O182" s="2" t="inlineStr"/>
     </row>
     <row r="183">
       <c r="A183" s="2" t="inlineStr">
@@ -11505,7 +11559,7 @@
           <t>A-20260182</t>
         </is>
       </c>
-      <c r="B183" s="3" t="n">
+      <c r="B183" s="6" t="n">
         <v>46040</v>
       </c>
       <c r="C183" s="2" t="inlineStr">
@@ -11558,6 +11612,7 @@
           <t>有効</t>
         </is>
       </c>
+      <c r="O183" s="2" t="inlineStr"/>
     </row>
     <row r="184">
       <c r="A184" s="2" t="inlineStr">
@@ -11565,12 +11620,12 @@
           <t>A-20260183</t>
         </is>
       </c>
-      <c r="B184" s="3" t="n">
+      <c r="B184" s="6" t="n">
         <v>46027</v>
       </c>
       <c r="C184" s="2" t="inlineStr">
         <is>
-          <t>名古屋 店</t>
+          <t>名古屋店</t>
         </is>
       </c>
       <c r="D184" s="2" t="inlineStr">
@@ -11585,7 +11640,7 @@
       </c>
       <c r="F184" s="2" t="inlineStr">
         <is>
-          <t>一般客</t>
+          <t>一般</t>
         </is>
       </c>
       <c r="G184" s="2" t="inlineStr">
@@ -11604,10 +11659,8 @@
       <c r="J184" s="2" t="n">
         <v>1800</v>
       </c>
-      <c r="K184" s="2" t="inlineStr">
-        <is>
-          <t>10%</t>
-        </is>
+      <c r="K184" s="2" t="n">
+        <v>0.1</v>
       </c>
       <c r="L184" s="2" t="inlineStr">
         <is>
@@ -11620,6 +11673,7 @@
           <t>有効</t>
         </is>
       </c>
+      <c r="O184" s="2" t="inlineStr"/>
     </row>
     <row r="185">
       <c r="A185" s="2" t="inlineStr">
@@ -11627,19 +11681,17 @@
           <t>A-20260184</t>
         </is>
       </c>
-      <c r="B185" s="2" t="inlineStr">
-        <is>
-          <t>2026-01-16</t>
-        </is>
+      <c r="B185" s="6" t="n">
+        <v>46038</v>
       </c>
       <c r="C185" s="2" t="inlineStr">
         <is>
-          <t>しんじゅく店</t>
+          <t>新宿店</t>
         </is>
       </c>
       <c r="D185" s="2" t="inlineStr">
         <is>
-          <t>オンライン</t>
+          <t>EC</t>
         </is>
       </c>
       <c r="E185" s="2" t="inlineStr">
@@ -11686,6 +11738,7 @@
           <t>有効</t>
         </is>
       </c>
+      <c r="O185" s="2" t="inlineStr"/>
     </row>
     <row r="186">
       <c r="A186" s="2" t="inlineStr">
@@ -11693,17 +11746,17 @@
           <t>A-20260185</t>
         </is>
       </c>
-      <c r="B186" s="3" t="n">
+      <c r="B186" s="6" t="n">
         <v>46029</v>
       </c>
       <c r="C186" s="2" t="inlineStr">
         <is>
-          <t>名古屋 店</t>
+          <t>名古屋店</t>
         </is>
       </c>
       <c r="D186" s="2" t="inlineStr">
         <is>
-          <t>店舗</t>
+          <t>店頭</t>
         </is>
       </c>
       <c r="E186" s="2" t="inlineStr">
@@ -11726,10 +11779,8 @@
           <t>深煎りブレンド 500g</t>
         </is>
       </c>
-      <c r="I186" s="2" t="inlineStr">
-        <is>
-          <t>１</t>
-        </is>
+      <c r="I186" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="J186" s="2" t="n">
         <v>2600</v>
@@ -11748,6 +11799,7 @@
           <t>有効</t>
         </is>
       </c>
+      <c r="O186" s="2" t="inlineStr"/>
     </row>
     <row r="187">
       <c r="A187" s="2" t="inlineStr">
@@ -11755,7 +11807,7 @@
           <t>A-20260186</t>
         </is>
       </c>
-      <c r="B187" s="3" t="n">
+      <c r="B187" s="6" t="n">
         <v>46050</v>
       </c>
       <c r="C187" s="2" t="inlineStr">
@@ -11765,7 +11817,7 @@
       </c>
       <c r="D187" s="2" t="inlineStr">
         <is>
-          <t>ec</t>
+          <t>EC</t>
         </is>
       </c>
       <c r="E187" s="2" t="inlineStr">
@@ -11808,6 +11860,7 @@
           <t>無効</t>
         </is>
       </c>
+      <c r="O187" s="2" t="inlineStr"/>
     </row>
     <row r="188">
       <c r="A188" s="2" t="inlineStr">
@@ -11815,7 +11868,7 @@
           <t>A-20260187</t>
         </is>
       </c>
-      <c r="B188" s="3" t="n">
+      <c r="B188" s="6" t="n">
         <v>46035</v>
       </c>
       <c r="C188" s="2" t="inlineStr">
@@ -11825,7 +11878,7 @@
       </c>
       <c r="D188" s="2" t="inlineStr">
         <is>
-          <t>Web</t>
+          <t>EC</t>
         </is>
       </c>
       <c r="E188" s="2" t="inlineStr">
@@ -11836,7 +11889,7 @@
       <c r="F188" s="2" t="n"/>
       <c r="G188" s="2" t="inlineStr">
         <is>
-          <t>コーヒー</t>
+          <t>コーヒー豆</t>
         </is>
       </c>
       <c r="H188" s="2" t="inlineStr">
@@ -11844,10 +11897,8 @@
           <t>モカ 200g</t>
         </is>
       </c>
-      <c r="I188" s="2" t="inlineStr">
-        <is>
-          <t>1個</t>
-        </is>
+      <c r="I188" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="J188" s="2" t="n">
         <v>1400</v>
@@ -11866,6 +11917,7 @@
           <t>有効</t>
         </is>
       </c>
+      <c r="O188" s="2" t="inlineStr"/>
     </row>
     <row r="189">
       <c r="A189" s="2" t="inlineStr">
@@ -11873,10 +11925,8 @@
           <t>A-20260188</t>
         </is>
       </c>
-      <c r="B189" s="2" t="inlineStr">
-        <is>
-          <t>1月29日</t>
-        </is>
+      <c r="B189" s="6" t="n">
+        <v>46051</v>
       </c>
       <c r="C189" s="2" t="inlineStr">
         <is>
@@ -11911,15 +11961,11 @@
       <c r="I189" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="J189" s="2" t="inlineStr">
-        <is>
-          <t>980円</t>
-        </is>
-      </c>
-      <c r="K189" s="2" t="inlineStr">
-        <is>
-          <t>10%</t>
-        </is>
+      <c r="J189" s="2" t="n">
+        <v>980</v>
+      </c>
+      <c r="K189" s="2" t="n">
+        <v>0.1</v>
       </c>
       <c r="L189" s="2" t="inlineStr">
         <is>
@@ -11932,6 +11978,7 @@
           <t>有効</t>
         </is>
       </c>
+      <c r="O189" s="2" t="inlineStr"/>
     </row>
     <row r="190">
       <c r="A190" s="2" t="inlineStr">
@@ -11939,7 +11986,7 @@
           <t>A-20260189</t>
         </is>
       </c>
-      <c r="B190" s="3" t="n">
+      <c r="B190" s="6" t="n">
         <v>46052</v>
       </c>
       <c r="C190" s="2" t="inlineStr">
@@ -11949,7 +11996,7 @@
       </c>
       <c r="D190" s="2" t="inlineStr">
         <is>
-          <t>店舗</t>
+          <t>店頭</t>
         </is>
       </c>
       <c r="E190" s="2" t="inlineStr">
@@ -11992,6 +12039,7 @@
           <t>有効</t>
         </is>
       </c>
+      <c r="O190" s="2" t="inlineStr"/>
     </row>
     <row r="191">
       <c r="A191" s="2" t="inlineStr">
@@ -11999,7 +12047,7 @@
           <t>A-20260190</t>
         </is>
       </c>
-      <c r="B191" s="3" t="n">
+      <c r="B191" s="6" t="n">
         <v>46047</v>
       </c>
       <c r="C191" s="2" t="inlineStr">
@@ -12009,7 +12057,7 @@
       </c>
       <c r="D191" s="2" t="inlineStr">
         <is>
-          <t>オフライン</t>
+          <t>店頭</t>
         </is>
       </c>
       <c r="E191" s="2" t="inlineStr">
@@ -12052,6 +12100,7 @@
           <t>有効</t>
         </is>
       </c>
+      <c r="O191" s="2" t="inlineStr"/>
     </row>
     <row r="192">
       <c r="A192" s="2" t="inlineStr">
@@ -12059,19 +12108,17 @@
           <t>A-20260191</t>
         </is>
       </c>
-      <c r="B192" s="2" t="inlineStr">
-        <is>
-          <t>2026/1/10</t>
-        </is>
+      <c r="B192" s="6" t="n">
+        <v>46032</v>
       </c>
       <c r="C192" s="2" t="inlineStr">
         <is>
-          <t>しんじゅく店</t>
+          <t>新宿店</t>
         </is>
       </c>
       <c r="D192" s="2" t="inlineStr">
         <is>
-          <t>オンライン</t>
+          <t>EC</t>
         </is>
       </c>
       <c r="E192" s="2" t="inlineStr">
@@ -12081,7 +12128,7 @@
       </c>
       <c r="F192" s="2" t="inlineStr">
         <is>
-          <t>メンバー</t>
+          <t>会員</t>
         </is>
       </c>
       <c r="G192" s="2" t="inlineStr">
@@ -12114,6 +12161,7 @@
           <t>有効</t>
         </is>
       </c>
+      <c r="O192" s="2" t="inlineStr"/>
     </row>
     <row r="193">
       <c r="A193" s="2" t="inlineStr">
@@ -12121,17 +12169,17 @@
           <t>A-20260192</t>
         </is>
       </c>
-      <c r="B193" s="2" t="n">
-        <v>20260111</v>
+      <c r="B193" s="6" t="n">
+        <v>46033</v>
       </c>
       <c r="C193" s="2" t="inlineStr">
         <is>
-          <t>新宿 店</t>
+          <t>新宿店</t>
         </is>
       </c>
       <c r="D193" s="2" t="inlineStr">
         <is>
-          <t>オンライン</t>
+          <t>EC</t>
         </is>
       </c>
       <c r="E193" s="2" t="inlineStr">
@@ -12141,7 +12189,7 @@
       </c>
       <c r="F193" s="2" t="inlineStr">
         <is>
-          <t>一般客</t>
+          <t>一般</t>
         </is>
       </c>
       <c r="G193" s="2" t="inlineStr">
@@ -12174,6 +12222,7 @@
           <t>有効</t>
         </is>
       </c>
+      <c r="O193" s="2" t="inlineStr"/>
     </row>
     <row r="194">
       <c r="A194" s="2" t="inlineStr">
@@ -12181,7 +12230,7 @@
           <t>A-20260193</t>
         </is>
       </c>
-      <c r="B194" s="3" t="n">
+      <c r="B194" s="6" t="n">
         <v>46044</v>
       </c>
       <c r="C194" s="2" t="inlineStr">
@@ -12191,7 +12240,7 @@
       </c>
       <c r="D194" s="2" t="inlineStr">
         <is>
-          <t>店舗</t>
+          <t>店頭</t>
         </is>
       </c>
       <c r="E194" s="2" t="inlineStr">
@@ -12234,6 +12283,7 @@
           <t>有効</t>
         </is>
       </c>
+      <c r="O194" s="2" t="inlineStr"/>
     </row>
     <row r="195">
       <c r="A195" s="2" t="inlineStr">
@@ -12241,17 +12291,17 @@
           <t>A-20260194</t>
         </is>
       </c>
-      <c r="B195" s="3" t="n">
+      <c r="B195" s="6" t="n">
         <v>46036</v>
       </c>
       <c r="C195" s="2" t="inlineStr">
         <is>
-          <t>フクオカ店</t>
+          <t>福岡店</t>
         </is>
       </c>
       <c r="D195" s="2" t="inlineStr">
         <is>
-          <t>店舗</t>
+          <t>店頭</t>
         </is>
       </c>
       <c r="E195" s="2" t="inlineStr">
@@ -12261,7 +12311,7 @@
       </c>
       <c r="F195" s="2" t="inlineStr">
         <is>
-          <t>一般客</t>
+          <t>一般</t>
         </is>
       </c>
       <c r="G195" s="2" t="inlineStr">
@@ -12294,6 +12344,7 @@
           <t>有効</t>
         </is>
       </c>
+      <c r="O195" s="2" t="inlineStr"/>
     </row>
     <row r="196">
       <c r="A196" s="2" t="inlineStr">
@@ -12301,7 +12352,7 @@
           <t>A-20260195</t>
         </is>
       </c>
-      <c r="B196" s="3" t="n">
+      <c r="B196" s="6" t="n">
         <v>46033</v>
       </c>
       <c r="C196" s="2" t="inlineStr">
@@ -12311,7 +12362,7 @@
       </c>
       <c r="D196" s="2" t="inlineStr">
         <is>
-          <t>Web</t>
+          <t>EC</t>
         </is>
       </c>
       <c r="E196" s="2" t="inlineStr">
@@ -12326,7 +12377,7 @@
       </c>
       <c r="G196" s="2" t="inlineStr">
         <is>
-          <t>抽出器具</t>
+          <t>器具</t>
         </is>
       </c>
       <c r="H196" s="2" t="inlineStr">
@@ -12354,6 +12405,7 @@
           <t>有効</t>
         </is>
       </c>
+      <c r="O196" s="2" t="inlineStr"/>
     </row>
     <row r="197">
       <c r="A197" s="2" t="inlineStr">
@@ -12361,14 +12413,12 @@
           <t>A-20260196</t>
         </is>
       </c>
-      <c r="B197" s="2" t="inlineStr">
-        <is>
-          <t>2026-01-10</t>
-        </is>
+      <c r="B197" s="6" t="n">
+        <v>46032</v>
       </c>
       <c r="C197" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">横浜店 </t>
+          <t>横浜店</t>
         </is>
       </c>
       <c r="D197" s="2" t="inlineStr">
@@ -12383,7 +12433,7 @@
       </c>
       <c r="F197" s="2" t="inlineStr">
         <is>
-          <t>法人顧客</t>
+          <t>法人</t>
         </is>
       </c>
       <c r="G197" s="2" t="inlineStr">
@@ -12416,6 +12466,7 @@
           <t>有効</t>
         </is>
       </c>
+      <c r="O197" s="2" t="inlineStr"/>
     </row>
     <row r="198">
       <c r="A198" s="2" t="inlineStr">
@@ -12423,12 +12474,12 @@
           <t>A-20260197</t>
         </is>
       </c>
-      <c r="B198" s="3" t="n">
+      <c r="B198" s="6" t="n">
         <v>46052</v>
       </c>
       <c r="C198" s="2" t="inlineStr">
         <is>
-          <t>シブヤ店</t>
+          <t>渋谷店</t>
         </is>
       </c>
       <c r="D198" s="2" t="inlineStr">
@@ -12443,12 +12494,12 @@
       </c>
       <c r="F198" s="2" t="inlineStr">
         <is>
-          <t>法人顧客</t>
+          <t>法人</t>
         </is>
       </c>
       <c r="G198" s="2" t="inlineStr">
         <is>
-          <t>珈琲豆</t>
+          <t>コーヒー豆</t>
         </is>
       </c>
       <c r="H198" s="2" t="inlineStr">
@@ -12476,6 +12527,7 @@
           <t>有効</t>
         </is>
       </c>
+      <c r="O198" s="2" t="inlineStr"/>
     </row>
     <row r="199">
       <c r="A199" s="2" t="inlineStr">
@@ -12483,7 +12535,7 @@
           <t>A-20260198</t>
         </is>
       </c>
-      <c r="B199" s="3" t="n">
+      <c r="B199" s="6" t="n">
         <v>46030</v>
       </c>
       <c r="C199" s="2" t="inlineStr">
@@ -12532,6 +12584,7 @@
           <t>有効</t>
         </is>
       </c>
+      <c r="O199" s="2" t="inlineStr"/>
     </row>
     <row r="200">
       <c r="A200" s="2" t="inlineStr">
@@ -12539,12 +12592,12 @@
           <t>A-20260199</t>
         </is>
       </c>
-      <c r="B200" s="3" t="n">
+      <c r="B200" s="6" t="n">
         <v>46037</v>
       </c>
       <c r="C200" s="2" t="inlineStr">
         <is>
-          <t>名古屋 店</t>
+          <t>名古屋店</t>
         </is>
       </c>
       <c r="D200" s="2" t="inlineStr">
@@ -12592,6 +12645,7 @@
           <t>有効</t>
         </is>
       </c>
+      <c r="O200" s="2" t="inlineStr"/>
     </row>
     <row r="201">
       <c r="A201" s="2" t="inlineStr">
@@ -12599,10 +12653,8 @@
           <t>A-20260200</t>
         </is>
       </c>
-      <c r="B201" s="2" t="inlineStr">
-        <is>
-          <t>1月8日</t>
-        </is>
+      <c r="B201" s="6" t="n">
+        <v>46030</v>
       </c>
       <c r="C201" s="2" t="inlineStr">
         <is>
@@ -12611,7 +12663,7 @@
       </c>
       <c r="D201" s="2" t="inlineStr">
         <is>
-          <t>店舗</t>
+          <t>店頭</t>
         </is>
       </c>
       <c r="E201" s="2" t="inlineStr">
@@ -12622,7 +12674,7 @@
       <c r="F201" s="2" t="n"/>
       <c r="G201" s="2" t="inlineStr">
         <is>
-          <t>ギフト商品</t>
+          <t>ギフト</t>
         </is>
       </c>
       <c r="H201" s="2" t="inlineStr">
@@ -12636,10 +12688,8 @@
       <c r="J201" s="2" t="n">
         <v>5800</v>
       </c>
-      <c r="K201" s="2" t="inlineStr">
-        <is>
-          <t>10%</t>
-        </is>
+      <c r="K201" s="2" t="n">
+        <v>0.1</v>
       </c>
       <c r="L201" s="2" t="inlineStr">
         <is>
@@ -12652,6 +12702,7 @@
           <t>有効</t>
         </is>
       </c>
+      <c r="O201" s="2" t="inlineStr"/>
     </row>
     <row r="202">
       <c r="A202" s="2" t="inlineStr">
@@ -12659,17 +12710,17 @@
           <t>A-20260201</t>
         </is>
       </c>
-      <c r="B202" s="3" t="n">
+      <c r="B202" s="6" t="n">
         <v>46050</v>
       </c>
       <c r="C202" s="2" t="inlineStr">
         <is>
-          <t>新宿 店</t>
+          <t>新宿店</t>
         </is>
       </c>
       <c r="D202" s="2" t="inlineStr">
         <is>
-          <t>店舗</t>
+          <t>店頭</t>
         </is>
       </c>
       <c r="E202" s="2" t="inlineStr">
@@ -12712,6 +12763,7 @@
           <t>有効</t>
         </is>
       </c>
+      <c r="O202" s="2" t="inlineStr"/>
     </row>
     <row r="203">
       <c r="A203" s="2" t="inlineStr">
@@ -12719,7 +12771,7 @@
           <t>A-20260202</t>
         </is>
       </c>
-      <c r="B203" s="3" t="n">
+      <c r="B203" s="6" t="n">
         <v>46024</v>
       </c>
       <c r="C203" s="2" t="inlineStr">
@@ -12739,7 +12791,7 @@
       </c>
       <c r="F203" s="2" t="inlineStr">
         <is>
-          <t>一般客</t>
+          <t>一般</t>
         </is>
       </c>
       <c r="G203" s="2" t="inlineStr">
@@ -12772,6 +12824,7 @@
           <t>有効</t>
         </is>
       </c>
+      <c r="O203" s="2" t="inlineStr"/>
     </row>
     <row r="204">
       <c r="A204" s="2" t="inlineStr">
@@ -12779,10 +12832,8 @@
           <t>A-20260203</t>
         </is>
       </c>
-      <c r="B204" s="2" t="inlineStr">
-        <is>
-          <t>2026/1/22</t>
-        </is>
+      <c r="B204" s="6" t="n">
+        <v>46044</v>
       </c>
       <c r="C204" s="2" t="inlineStr">
         <is>
@@ -12834,6 +12885,7 @@
           <t>有効</t>
         </is>
       </c>
+      <c r="O204" s="2" t="inlineStr"/>
     </row>
     <row r="205">
       <c r="A205" s="2" t="inlineStr">
@@ -12841,8 +12893,8 @@
           <t>A-20260204</t>
         </is>
       </c>
-      <c r="B205" s="2" t="n">
-        <v>20260102</v>
+      <c r="B205" s="6" t="n">
+        <v>46024</v>
       </c>
       <c r="C205" s="2" t="inlineStr">
         <is>
@@ -12851,7 +12903,7 @@
       </c>
       <c r="D205" s="2" t="inlineStr">
         <is>
-          <t>Ｅ Ｃ</t>
+          <t>EC</t>
         </is>
       </c>
       <c r="E205" s="2" t="inlineStr">
@@ -12877,10 +12929,8 @@
       <c r="I205" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="J205" s="2" t="inlineStr">
-        <is>
-          <t>¥3,200</t>
-        </is>
+      <c r="J205" s="2" t="n">
+        <v>3200</v>
       </c>
       <c r="K205" s="2" t="n">
         <v>0.05</v>
@@ -12896,6 +12946,7 @@
           <t>有効</t>
         </is>
       </c>
+      <c r="O205" s="2" t="inlineStr"/>
     </row>
     <row r="206">
       <c r="A206" s="2" t="inlineStr">
@@ -12903,7 +12954,7 @@
           <t>A-20260205</t>
         </is>
       </c>
-      <c r="B206" s="3" t="n">
+      <c r="B206" s="6" t="n">
         <v>46046</v>
       </c>
       <c r="C206" s="2" t="inlineStr">
@@ -12939,10 +12990,8 @@
       <c r="I206" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="J206" s="2" t="inlineStr">
-        <is>
-          <t>5,800円</t>
-        </is>
+      <c r="J206" s="2" t="n">
+        <v>5800</v>
       </c>
       <c r="K206" s="2" t="n">
         <v>0.1</v>
@@ -12958,6 +13007,7 @@
           <t>有効</t>
         </is>
       </c>
+      <c r="O206" s="2" t="inlineStr"/>
     </row>
     <row r="207">
       <c r="A207" s="2" t="inlineStr">
@@ -12965,7 +13015,7 @@
           <t>A-20260206</t>
         </is>
       </c>
-      <c r="B207" s="3" t="n">
+      <c r="B207" s="6" t="n">
         <v>46036</v>
       </c>
       <c r="C207" s="2" t="inlineStr">
@@ -12975,7 +13025,7 @@
       </c>
       <c r="D207" s="2" t="inlineStr">
         <is>
-          <t>店舗</t>
+          <t>店頭</t>
         </is>
       </c>
       <c r="E207" s="2" t="inlineStr">
@@ -13001,7 +13051,9 @@
       <c r="I207" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="J207" s="2" t="n"/>
+      <c r="J207" s="7" t="n">
+        <v>2800</v>
+      </c>
       <c r="K207" s="2" t="n">
         <v>0.05</v>
       </c>
@@ -13016,6 +13068,11 @@
           <t>有効</t>
         </is>
       </c>
+      <c r="O207" s="2" t="inlineStr">
+        <is>
+          <t>補完</t>
+        </is>
+      </c>
     </row>
     <row r="208">
       <c r="A208" s="2" t="inlineStr">
@@ -13023,17 +13080,17 @@
           <t>A-20260207</t>
         </is>
       </c>
-      <c r="B208" s="3" t="n">
+      <c r="B208" s="6" t="n">
         <v>46036</v>
       </c>
       <c r="C208" s="2" t="inlineStr">
         <is>
-          <t>フクオカ店</t>
+          <t>福岡店</t>
         </is>
       </c>
       <c r="D208" s="2" t="inlineStr">
         <is>
-          <t>Ｅ Ｃ</t>
+          <t>EC</t>
         </is>
       </c>
       <c r="E208" s="2" t="inlineStr">
@@ -13048,7 +13105,7 @@
       </c>
       <c r="G208" s="2" t="inlineStr">
         <is>
-          <t>ギフト商品</t>
+          <t>ギフト</t>
         </is>
       </c>
       <c r="H208" s="2" t="inlineStr">
@@ -13076,6 +13133,7 @@
           <t>有効</t>
         </is>
       </c>
+      <c r="O208" s="2" t="inlineStr"/>
     </row>
     <row r="209">
       <c r="A209" s="2" t="inlineStr">
@@ -13083,19 +13141,17 @@
           <t>A-20260208</t>
         </is>
       </c>
-      <c r="B209" s="2" t="inlineStr">
-        <is>
-          <t>2026-01-03</t>
-        </is>
+      <c r="B209" s="6" t="n">
+        <v>46025</v>
       </c>
       <c r="C209" s="2" t="inlineStr">
         <is>
-          <t>フクオカ店</t>
+          <t>福岡店</t>
         </is>
       </c>
       <c r="D209" s="2" t="inlineStr">
         <is>
-          <t>店舗</t>
+          <t>店頭</t>
         </is>
       </c>
       <c r="E209" s="2" t="inlineStr">
@@ -13114,10 +13170,8 @@
           <t>コーヒーゼリー 4個</t>
         </is>
       </c>
-      <c r="I209" s="2" t="inlineStr">
-        <is>
-          <t>２</t>
-        </is>
+      <c r="I209" s="2" t="n">
+        <v>2</v>
       </c>
       <c r="J209" s="2" t="n">
         <v>980</v>
@@ -13136,6 +13190,7 @@
           <t>有効</t>
         </is>
       </c>
+      <c r="O209" s="2" t="inlineStr"/>
     </row>
     <row r="210">
       <c r="A210" s="2" t="inlineStr">
@@ -13143,7 +13198,7 @@
           <t>A-20260209</t>
         </is>
       </c>
-      <c r="B210" s="3" t="n">
+      <c r="B210" s="6" t="n">
         <v>46030</v>
       </c>
       <c r="C210" s="2" t="inlineStr">
@@ -13196,6 +13251,7 @@
           <t>有効</t>
         </is>
       </c>
+      <c r="O210" s="2" t="inlineStr"/>
     </row>
     <row r="211">
       <c r="A211" s="2" t="inlineStr">
@@ -13203,7 +13259,7 @@
           <t>A-20260210</t>
         </is>
       </c>
-      <c r="B211" s="3" t="n">
+      <c r="B211" s="6" t="n">
         <v>46023</v>
       </c>
       <c r="C211" s="2" t="inlineStr">
@@ -13213,7 +13269,7 @@
       </c>
       <c r="D211" s="2" t="inlineStr">
         <is>
-          <t>オフライン</t>
+          <t>店頭</t>
         </is>
       </c>
       <c r="E211" s="2" t="inlineStr">
@@ -13223,12 +13279,12 @@
       </c>
       <c r="F211" s="2" t="inlineStr">
         <is>
-          <t>メンバー</t>
+          <t>会員</t>
         </is>
       </c>
       <c r="G211" s="2" t="inlineStr">
         <is>
-          <t>珈琲豆</t>
+          <t>コーヒー豆</t>
         </is>
       </c>
       <c r="H211" s="2" t="inlineStr">
@@ -13256,6 +13312,7 @@
           <t>有効</t>
         </is>
       </c>
+      <c r="O211" s="2" t="inlineStr"/>
     </row>
     <row r="212">
       <c r="A212" s="2" t="inlineStr">
@@ -13263,17 +13320,17 @@
           <t>A-20260211</t>
         </is>
       </c>
-      <c r="B212" s="3" t="n">
+      <c r="B212" s="6" t="n">
         <v>46035</v>
       </c>
       <c r="C212" s="2" t="inlineStr">
         <is>
-          <t>しんじゅく店</t>
+          <t>新宿店</t>
         </is>
       </c>
       <c r="D212" s="2" t="inlineStr">
         <is>
-          <t>Web</t>
+          <t>EC</t>
         </is>
       </c>
       <c r="E212" s="2" t="inlineStr">
@@ -13312,6 +13369,7 @@
           <t>有効</t>
         </is>
       </c>
+      <c r="O212" s="2" t="inlineStr"/>
     </row>
     <row r="213">
       <c r="A213" s="2" t="inlineStr">
@@ -13319,10 +13377,8 @@
           <t>A-20260212</t>
         </is>
       </c>
-      <c r="B213" s="2" t="inlineStr">
-        <is>
-          <t>1月23日</t>
-        </is>
+      <c r="B213" s="6" t="n">
+        <v>46045</v>
       </c>
       <c r="C213" s="2" t="inlineStr">
         <is>
@@ -13331,7 +13387,7 @@
       </c>
       <c r="D213" s="2" t="inlineStr">
         <is>
-          <t>オフライン</t>
+          <t>店頭</t>
         </is>
       </c>
       <c r="E213" s="2" t="inlineStr">
@@ -13370,6 +13426,7 @@
           <t>有効</t>
         </is>
       </c>
+      <c r="O213" s="2" t="inlineStr"/>
     </row>
     <row r="214">
       <c r="A214" s="2" t="inlineStr">
@@ -13377,7 +13434,7 @@
           <t>A-20260213</t>
         </is>
       </c>
-      <c r="B214" s="3" t="n">
+      <c r="B214" s="6" t="n">
         <v>46026</v>
       </c>
       <c r="C214" s="2" t="inlineStr">
@@ -13430,6 +13487,7 @@
           <t>無効</t>
         </is>
       </c>
+      <c r="O214" s="2" t="inlineStr"/>
     </row>
     <row r="215">
       <c r="A215" s="2" t="inlineStr">
@@ -13437,17 +13495,17 @@
           <t>A-20260214</t>
         </is>
       </c>
-      <c r="B215" s="3" t="n">
+      <c r="B215" s="6" t="n">
         <v>46051</v>
       </c>
       <c r="C215" s="2" t="inlineStr">
         <is>
-          <t>渋谷　店</t>
+          <t>渋谷店</t>
         </is>
       </c>
       <c r="D215" s="2" t="inlineStr">
         <is>
-          <t>店舗</t>
+          <t>店頭</t>
         </is>
       </c>
       <c r="E215" s="2" t="inlineStr">
@@ -13490,6 +13548,7 @@
           <t>有効</t>
         </is>
       </c>
+      <c r="O215" s="2" t="inlineStr"/>
     </row>
     <row r="216">
       <c r="A216" s="2" t="inlineStr">
@@ -13497,10 +13556,8 @@
           <t>A-20260215</t>
         </is>
       </c>
-      <c r="B216" s="2" t="inlineStr">
-        <is>
-          <t>2026/1/14</t>
-        </is>
+      <c r="B216" s="6" t="n">
+        <v>46036</v>
       </c>
       <c r="C216" s="2" t="inlineStr">
         <is>
@@ -13519,12 +13576,12 @@
       </c>
       <c r="F216" s="2" t="inlineStr">
         <is>
-          <t>メンバー</t>
+          <t>会員</t>
         </is>
       </c>
       <c r="G216" s="2" t="inlineStr">
         <is>
-          <t>珈琲豆</t>
+          <t>コーヒー豆</t>
         </is>
       </c>
       <c r="H216" s="2" t="inlineStr">
@@ -13552,6 +13609,7 @@
           <t>有効</t>
         </is>
       </c>
+      <c r="O216" s="2" t="inlineStr"/>
     </row>
     <row r="217">
       <c r="A217" s="2" t="inlineStr">
@@ -13559,8 +13617,8 @@
           <t>A-20260216</t>
         </is>
       </c>
-      <c r="B217" s="2" t="n">
-        <v>20260118</v>
+      <c r="B217" s="6" t="n">
+        <v>46040</v>
       </c>
       <c r="C217" s="2" t="inlineStr">
         <is>
@@ -13569,7 +13627,7 @@
       </c>
       <c r="D217" s="2" t="inlineStr">
         <is>
-          <t>オフライン</t>
+          <t>店頭</t>
         </is>
       </c>
       <c r="E217" s="2" t="inlineStr">
@@ -13579,12 +13637,12 @@
       </c>
       <c r="F217" s="2" t="inlineStr">
         <is>
-          <t>法人顧客</t>
+          <t>法人</t>
         </is>
       </c>
       <c r="G217" s="2" t="inlineStr">
         <is>
-          <t>お菓子</t>
+          <t>菓子</t>
         </is>
       </c>
       <c r="H217" s="2" t="inlineStr">
@@ -13612,6 +13670,7 @@
           <t>有効</t>
         </is>
       </c>
+      <c r="O217" s="2" t="inlineStr"/>
     </row>
     <row r="218">
       <c r="A218" s="2" t="inlineStr">
@@ -13619,7 +13678,7 @@
           <t>A-20260217</t>
         </is>
       </c>
-      <c r="B218" s="3" t="n">
+      <c r="B218" s="6" t="n">
         <v>46051</v>
       </c>
       <c r="C218" s="2" t="inlineStr">
@@ -13629,7 +13688,7 @@
       </c>
       <c r="D218" s="2" t="inlineStr">
         <is>
-          <t>店舗</t>
+          <t>店頭</t>
         </is>
       </c>
       <c r="E218" s="2" t="inlineStr">
@@ -13672,6 +13731,7 @@
           <t>有効</t>
         </is>
       </c>
+      <c r="O218" s="2" t="inlineStr"/>
     </row>
     <row r="219">
       <c r="A219" s="2" t="inlineStr">
@@ -13679,7 +13739,7 @@
           <t>A-20260218</t>
         </is>
       </c>
-      <c r="B219" s="3" t="n">
+      <c r="B219" s="6" t="n">
         <v>46036</v>
       </c>
       <c r="C219" s="2" t="inlineStr">
@@ -13699,12 +13759,12 @@
       </c>
       <c r="F219" s="2" t="inlineStr">
         <is>
-          <t>一般客</t>
+          <t>一般</t>
         </is>
       </c>
       <c r="G219" s="2" t="inlineStr">
         <is>
-          <t>珈琲豆</t>
+          <t>コーヒー豆</t>
         </is>
       </c>
       <c r="H219" s="2" t="inlineStr">
@@ -13712,10 +13772,8 @@
           <t>モカ 200g</t>
         </is>
       </c>
-      <c r="I219" s="2" t="inlineStr">
-        <is>
-          <t>4個</t>
-        </is>
+      <c r="I219" s="2" t="n">
+        <v>4</v>
       </c>
       <c r="J219" s="2" t="n">
         <v>1400</v>
@@ -13734,6 +13792,7 @@
           <t>有効</t>
         </is>
       </c>
+      <c r="O219" s="2" t="inlineStr"/>
     </row>
     <row r="220">
       <c r="A220" s="2" t="inlineStr">
@@ -13741,7 +13800,7 @@
           <t>A-20260219</t>
         </is>
       </c>
-      <c r="B220" s="3" t="n">
+      <c r="B220" s="6" t="n">
         <v>46033</v>
       </c>
       <c r="C220" s="2" t="inlineStr">
@@ -13790,6 +13849,7 @@
           <t>有効</t>
         </is>
       </c>
+      <c r="O220" s="2" t="inlineStr"/>
     </row>
     <row r="221">
       <c r="A221" s="2" t="inlineStr">
@@ -13797,14 +13857,12 @@
           <t>A-20260220</t>
         </is>
       </c>
-      <c r="B221" s="2" t="inlineStr">
-        <is>
-          <t>2026-01-20</t>
-        </is>
+      <c r="B221" s="6" t="n">
+        <v>46042</v>
       </c>
       <c r="C221" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">渋谷店 </t>
+          <t>渋谷店</t>
         </is>
       </c>
       <c r="D221" s="2" t="inlineStr">
@@ -13819,7 +13877,7 @@
       </c>
       <c r="F221" s="2" t="inlineStr">
         <is>
-          <t>一般客</t>
+          <t>一般</t>
         </is>
       </c>
       <c r="G221" s="2" t="inlineStr">
@@ -13852,6 +13910,7 @@
           <t>有効</t>
         </is>
       </c>
+      <c r="O221" s="2" t="inlineStr"/>
     </row>
     <row r="222">
       <c r="A222" s="2" t="inlineStr">
@@ -13859,7 +13918,7 @@
           <t>A-20260221</t>
         </is>
       </c>
-      <c r="B222" s="3" t="n">
+      <c r="B222" s="6" t="n">
         <v>46041</v>
       </c>
       <c r="C222" s="2" t="inlineStr">
@@ -13869,7 +13928,7 @@
       </c>
       <c r="D222" s="2" t="inlineStr">
         <is>
-          <t>ec</t>
+          <t>EC</t>
         </is>
       </c>
       <c r="E222" s="2" t="inlineStr">
@@ -13879,7 +13938,7 @@
       </c>
       <c r="F222" s="2" t="inlineStr">
         <is>
-          <t>一般客</t>
+          <t>一般</t>
         </is>
       </c>
       <c r="G222" s="2" t="inlineStr">
@@ -13912,6 +13971,7 @@
           <t>有効</t>
         </is>
       </c>
+      <c r="O222" s="2" t="inlineStr"/>
     </row>
     <row r="223">
       <c r="A223" s="2" t="inlineStr">
@@ -13919,7 +13979,7 @@
           <t>A-20260222</t>
         </is>
       </c>
-      <c r="B223" s="3" t="n">
+      <c r="B223" s="6" t="n">
         <v>46041</v>
       </c>
       <c r="C223" s="2" t="inlineStr">
@@ -13929,7 +13989,7 @@
       </c>
       <c r="D223" s="2" t="inlineStr">
         <is>
-          <t>オフライン</t>
+          <t>店頭</t>
         </is>
       </c>
       <c r="E223" s="2" t="inlineStr">
@@ -13944,7 +14004,7 @@
       </c>
       <c r="G223" s="2" t="inlineStr">
         <is>
-          <t>コーヒー</t>
+          <t>コーヒー豆</t>
         </is>
       </c>
       <c r="H223" s="2" t="inlineStr">
@@ -13955,10 +14015,8 @@
       <c r="I223" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="J223" s="2" t="inlineStr">
-        <is>
-          <t>1,200円</t>
-        </is>
+      <c r="J223" s="2" t="n">
+        <v>1200</v>
       </c>
       <c r="K223" s="2" t="n">
         <v>0</v>
@@ -13974,6 +14032,7 @@
           <t>有効</t>
         </is>
       </c>
+      <c r="O223" s="2" t="inlineStr"/>
     </row>
     <row r="224">
       <c r="A224" s="2" t="inlineStr">
@@ -13981,7 +14040,7 @@
           <t>A-20260223</t>
         </is>
       </c>
-      <c r="B224" s="3" t="n">
+      <c r="B224" s="6" t="n">
         <v>46029</v>
       </c>
       <c r="C224" s="2" t="inlineStr">
@@ -13991,7 +14050,7 @@
       </c>
       <c r="D224" s="2" t="inlineStr">
         <is>
-          <t>Ｅ Ｃ</t>
+          <t>EC</t>
         </is>
       </c>
       <c r="E224" s="2" t="inlineStr">
@@ -14034,6 +14093,7 @@
           <t>無効</t>
         </is>
       </c>
+      <c r="O224" s="2" t="inlineStr"/>
     </row>
     <row r="225">
       <c r="A225" s="2" t="inlineStr">
@@ -14041,19 +14101,17 @@
           <t>A-20260224</t>
         </is>
       </c>
-      <c r="B225" s="2" t="inlineStr">
-        <is>
-          <t>1月19日</t>
-        </is>
+      <c r="B225" s="6" t="n">
+        <v>46041</v>
       </c>
       <c r="C225" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">横浜店 </t>
+          <t>横浜店</t>
         </is>
       </c>
       <c r="D225" s="2" t="inlineStr">
         <is>
-          <t>Web</t>
+          <t>EC</t>
         </is>
       </c>
       <c r="E225" s="2" t="inlineStr">
@@ -14096,6 +14154,7 @@
           <t>有効</t>
         </is>
       </c>
+      <c r="O225" s="2" t="inlineStr"/>
     </row>
     <row r="226">
       <c r="A226" s="2" t="inlineStr">
@@ -14103,7 +14162,7 @@
           <t>A-20260225</t>
         </is>
       </c>
-      <c r="B226" s="3" t="n">
+      <c r="B226" s="6" t="n">
         <v>46044</v>
       </c>
       <c r="C226" s="2" t="inlineStr">
@@ -14128,7 +14187,7 @@
       </c>
       <c r="G226" s="2" t="inlineStr">
         <is>
-          <t>コーヒー</t>
+          <t>コーヒー豆</t>
         </is>
       </c>
       <c r="H226" s="2" t="inlineStr">
@@ -14156,6 +14215,7 @@
           <t>有効</t>
         </is>
       </c>
+      <c r="O226" s="2" t="inlineStr"/>
     </row>
     <row r="227">
       <c r="A227" s="2" t="inlineStr">
@@ -14163,7 +14223,7 @@
           <t>A-20260226</t>
         </is>
       </c>
-      <c r="B227" s="3" t="n">
+      <c r="B227" s="6" t="n">
         <v>46024</v>
       </c>
       <c r="C227" s="2" t="inlineStr">
@@ -14212,6 +14272,7 @@
           <t>有効</t>
         </is>
       </c>
+      <c r="O227" s="2" t="inlineStr"/>
     </row>
     <row r="228">
       <c r="A228" s="2" t="inlineStr">
@@ -14219,14 +14280,12 @@
           <t>A-20260227</t>
         </is>
       </c>
-      <c r="B228" s="2" t="inlineStr">
-        <is>
-          <t>2026/1/9</t>
-        </is>
+      <c r="B228" s="6" t="n">
+        <v>46031</v>
       </c>
       <c r="C228" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">渋谷店 </t>
+          <t>渋谷店</t>
         </is>
       </c>
       <c r="D228" s="2" t="inlineStr">
@@ -14246,7 +14305,7 @@
       </c>
       <c r="G228" s="2" t="inlineStr">
         <is>
-          <t>コーヒー</t>
+          <t>コーヒー豆</t>
         </is>
       </c>
       <c r="H228" s="2" t="inlineStr">
@@ -14274,6 +14333,7 @@
           <t>有効</t>
         </is>
       </c>
+      <c r="O228" s="2" t="inlineStr"/>
     </row>
     <row r="229">
       <c r="A229" s="2" t="inlineStr">
@@ -14281,8 +14341,8 @@
           <t>A-20260228</t>
         </is>
       </c>
-      <c r="B229" s="2" t="n">
-        <v>20260111</v>
+      <c r="B229" s="6" t="n">
+        <v>46033</v>
       </c>
       <c r="C229" s="2" t="inlineStr">
         <is>
@@ -14291,7 +14351,7 @@
       </c>
       <c r="D229" s="2" t="inlineStr">
         <is>
-          <t>オンライン</t>
+          <t>EC</t>
         </is>
       </c>
       <c r="E229" s="2" t="inlineStr">
@@ -14334,6 +14394,7 @@
           <t>有効</t>
         </is>
       </c>
+      <c r="O229" s="2" t="inlineStr"/>
     </row>
     <row r="230">
       <c r="A230" s="2" t="inlineStr">
@@ -14341,7 +14402,7 @@
           <t>A-20260229</t>
         </is>
       </c>
-      <c r="B230" s="3" t="n">
+      <c r="B230" s="6" t="n">
         <v>46050</v>
       </c>
       <c r="C230" s="2" t="inlineStr">
@@ -14394,6 +14455,7 @@
           <t>有効</t>
         </is>
       </c>
+      <c r="O230" s="2" t="inlineStr"/>
     </row>
     <row r="231">
       <c r="A231" s="2" t="inlineStr">
@@ -14401,17 +14463,17 @@
           <t>A-20260230</t>
         </is>
       </c>
-      <c r="B231" s="3" t="n">
+      <c r="B231" s="6" t="n">
         <v>46035</v>
       </c>
       <c r="C231" s="2" t="inlineStr">
         <is>
-          <t>しんじゅく店</t>
+          <t>新宿店</t>
         </is>
       </c>
       <c r="D231" s="2" t="inlineStr">
         <is>
-          <t>ec</t>
+          <t>EC</t>
         </is>
       </c>
       <c r="E231" s="2" t="inlineStr">
@@ -14422,7 +14484,7 @@
       <c r="F231" s="2" t="n"/>
       <c r="G231" s="2" t="inlineStr">
         <is>
-          <t>ギフト商品</t>
+          <t>ギフト</t>
         </is>
       </c>
       <c r="H231" s="2" t="inlineStr">
@@ -14450,6 +14512,7 @@
           <t>有効</t>
         </is>
       </c>
+      <c r="O231" s="2" t="inlineStr"/>
     </row>
     <row r="232">
       <c r="A232" s="2" t="inlineStr">
@@ -14457,7 +14520,7 @@
           <t>A-20260231</t>
         </is>
       </c>
-      <c r="B232" s="3" t="n">
+      <c r="B232" s="6" t="n">
         <v>46051</v>
       </c>
       <c r="C232" s="2" t="inlineStr">
@@ -14467,7 +14530,7 @@
       </c>
       <c r="D232" s="2" t="inlineStr">
         <is>
-          <t>ec</t>
+          <t>EC</t>
         </is>
       </c>
       <c r="E232" s="2" t="inlineStr">
@@ -14482,7 +14545,7 @@
       </c>
       <c r="G232" s="2" t="inlineStr">
         <is>
-          <t>抽出器具</t>
+          <t>器具</t>
         </is>
       </c>
       <c r="H232" s="2" t="inlineStr">
@@ -14490,16 +14553,14 @@
           <t>ペーパーフィルター</t>
         </is>
       </c>
-      <c r="I232" s="2" t="inlineStr">
-        <is>
-          <t>１０</t>
-        </is>
+      <c r="I232" s="2" t="n">
+        <v>10</v>
       </c>
       <c r="J232" s="2" t="n">
         <v>480</v>
       </c>
       <c r="K232" s="2" t="n">
-        <v>5</v>
+        <v>0.05</v>
       </c>
       <c r="L232" s="2" t="inlineStr">
         <is>
@@ -14512,6 +14573,7 @@
           <t>有効</t>
         </is>
       </c>
+      <c r="O232" s="2" t="inlineStr"/>
     </row>
     <row r="233">
       <c r="A233" s="2" t="inlineStr">
@@ -14519,10 +14581,8 @@
           <t>A-20260232</t>
         </is>
       </c>
-      <c r="B233" s="2" t="inlineStr">
-        <is>
-          <t>2026-01-24</t>
-        </is>
+      <c r="B233" s="6" t="n">
+        <v>46046</v>
       </c>
       <c r="C233" s="2" t="inlineStr">
         <is>
@@ -14531,7 +14591,7 @@
       </c>
       <c r="D233" s="2" t="inlineStr">
         <is>
-          <t>オフライン</t>
+          <t>店頭</t>
         </is>
       </c>
       <c r="E233" s="2" t="inlineStr">
@@ -14574,6 +14634,7 @@
           <t>有効</t>
         </is>
       </c>
+      <c r="O233" s="2" t="inlineStr"/>
     </row>
     <row r="234">
       <c r="A234" s="2" t="inlineStr">
@@ -14581,7 +14642,7 @@
           <t>A-20260233</t>
         </is>
       </c>
-      <c r="B234" s="3" t="n">
+      <c r="B234" s="6" t="n">
         <v>46043</v>
       </c>
       <c r="C234" s="2" t="inlineStr">
@@ -14591,7 +14652,7 @@
       </c>
       <c r="D234" s="2" t="inlineStr">
         <is>
-          <t>オンライン</t>
+          <t>EC</t>
         </is>
       </c>
       <c r="E234" s="2" t="inlineStr">
@@ -14606,7 +14667,7 @@
       </c>
       <c r="G234" s="2" t="inlineStr">
         <is>
-          <t>ギフト商品</t>
+          <t>ギフト</t>
         </is>
       </c>
       <c r="H234" s="2" t="inlineStr">
@@ -14617,10 +14678,8 @@
       <c r="I234" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="J234" s="2" t="inlineStr">
-        <is>
-          <t>¥5,800</t>
-        </is>
+      <c r="J234" s="2" t="n">
+        <v>5800</v>
       </c>
       <c r="K234" s="2" t="n">
         <v>0.05</v>
@@ -14636,6 +14695,7 @@
           <t>有効</t>
         </is>
       </c>
+      <c r="O234" s="2" t="inlineStr"/>
     </row>
     <row r="235">
       <c r="A235" s="2" t="inlineStr">
@@ -14643,17 +14703,17 @@
           <t>A-20260234</t>
         </is>
       </c>
-      <c r="B235" s="3" t="n">
+      <c r="B235" s="6" t="n">
         <v>46050</v>
       </c>
       <c r="C235" s="2" t="inlineStr">
         <is>
-          <t>しんじゅく店</t>
+          <t>新宿店</t>
         </is>
       </c>
       <c r="D235" s="2" t="inlineStr">
         <is>
-          <t>オフライン</t>
+          <t>店頭</t>
         </is>
       </c>
       <c r="E235" s="2" t="inlineStr">
@@ -14682,10 +14742,8 @@
       <c r="J235" s="2" t="n">
         <v>2600</v>
       </c>
-      <c r="K235" s="2" t="inlineStr">
-        <is>
-          <t>10%</t>
-        </is>
+      <c r="K235" s="2" t="n">
+        <v>0.1</v>
       </c>
       <c r="L235" s="2" t="inlineStr">
         <is>
@@ -14698,6 +14756,7 @@
           <t>有効</t>
         </is>
       </c>
+      <c r="O235" s="2" t="inlineStr"/>
     </row>
     <row r="236">
       <c r="A236" s="2" t="inlineStr">
@@ -14705,7 +14764,7 @@
           <t>A-20260235</t>
         </is>
       </c>
-      <c r="B236" s="3" t="n">
+      <c r="B236" s="6" t="n">
         <v>46047</v>
       </c>
       <c r="C236" s="2" t="inlineStr">
@@ -14744,10 +14803,8 @@
       <c r="J236" s="2" t="n">
         <v>5800</v>
       </c>
-      <c r="K236" s="2" t="inlineStr">
-        <is>
-          <t>10%</t>
-        </is>
+      <c r="K236" s="2" t="n">
+        <v>0.1</v>
       </c>
       <c r="L236" s="2" t="inlineStr">
         <is>
@@ -14760,6 +14817,7 @@
           <t>有効</t>
         </is>
       </c>
+      <c r="O236" s="2" t="inlineStr"/>
     </row>
     <row r="237">
       <c r="A237" s="2" t="inlineStr">
@@ -14767,19 +14825,17 @@
           <t>A-20260236</t>
         </is>
       </c>
-      <c r="B237" s="2" t="inlineStr">
-        <is>
-          <t>1月3日</t>
-        </is>
+      <c r="B237" s="6" t="n">
+        <v>46025</v>
       </c>
       <c r="C237" s="2" t="inlineStr">
         <is>
-          <t>ヨコハマ店</t>
+          <t>横浜店</t>
         </is>
       </c>
       <c r="D237" s="2" t="inlineStr">
         <is>
-          <t>オフライン</t>
+          <t>店頭</t>
         </is>
       </c>
       <c r="E237" s="2" t="inlineStr">
@@ -14804,10 +14860,8 @@
       <c r="J237" s="2" t="n">
         <v>2600</v>
       </c>
-      <c r="K237" s="2" t="inlineStr">
-        <is>
-          <t>10%</t>
-        </is>
+      <c r="K237" s="2" t="n">
+        <v>0.1</v>
       </c>
       <c r="L237" s="2" t="inlineStr">
         <is>
@@ -14820,6 +14874,7 @@
           <t>有効</t>
         </is>
       </c>
+      <c r="O237" s="2" t="inlineStr"/>
     </row>
     <row r="238">
       <c r="A238" s="2" t="inlineStr">
@@ -14827,12 +14882,12 @@
           <t>A-20260237</t>
         </is>
       </c>
-      <c r="B238" s="3" t="n">
+      <c r="B238" s="6" t="n">
         <v>46037</v>
       </c>
       <c r="C238" s="2" t="inlineStr">
         <is>
-          <t>シブヤ店</t>
+          <t>渋谷店</t>
         </is>
       </c>
       <c r="D238" s="2" t="inlineStr">
@@ -14880,6 +14935,7 @@
           <t>有効</t>
         </is>
       </c>
+      <c r="O238" s="2" t="inlineStr"/>
     </row>
     <row r="239">
       <c r="A239" s="2" t="inlineStr">
@@ -14887,7 +14943,7 @@
           <t>A-20260238</t>
         </is>
       </c>
-      <c r="B239" s="3" t="n">
+      <c r="B239" s="6" t="n">
         <v>46053</v>
       </c>
       <c r="C239" s="2" t="inlineStr">
@@ -14912,7 +14968,7 @@
       </c>
       <c r="G239" s="2" t="inlineStr">
         <is>
-          <t>お菓子</t>
+          <t>菓子</t>
         </is>
       </c>
       <c r="H239" s="2" t="inlineStr">
@@ -14940,6 +14996,7 @@
           <t>有効</t>
         </is>
       </c>
+      <c r="O239" s="2" t="inlineStr"/>
     </row>
     <row r="240">
       <c r="A240" s="2" t="inlineStr">
@@ -14947,14 +15004,12 @@
           <t>A-20260239</t>
         </is>
       </c>
-      <c r="B240" s="2" t="inlineStr">
-        <is>
-          <t>2026/1/13</t>
-        </is>
+      <c r="B240" s="6" t="n">
+        <v>46035</v>
       </c>
       <c r="C240" s="2" t="inlineStr">
         <is>
-          <t>シブヤ店</t>
+          <t>渋谷店</t>
         </is>
       </c>
       <c r="D240" s="2" t="inlineStr">
@@ -14969,7 +15024,7 @@
       </c>
       <c r="F240" s="2" t="inlineStr">
         <is>
-          <t>一般客</t>
+          <t>一般</t>
         </is>
       </c>
       <c r="G240" s="2" t="inlineStr">
@@ -14985,10 +15040,8 @@
       <c r="I240" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="J240" s="2" t="inlineStr">
-        <is>
-          <t>2,600円</t>
-        </is>
+      <c r="J240" s="2" t="n">
+        <v>2600</v>
       </c>
       <c r="K240" s="2" t="n">
         <v>0</v>
@@ -15004,6 +15057,7 @@
           <t>有効</t>
         </is>
       </c>
+      <c r="O240" s="2" t="inlineStr"/>
     </row>
     <row r="241">
       <c r="A241" s="2" t="inlineStr">
@@ -15011,8 +15065,8 @@
           <t>A-20260240</t>
         </is>
       </c>
-      <c r="B241" s="2" t="n">
-        <v>20260107</v>
+      <c r="B241" s="6" t="n">
+        <v>46029</v>
       </c>
       <c r="C241" s="2" t="inlineStr">
         <is>
@@ -15021,7 +15075,7 @@
       </c>
       <c r="D241" s="2" t="inlineStr">
         <is>
-          <t>店舗</t>
+          <t>店頭</t>
         </is>
       </c>
       <c r="E241" s="2" t="inlineStr">
@@ -15051,7 +15105,7 @@
         <v>1200</v>
       </c>
       <c r="K241" s="2" t="n">
-        <v>5</v>
+        <v>0.05</v>
       </c>
       <c r="L241" s="2" t="inlineStr">
         <is>
@@ -15064,6 +15118,7 @@
           <t>有効</t>
         </is>
       </c>
+      <c r="O241" s="2" t="inlineStr"/>
     </row>
     <row r="242">
       <c r="A242" s="2" t="inlineStr">
@@ -15071,17 +15126,17 @@
           <t>A-20260241</t>
         </is>
       </c>
-      <c r="B242" s="3" t="n">
+      <c r="B242" s="6" t="n">
         <v>46045</v>
       </c>
       <c r="C242" s="2" t="inlineStr">
         <is>
-          <t>新宿 店</t>
+          <t>新宿店</t>
         </is>
       </c>
       <c r="D242" s="2" t="inlineStr">
         <is>
-          <t>ec</t>
+          <t>EC</t>
         </is>
       </c>
       <c r="E242" s="2" t="inlineStr">
@@ -15124,6 +15179,7 @@
           <t>有効</t>
         </is>
       </c>
+      <c r="O242" s="2" t="inlineStr"/>
     </row>
     <row r="243">
       <c r="A243" s="2" t="inlineStr">
@@ -15131,12 +15187,12 @@
           <t>A-20260242</t>
         </is>
       </c>
-      <c r="B243" s="3" t="n">
+      <c r="B243" s="6" t="n">
         <v>46027</v>
       </c>
       <c r="C243" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">横浜店 </t>
+          <t>横浜店</t>
         </is>
       </c>
       <c r="D243" s="2" t="inlineStr">
@@ -15151,7 +15207,7 @@
       </c>
       <c r="F243" s="2" t="inlineStr">
         <is>
-          <t>メンバー</t>
+          <t>会員</t>
         </is>
       </c>
       <c r="G243" s="2" t="inlineStr">
@@ -15184,6 +15240,7 @@
           <t>有効</t>
         </is>
       </c>
+      <c r="O243" s="2" t="inlineStr"/>
     </row>
     <row r="244">
       <c r="A244" s="2" t="inlineStr">
@@ -15191,12 +15248,12 @@
           <t>A-20260243</t>
         </is>
       </c>
-      <c r="B244" s="3" t="n">
+      <c r="B244" s="6" t="n">
         <v>46050</v>
       </c>
       <c r="C244" s="2" t="inlineStr">
         <is>
-          <t>名古屋 店</t>
+          <t>名古屋店</t>
         </is>
       </c>
       <c r="D244" s="2" t="inlineStr">
@@ -15211,12 +15268,12 @@
       </c>
       <c r="F244" s="2" t="inlineStr">
         <is>
-          <t>一般客</t>
+          <t>一般</t>
         </is>
       </c>
       <c r="G244" s="2" t="inlineStr">
         <is>
-          <t>抽出器具</t>
+          <t>器具</t>
         </is>
       </c>
       <c r="H244" s="2" t="inlineStr">
@@ -15244,6 +15301,7 @@
           <t>有効</t>
         </is>
       </c>
+      <c r="O244" s="2" t="inlineStr"/>
     </row>
     <row r="245">
       <c r="A245" s="2" t="inlineStr">
@@ -15251,19 +15309,17 @@
           <t>A-20260244</t>
         </is>
       </c>
-      <c r="B245" s="2" t="inlineStr">
-        <is>
-          <t>2026-01-26</t>
-        </is>
+      <c r="B245" s="6" t="n">
+        <v>46048</v>
       </c>
       <c r="C245" s="2" t="inlineStr">
         <is>
-          <t>ヨコハマ店</t>
+          <t>横浜店</t>
         </is>
       </c>
       <c r="D245" s="2" t="inlineStr">
         <is>
-          <t>オフライン</t>
+          <t>店頭</t>
         </is>
       </c>
       <c r="E245" s="2" t="inlineStr">
@@ -15273,12 +15329,12 @@
       </c>
       <c r="F245" s="2" t="inlineStr">
         <is>
-          <t>一般客</t>
+          <t>一般</t>
         </is>
       </c>
       <c r="G245" s="2" t="inlineStr">
         <is>
-          <t>ギフト商品</t>
+          <t>ギフト</t>
         </is>
       </c>
       <c r="H245" s="2" t="inlineStr">
@@ -15306,6 +15362,7 @@
           <t>有効</t>
         </is>
       </c>
+      <c r="O245" s="2" t="inlineStr"/>
     </row>
     <row r="246">
       <c r="A246" s="2" t="inlineStr">
@@ -15313,7 +15370,7 @@
           <t>A-20260245</t>
         </is>
       </c>
-      <c r="B246" s="3" t="n">
+      <c r="B246" s="6" t="n">
         <v>46050</v>
       </c>
       <c r="C246" s="2" t="inlineStr">
@@ -15323,7 +15380,7 @@
       </c>
       <c r="D246" s="2" t="inlineStr">
         <is>
-          <t>オフライン</t>
+          <t>店頭</t>
         </is>
       </c>
       <c r="E246" s="2" t="inlineStr">
@@ -15333,12 +15390,12 @@
       </c>
       <c r="F246" s="2" t="inlineStr">
         <is>
-          <t>一般客</t>
+          <t>一般</t>
         </is>
       </c>
       <c r="G246" s="2" t="inlineStr">
         <is>
-          <t>抽出器具</t>
+          <t>器具</t>
         </is>
       </c>
       <c r="H246" s="2" t="inlineStr">
@@ -15370,6 +15427,7 @@
           <t>有効</t>
         </is>
       </c>
+      <c r="O246" s="2" t="inlineStr"/>
     </row>
     <row r="247">
       <c r="A247" s="2" t="inlineStr">
@@ -15377,12 +15435,12 @@
           <t>A-20260246</t>
         </is>
       </c>
-      <c r="B247" s="3" t="n">
+      <c r="B247" s="6" t="n">
         <v>46034</v>
       </c>
       <c r="C247" s="2" t="inlineStr">
         <is>
-          <t>名古屋 店</t>
+          <t>名古屋店</t>
         </is>
       </c>
       <c r="D247" s="2" t="inlineStr">
@@ -15397,12 +15455,12 @@
       </c>
       <c r="F247" s="2" t="inlineStr">
         <is>
-          <t>一般客</t>
+          <t>一般</t>
         </is>
       </c>
       <c r="G247" s="2" t="inlineStr">
         <is>
-          <t>ギフト商品</t>
+          <t>ギフト</t>
         </is>
       </c>
       <c r="H247" s="2" t="inlineStr">
@@ -15430,6 +15488,7 @@
           <t>有効</t>
         </is>
       </c>
+      <c r="O247" s="2" t="inlineStr"/>
     </row>
     <row r="248">
       <c r="A248" s="2" t="inlineStr">
@@ -15437,12 +15496,12 @@
           <t>A-20260247</t>
         </is>
       </c>
-      <c r="B248" s="3" t="n">
+      <c r="B248" s="6" t="n">
         <v>46053</v>
       </c>
       <c r="C248" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">横浜店 </t>
+          <t>横浜店</t>
         </is>
       </c>
       <c r="D248" s="2" t="inlineStr">
@@ -15457,7 +15516,7 @@
       </c>
       <c r="F248" s="2" t="inlineStr">
         <is>
-          <t>法人顧客</t>
+          <t>法人</t>
         </is>
       </c>
       <c r="G248" s="2" t="inlineStr">
@@ -15473,7 +15532,9 @@
       <c r="I248" s="2" t="n">
         <v>8</v>
       </c>
-      <c r="J248" s="2" t="n"/>
+      <c r="J248" s="7" t="n">
+        <v>980</v>
+      </c>
       <c r="K248" s="2" t="n">
         <v>0</v>
       </c>
@@ -15488,6 +15549,11 @@
           <t>有効</t>
         </is>
       </c>
+      <c r="O248" s="2" t="inlineStr">
+        <is>
+          <t>補完</t>
+        </is>
+      </c>
     </row>
     <row r="249">
       <c r="A249" s="2" t="inlineStr">
@@ -15495,10 +15561,8 @@
           <t>A-20260248</t>
         </is>
       </c>
-      <c r="B249" s="2" t="inlineStr">
-        <is>
-          <t>1月26日</t>
-        </is>
+      <c r="B249" s="6" t="n">
+        <v>46048</v>
       </c>
       <c r="C249" s="2" t="inlineStr">
         <is>
@@ -15507,7 +15571,7 @@
       </c>
       <c r="D249" s="2" t="inlineStr">
         <is>
-          <t>店舗</t>
+          <t>店頭</t>
         </is>
       </c>
       <c r="E249" s="2" t="inlineStr">
@@ -15517,7 +15581,7 @@
       </c>
       <c r="F249" s="2" t="inlineStr">
         <is>
-          <t>一般客</t>
+          <t>一般</t>
         </is>
       </c>
       <c r="G249" s="2" t="inlineStr">
@@ -15550,6 +15614,7 @@
           <t>有効</t>
         </is>
       </c>
+      <c r="O249" s="2" t="inlineStr"/>
     </row>
     <row r="250">
       <c r="A250" s="2" t="inlineStr">
@@ -15557,17 +15622,17 @@
           <t>A-20260249</t>
         </is>
       </c>
-      <c r="B250" s="3" t="n">
+      <c r="B250" s="6" t="n">
         <v>46033</v>
       </c>
       <c r="C250" s="2" t="inlineStr">
         <is>
-          <t>渋谷　店</t>
+          <t>渋谷店</t>
         </is>
       </c>
       <c r="D250" s="2" t="inlineStr">
         <is>
-          <t>店舗</t>
+          <t>店頭</t>
         </is>
       </c>
       <c r="E250" s="2" t="inlineStr">
@@ -15590,10 +15655,8 @@
           <t>ブレンド 200g</t>
         </is>
       </c>
-      <c r="I250" s="2" t="inlineStr">
-        <is>
-          <t>1個</t>
-        </is>
+      <c r="I250" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="J250" s="2" t="n">
         <v>1200</v>
@@ -15612,6 +15675,7 @@
           <t>有効</t>
         </is>
       </c>
+      <c r="O250" s="2" t="inlineStr"/>
     </row>
     <row r="251">
       <c r="A251" s="2" t="inlineStr">
@@ -15619,17 +15683,17 @@
           <t>A-20260250</t>
         </is>
       </c>
-      <c r="B251" s="3" t="n">
+      <c r="B251" s="6" t="n">
         <v>46043</v>
       </c>
       <c r="C251" s="2" t="inlineStr">
         <is>
-          <t>ヨコハマ店</t>
+          <t>横浜店</t>
         </is>
       </c>
       <c r="D251" s="2" t="inlineStr">
         <is>
-          <t>オフライン</t>
+          <t>店頭</t>
         </is>
       </c>
       <c r="E251" s="2" t="inlineStr">
@@ -15672,6 +15736,7 @@
           <t>有効</t>
         </is>
       </c>
+      <c r="O251" s="2" t="inlineStr"/>
     </row>
     <row r="252">
       <c r="A252" s="2" t="inlineStr">
@@ -15679,14 +15744,12 @@
           <t>A-20260251</t>
         </is>
       </c>
-      <c r="B252" s="2" t="inlineStr">
-        <is>
-          <t>2026/1/8</t>
-        </is>
+      <c r="B252" s="6" t="n">
+        <v>46030</v>
       </c>
       <c r="C252" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">渋谷店 </t>
+          <t>渋谷店</t>
         </is>
       </c>
       <c r="D252" s="2" t="inlineStr">
@@ -15721,7 +15784,7 @@
         <v>2800</v>
       </c>
       <c r="K252" s="2" t="n">
-        <v>5</v>
+        <v>0.05</v>
       </c>
       <c r="L252" s="2" t="inlineStr">
         <is>
@@ -15734,6 +15797,7 @@
           <t>有効</t>
         </is>
       </c>
+      <c r="O252" s="2" t="inlineStr"/>
     </row>
     <row r="253">
       <c r="A253" s="2" t="inlineStr">
@@ -15741,17 +15805,17 @@
           <t>A-20260252</t>
         </is>
       </c>
-      <c r="B253" s="2" t="n">
-        <v>20260119</v>
+      <c r="B253" s="6" t="n">
+        <v>46041</v>
       </c>
       <c r="C253" s="2" t="inlineStr">
         <is>
-          <t>シブヤ店</t>
+          <t>渋谷店</t>
         </is>
       </c>
       <c r="D253" s="2" t="inlineStr">
         <is>
-          <t>店舗</t>
+          <t>店頭</t>
         </is>
       </c>
       <c r="E253" s="2" t="inlineStr">
@@ -15794,6 +15858,7 @@
           <t>有効</t>
         </is>
       </c>
+      <c r="O253" s="2" t="inlineStr"/>
     </row>
     <row r="254">
       <c r="A254" s="2" t="inlineStr">
@@ -15801,7 +15866,7 @@
           <t>A-20260253</t>
         </is>
       </c>
-      <c r="B254" s="3" t="n">
+      <c r="B254" s="6" t="n">
         <v>46037</v>
       </c>
       <c r="C254" s="2" t="inlineStr">
@@ -15821,12 +15886,12 @@
       </c>
       <c r="F254" s="2" t="inlineStr">
         <is>
-          <t>メンバー</t>
+          <t>会員</t>
         </is>
       </c>
       <c r="G254" s="2" t="inlineStr">
         <is>
-          <t>お菓子</t>
+          <t>菓子</t>
         </is>
       </c>
       <c r="H254" s="2" t="inlineStr">
@@ -15854,6 +15919,7 @@
           <t>有効</t>
         </is>
       </c>
+      <c r="O254" s="2" t="inlineStr"/>
     </row>
     <row r="255">
       <c r="A255" s="2" t="inlineStr">
@@ -15861,12 +15927,12 @@
           <t>A-20260254</t>
         </is>
       </c>
-      <c r="B255" s="3" t="n">
+      <c r="B255" s="6" t="n">
         <v>46042</v>
       </c>
       <c r="C255" s="2" t="inlineStr">
         <is>
-          <t>渋谷　店</t>
+          <t>渋谷店</t>
         </is>
       </c>
       <c r="D255" s="2" t="inlineStr">
@@ -15886,7 +15952,7 @@
       </c>
       <c r="G255" s="2" t="inlineStr">
         <is>
-          <t>お菓子</t>
+          <t>菓子</t>
         </is>
       </c>
       <c r="H255" s="2" t="inlineStr">
@@ -15894,10 +15960,8 @@
           <t>焼き菓子アソート</t>
         </is>
       </c>
-      <c r="I255" s="2" t="inlineStr">
-        <is>
-          <t>１０</t>
-        </is>
+      <c r="I255" s="2" t="n">
+        <v>10</v>
       </c>
       <c r="J255" s="2" t="n">
         <v>1500</v>
@@ -15916,6 +15980,7 @@
           <t>有効</t>
         </is>
       </c>
+      <c r="O255" s="2" t="inlineStr"/>
     </row>
     <row r="256">
       <c r="A256" s="2" t="inlineStr">
@@ -15923,17 +15988,17 @@
           <t>A-20260255</t>
         </is>
       </c>
-      <c r="B256" s="3" t="n">
+      <c r="B256" s="6" t="n">
         <v>46035</v>
       </c>
       <c r="C256" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">横浜店 </t>
+          <t>横浜店</t>
         </is>
       </c>
       <c r="D256" s="2" t="inlineStr">
         <is>
-          <t>店舗</t>
+          <t>店頭</t>
         </is>
       </c>
       <c r="E256" s="2" t="inlineStr">
@@ -15943,12 +16008,12 @@
       </c>
       <c r="F256" s="2" t="inlineStr">
         <is>
-          <t>法人顧客</t>
+          <t>法人</t>
         </is>
       </c>
       <c r="G256" s="2" t="inlineStr">
         <is>
-          <t>抽出器具</t>
+          <t>器具</t>
         </is>
       </c>
       <c r="H256" s="2" t="inlineStr">
@@ -15976,6 +16041,7 @@
           <t>有効</t>
         </is>
       </c>
+      <c r="O256" s="2" t="inlineStr"/>
     </row>
     <row r="257">
       <c r="A257" s="2" t="inlineStr">
@@ -15983,10 +16049,8 @@
           <t>A-20260256</t>
         </is>
       </c>
-      <c r="B257" s="2" t="inlineStr">
-        <is>
-          <t>2026-01-14</t>
-        </is>
+      <c r="B257" s="6" t="n">
+        <v>46036</v>
       </c>
       <c r="C257" s="2" t="inlineStr">
         <is>
@@ -16005,12 +16069,12 @@
       </c>
       <c r="F257" s="2" t="inlineStr">
         <is>
-          <t>一般客</t>
+          <t>一般</t>
         </is>
       </c>
       <c r="G257" s="2" t="inlineStr">
         <is>
-          <t>抽出器具</t>
+          <t>器具</t>
         </is>
       </c>
       <c r="H257" s="2" t="inlineStr">
@@ -16021,10 +16085,8 @@
       <c r="I257" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="J257" s="2" t="inlineStr">
-        <is>
-          <t>480円</t>
-        </is>
+      <c r="J257" s="2" t="n">
+        <v>480</v>
       </c>
       <c r="K257" s="2" t="n">
         <v>0</v>
@@ -16040,6 +16102,7 @@
           <t>有効</t>
         </is>
       </c>
+      <c r="O257" s="2" t="inlineStr"/>
     </row>
     <row r="258">
       <c r="A258" s="2" t="inlineStr">
@@ -16047,12 +16110,12 @@
           <t>A-20260257</t>
         </is>
       </c>
-      <c r="B258" s="3" t="n">
+      <c r="B258" s="6" t="n">
         <v>46049</v>
       </c>
       <c r="C258" s="2" t="inlineStr">
         <is>
-          <t>フクオカ店</t>
+          <t>福岡店</t>
         </is>
       </c>
       <c r="D258" s="2" t="inlineStr">
@@ -16100,6 +16163,7 @@
           <t>有効</t>
         </is>
       </c>
+      <c r="O258" s="2" t="inlineStr"/>
     </row>
     <row r="259">
       <c r="A259" s="2" t="inlineStr">
@@ -16107,7 +16171,7 @@
           <t>A-20260258</t>
         </is>
       </c>
-      <c r="B259" s="3" t="n">
+      <c r="B259" s="6" t="n">
         <v>46051</v>
       </c>
       <c r="C259" s="2" t="inlineStr">
@@ -16117,7 +16181,7 @@
       </c>
       <c r="D259" s="2" t="inlineStr">
         <is>
-          <t>オフライン</t>
+          <t>店頭</t>
         </is>
       </c>
       <c r="E259" s="2" t="inlineStr">
@@ -16156,6 +16220,7 @@
           <t>有効</t>
         </is>
       </c>
+      <c r="O259" s="2" t="inlineStr"/>
     </row>
     <row r="260">
       <c r="A260" s="2" t="inlineStr">
@@ -16163,12 +16228,12 @@
           <t>A-20260259</t>
         </is>
       </c>
-      <c r="B260" s="3" t="n">
+      <c r="B260" s="6" t="n">
         <v>46052</v>
       </c>
       <c r="C260" s="2" t="inlineStr">
         <is>
-          <t>名古屋 店</t>
+          <t>名古屋店</t>
         </is>
       </c>
       <c r="D260" s="2" t="inlineStr">
@@ -16184,7 +16249,7 @@
       <c r="F260" s="2" t="n"/>
       <c r="G260" s="2" t="inlineStr">
         <is>
-          <t>抽出器具</t>
+          <t>器具</t>
         </is>
       </c>
       <c r="H260" s="2" t="inlineStr">
@@ -16212,6 +16277,7 @@
           <t>有効</t>
         </is>
       </c>
+      <c r="O260" s="2" t="inlineStr"/>
     </row>
     <row r="261">
       <c r="A261" s="2" t="inlineStr">
@@ -16219,10 +16285,8 @@
           <t>A-20260260</t>
         </is>
       </c>
-      <c r="B261" s="2" t="inlineStr">
-        <is>
-          <t>1月23日</t>
-        </is>
+      <c r="B261" s="6" t="n">
+        <v>46045</v>
       </c>
       <c r="C261" s="2" t="inlineStr">
         <is>
@@ -16231,7 +16295,7 @@
       </c>
       <c r="D261" s="2" t="inlineStr">
         <is>
-          <t>ec</t>
+          <t>EC</t>
         </is>
       </c>
       <c r="E261" s="2" t="inlineStr">
@@ -16241,7 +16305,7 @@
       </c>
       <c r="F261" s="2" t="inlineStr">
         <is>
-          <t>メンバー</t>
+          <t>会員</t>
         </is>
       </c>
       <c r="G261" s="2" t="inlineStr">
@@ -16278,6 +16342,7 @@
           <t>無効</t>
         </is>
       </c>
+      <c r="O261" s="2" t="inlineStr"/>
     </row>
     <row r="262">
       <c r="A262" s="2" t="inlineStr">
@@ -16285,7 +16350,7 @@
           <t>A-20260261</t>
         </is>
       </c>
-      <c r="B262" s="3" t="n">
+      <c r="B262" s="6" t="n">
         <v>46037</v>
       </c>
       <c r="C262" s="2" t="inlineStr">
@@ -16295,7 +16360,7 @@
       </c>
       <c r="D262" s="2" t="inlineStr">
         <is>
-          <t>Web</t>
+          <t>EC</t>
         </is>
       </c>
       <c r="E262" s="2" t="inlineStr">
@@ -16334,6 +16399,7 @@
           <t>有効</t>
         </is>
       </c>
+      <c r="O262" s="2" t="inlineStr"/>
     </row>
     <row r="263">
       <c r="A263" s="2" t="inlineStr">
@@ -16341,7 +16407,7 @@
           <t>A-20260262</t>
         </is>
       </c>
-      <c r="B263" s="3" t="n">
+      <c r="B263" s="6" t="n">
         <v>46042</v>
       </c>
       <c r="C263" s="2" t="inlineStr">
@@ -16361,7 +16427,7 @@
       </c>
       <c r="F263" s="2" t="inlineStr">
         <is>
-          <t>メンバー</t>
+          <t>会員</t>
         </is>
       </c>
       <c r="G263" s="2" t="inlineStr">
@@ -16377,13 +16443,11 @@
       <c r="I263" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="J263" s="2" t="inlineStr">
-        <is>
-          <t>¥3,200</t>
-        </is>
+      <c r="J263" s="2" t="n">
+        <v>3200</v>
       </c>
       <c r="K263" s="2" t="n">
-        <v>5</v>
+        <v>0.05</v>
       </c>
       <c r="L263" s="2" t="inlineStr">
         <is>
@@ -16396,6 +16460,7 @@
           <t>有効</t>
         </is>
       </c>
+      <c r="O263" s="2" t="inlineStr"/>
     </row>
     <row r="264">
       <c r="A264" s="2" t="inlineStr">
@@ -16403,10 +16468,8 @@
           <t>A-20260263</t>
         </is>
       </c>
-      <c r="B264" s="2" t="inlineStr">
-        <is>
-          <t>2026/1/7</t>
-        </is>
+      <c r="B264" s="6" t="n">
+        <v>46029</v>
       </c>
       <c r="C264" s="2" t="inlineStr">
         <is>
@@ -16415,7 +16478,7 @@
       </c>
       <c r="D264" s="2" t="inlineStr">
         <is>
-          <t>オフライン</t>
+          <t>店頭</t>
         </is>
       </c>
       <c r="E264" s="2" t="inlineStr">
@@ -16458,6 +16521,7 @@
           <t>有効</t>
         </is>
       </c>
+      <c r="O264" s="2" t="inlineStr"/>
     </row>
     <row r="265">
       <c r="A265" s="2" t="inlineStr">
@@ -16465,8 +16529,8 @@
           <t>A-20260264</t>
         </is>
       </c>
-      <c r="B265" s="2" t="n">
-        <v>20260117</v>
+      <c r="B265" s="6" t="n">
+        <v>46039</v>
       </c>
       <c r="C265" s="2" t="inlineStr">
         <is>
@@ -16475,7 +16539,7 @@
       </c>
       <c r="D265" s="2" t="inlineStr">
         <is>
-          <t>ec</t>
+          <t>EC</t>
         </is>
       </c>
       <c r="E265" s="2" t="inlineStr">
@@ -16490,7 +16554,7 @@
       </c>
       <c r="G265" s="2" t="inlineStr">
         <is>
-          <t>抽出器具</t>
+          <t>器具</t>
         </is>
       </c>
       <c r="H265" s="2" t="inlineStr">
@@ -16518,6 +16582,7 @@
           <t>有効</t>
         </is>
       </c>
+      <c r="O265" s="2" t="inlineStr"/>
     </row>
     <row r="266">
       <c r="A266" s="2" t="inlineStr">
@@ -16525,17 +16590,17 @@
           <t>A-20260265</t>
         </is>
       </c>
-      <c r="B266" s="3" t="n">
+      <c r="B266" s="6" t="n">
         <v>46024</v>
       </c>
       <c r="C266" s="2" t="inlineStr">
         <is>
-          <t>名古屋 店</t>
+          <t>名古屋店</t>
         </is>
       </c>
       <c r="D266" s="2" t="inlineStr">
         <is>
-          <t>オフライン</t>
+          <t>店頭</t>
         </is>
       </c>
       <c r="E266" s="2" t="inlineStr">
@@ -16578,6 +16643,7 @@
           <t>有効</t>
         </is>
       </c>
+      <c r="O266" s="2" t="inlineStr"/>
     </row>
     <row r="267">
       <c r="A267" s="2" t="inlineStr">
@@ -16585,7 +16651,7 @@
           <t>A-20260266</t>
         </is>
       </c>
-      <c r="B267" s="3" t="n">
+      <c r="B267" s="6" t="n">
         <v>46032</v>
       </c>
       <c r="C267" s="2" t="inlineStr">
@@ -16642,6 +16708,7 @@
           <t>無効</t>
         </is>
       </c>
+      <c r="O267" s="2" t="inlineStr"/>
     </row>
     <row r="268">
       <c r="A268" s="2" t="inlineStr">
@@ -16649,12 +16716,12 @@
           <t>A-20260267</t>
         </is>
       </c>
-      <c r="B268" s="3" t="n">
+      <c r="B268" s="6" t="n">
         <v>46031</v>
       </c>
       <c r="C268" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">横浜店 </t>
+          <t>横浜店</t>
         </is>
       </c>
       <c r="D268" s="2" t="inlineStr">
@@ -16702,6 +16769,7 @@
           <t>有効</t>
         </is>
       </c>
+      <c r="O268" s="2" t="inlineStr"/>
     </row>
     <row r="269">
       <c r="A269" s="2" t="inlineStr">
@@ -16709,14 +16777,12 @@
           <t>A-20260268</t>
         </is>
       </c>
-      <c r="B269" s="2" t="inlineStr">
-        <is>
-          <t>2026-01-18</t>
-        </is>
+      <c r="B269" s="6" t="n">
+        <v>46040</v>
       </c>
       <c r="C269" s="2" t="inlineStr">
         <is>
-          <t>名古屋 店</t>
+          <t>名古屋店</t>
         </is>
       </c>
       <c r="D269" s="2" t="inlineStr">
@@ -16732,7 +16798,7 @@
       <c r="F269" s="2" t="n"/>
       <c r="G269" s="2" t="inlineStr">
         <is>
-          <t>コーヒー</t>
+          <t>コーヒー豆</t>
         </is>
       </c>
       <c r="H269" s="2" t="inlineStr">
@@ -16760,6 +16826,7 @@
           <t>有効</t>
         </is>
       </c>
+      <c r="O269" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
